--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -530,50 +530,50 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>102.4</v>
+        <v>100.23</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.13</v>
+        <v>-2.12</v>
       </c>
       <c r="E2" t="n">
-        <v>103.6</v>
+        <v>102.73</v>
       </c>
       <c r="F2" t="n">
+        <v>102.77</v>
+      </c>
+      <c r="G2" t="n">
         <v>102.9</v>
       </c>
-      <c r="G2" t="n">
-        <v>103.2</v>
-      </c>
       <c r="H2" t="n">
-        <v>-0.456</v>
+        <v>-0.5580000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.531</v>
+        <v>-0.422</v>
       </c>
       <c r="J2" t="n">
-        <v>10.29</v>
+        <v>20.52</v>
       </c>
       <c r="K2" t="n">
-        <v>15.69</v>
+        <v>15.51</v>
       </c>
       <c r="L2" t="n">
-        <v>0.66</v>
+        <v>1.32</v>
       </c>
       <c r="M2" t="n">
-        <v>102.53</v>
+        <v>101.4</v>
       </c>
       <c r="N2" t="n">
-        <v>103.18</v>
+        <v>101.78</v>
       </c>
       <c r="O2" t="n">
-        <v>101.9</v>
+        <v>100.04</v>
       </c>
       <c r="P2" t="n">
-        <v>0.27</v>
+        <v>0.53</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="R2" t="n">
@@ -594,50 +594,50 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>413</v>
+        <v>401.99</v>
       </c>
       <c r="D3" t="n">
-        <v>3.12</v>
+        <v>-2.67</v>
       </c>
       <c r="E3" t="n">
-        <v>405.78</v>
+        <v>404.5</v>
       </c>
       <c r="F3" t="n">
-        <v>395.2</v>
+        <v>399.65</v>
       </c>
       <c r="G3" t="n">
-        <v>372.89</v>
+        <v>374.72</v>
       </c>
       <c r="H3" t="n">
-        <v>14.379</v>
+        <v>14.352</v>
       </c>
       <c r="I3" t="n">
-        <v>10.013</v>
+        <v>11.096</v>
       </c>
       <c r="J3" t="n">
-        <v>53.73</v>
+        <v>44.61</v>
       </c>
       <c r="K3" t="n">
-        <v>33.29</v>
+        <v>34.41</v>
       </c>
       <c r="L3" t="n">
-        <v>1.61</v>
+        <v>1.3</v>
       </c>
       <c r="M3" t="n">
-        <v>405.08</v>
+        <v>417.33</v>
       </c>
       <c r="N3" t="n">
-        <v>422.08</v>
+        <v>417.36</v>
       </c>
       <c r="O3" t="n">
-        <v>400.13</v>
+        <v>398.75</v>
       </c>
       <c r="P3" t="n">
-        <v>1.26</v>
+        <v>1.05</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="R3" t="n">
@@ -658,50 +658,50 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>25.3</v>
+        <v>24.29</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.21</v>
+        <v>-3.99</v>
       </c>
       <c r="E4" t="n">
-        <v>25.66</v>
+        <v>25.42</v>
       </c>
       <c r="F4" t="n">
-        <v>25.81</v>
+        <v>25.65</v>
       </c>
       <c r="G4" t="n">
-        <v>26.42</v>
+        <v>26.26</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.53</v>
+        <v>-0.624</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.463</v>
+        <v>-0.495</v>
       </c>
       <c r="J4" t="n">
-        <v>100.9</v>
+        <v>199.27</v>
       </c>
       <c r="K4" t="n">
-        <v>111.34</v>
+        <v>115.85</v>
       </c>
       <c r="L4" t="n">
-        <v>0.91</v>
+        <v>1.72</v>
       </c>
       <c r="M4" t="n">
-        <v>25.62</v>
+        <v>25</v>
       </c>
       <c r="N4" t="n">
-        <v>25.71</v>
+        <v>25</v>
       </c>
       <c r="O4" t="n">
-        <v>25.3</v>
+        <v>24.09</v>
       </c>
       <c r="P4" t="n">
-        <v>0.83</v>
+        <v>1.64</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="R4" t="n">
@@ -722,50 +722,50 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>81.65000000000001</v>
+        <v>77.75</v>
       </c>
       <c r="D5" t="n">
-        <v>-2.66</v>
+        <v>-4.78</v>
       </c>
       <c r="E5" t="n">
-        <v>83.58</v>
+        <v>82.17</v>
       </c>
       <c r="F5" t="n">
-        <v>87.53</v>
+        <v>86.12</v>
       </c>
       <c r="G5" t="n">
-        <v>89.52</v>
+        <v>89.09</v>
       </c>
       <c r="H5" t="n">
-        <v>-3.007</v>
+        <v>-3.254</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.243</v>
+        <v>-2.12</v>
       </c>
       <c r="J5" t="n">
-        <v>26.8</v>
+        <v>33.63</v>
       </c>
       <c r="K5" t="n">
-        <v>47.26</v>
+        <v>47.52</v>
       </c>
       <c r="L5" t="n">
-        <v>0.57</v>
+        <v>0.71</v>
       </c>
       <c r="M5" t="n">
-        <v>84</v>
+        <v>79.8</v>
       </c>
       <c r="N5" t="n">
-        <v>84.68000000000001</v>
+        <v>81.73999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>81.45</v>
+        <v>77.66</v>
       </c>
       <c r="P5" t="n">
-        <v>2.27</v>
+        <v>2.84</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="R5" t="n">
@@ -786,50 +786,50 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>612</v>
+        <v>599.62</v>
       </c>
       <c r="D6" t="n">
-        <v>6.4</v>
+        <v>-2.02</v>
       </c>
       <c r="E6" t="n">
-        <v>574.38</v>
+        <v>581.96</v>
       </c>
       <c r="F6" t="n">
-        <v>557.64</v>
+        <v>565</v>
       </c>
       <c r="G6" t="n">
-        <v>555.48</v>
+        <v>558.91</v>
       </c>
       <c r="H6" t="n">
-        <v>1.148</v>
+        <v>2.769</v>
       </c>
       <c r="I6" t="n">
-        <v>-6.516</v>
+        <v>-5.89</v>
       </c>
       <c r="J6" t="n">
-        <v>53.85</v>
+        <v>37.85</v>
       </c>
       <c r="K6" t="n">
-        <v>31.67</v>
+        <v>32.26</v>
       </c>
       <c r="L6" t="n">
-        <v>1.7</v>
+        <v>1.17</v>
       </c>
       <c r="M6" t="n">
-        <v>605</v>
+        <v>590.3099999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>632.72</v>
+        <v>618.1</v>
       </c>
       <c r="O6" t="n">
-        <v>604.1</v>
+        <v>585</v>
       </c>
       <c r="P6" t="n">
-        <v>4.87</v>
+        <v>3.42</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="R6" t="n">
@@ -850,50 +850,50 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7.5</v>
+        <v>7.25</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4</v>
+        <v>-3.33</v>
       </c>
       <c r="E7" t="n">
         <v>7.41</v>
       </c>
       <c r="F7" t="n">
-        <v>7.27</v>
+        <v>7.28</v>
       </c>
       <c r="G7" t="n">
         <v>7.16</v>
       </c>
       <c r="H7" t="n">
-        <v>0.05</v>
+        <v>0.057</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.01</v>
+        <v>0.02</v>
       </c>
       <c r="J7" t="n">
-        <v>391.25</v>
+        <v>502.32</v>
       </c>
       <c r="K7" t="n">
-        <v>332.52</v>
+        <v>341.77</v>
       </c>
       <c r="L7" t="n">
-        <v>1.18</v>
+        <v>1.47</v>
       </c>
       <c r="M7" t="n">
-        <v>7.53</v>
+        <v>7.48</v>
       </c>
       <c r="N7" t="n">
-        <v>7.61</v>
+        <v>7.48</v>
       </c>
       <c r="O7" t="n">
-        <v>7.48</v>
+        <v>7.2</v>
       </c>
       <c r="P7" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="R7" t="n">
@@ -914,50 +914,50 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>15.83</v>
+        <v>15.38</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-2.84</v>
       </c>
       <c r="E8" t="n">
-        <v>16.05</v>
+        <v>15.91</v>
       </c>
       <c r="F8" t="n">
-        <v>15.86</v>
+        <v>15.85</v>
       </c>
       <c r="G8" t="n">
-        <v>15.62</v>
+        <v>15.68</v>
       </c>
       <c r="H8" t="n">
-        <v>0.338</v>
+        <v>0.273</v>
       </c>
       <c r="I8" t="n">
-        <v>0.344</v>
+        <v>0.324</v>
       </c>
       <c r="J8" t="n">
-        <v>148.64</v>
+        <v>144.1</v>
       </c>
       <c r="K8" t="n">
-        <v>178.14</v>
+        <v>181.7</v>
       </c>
       <c r="L8" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="M8" t="n">
-        <v>15.69</v>
+        <v>15.66</v>
       </c>
       <c r="N8" t="n">
-        <v>15.96</v>
+        <v>15.7</v>
       </c>
       <c r="O8" t="n">
-        <v>15.65</v>
+        <v>15.33</v>
       </c>
       <c r="P8" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="R8" t="n">

--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -464,57 +464,57 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t>KDJ_K</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>KDJ_D</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>KDJ_J</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
           <t>成交量(万)</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>均量(万)</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>量比</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>开盘价</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>最高价</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>最低价</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>换手率</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>更新日期</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>DAYS_BACK</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>所属行业</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>关注理由</t>
         </is>
       </c>
     </row>
@@ -530,57 +530,61 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>102.65</v>
+        <v>102.72</v>
       </c>
       <c r="D2" t="n">
-        <v>1.35</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>101.59</v>
+        <v>102.09</v>
       </c>
       <c r="F2" t="n">
-        <v>102.59</v>
+        <v>102.41</v>
       </c>
       <c r="G2" t="n">
-        <v>102.38</v>
+        <v>102.35</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.535</v>
+        <v>-0.948</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.493</v>
+        <v>-1.162</v>
       </c>
       <c r="J2" t="n">
-        <v>10.3</v>
+        <v>40.45</v>
       </c>
       <c r="K2" t="n">
-        <v>14.22</v>
+        <v>35.1</v>
       </c>
       <c r="L2" t="n">
-        <v>0.72</v>
+        <v>51.16</v>
       </c>
       <c r="M2" t="n">
-        <v>100.5</v>
+        <v>4.74</v>
       </c>
       <c r="N2" t="n">
-        <v>102.88</v>
+        <v>13.43</v>
       </c>
       <c r="O2" t="n">
-        <v>100.41</v>
+        <v>0.35</v>
       </c>
       <c r="P2" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
+        <v>101.99</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>102.85</v>
       </c>
       <c r="R2" t="n">
-        <v>2</v>
-      </c>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
+        <v>101.8</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -594,57 +598,61 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>416.18</v>
+        <v>409.96</v>
       </c>
       <c r="D3" t="n">
-        <v>3.4</v>
+        <v>-1.49</v>
       </c>
       <c r="E3" t="n">
-        <v>403.09</v>
+        <v>404.69</v>
       </c>
       <c r="F3" t="n">
-        <v>404.44</v>
+        <v>404.6</v>
       </c>
       <c r="G3" t="n">
-        <v>384.78</v>
+        <v>388.27</v>
       </c>
       <c r="H3" t="n">
-        <v>13.557</v>
+        <v>13.447</v>
       </c>
       <c r="I3" t="n">
-        <v>12.557</v>
+        <v>12.726</v>
       </c>
       <c r="J3" t="n">
-        <v>30.26</v>
+        <v>60.33</v>
       </c>
       <c r="K3" t="n">
-        <v>34.9</v>
+        <v>58.3</v>
       </c>
       <c r="L3" t="n">
-        <v>0.87</v>
+        <v>64.37</v>
       </c>
       <c r="M3" t="n">
-        <v>406.12</v>
+        <v>15.03</v>
       </c>
       <c r="N3" t="n">
-        <v>418.33</v>
+        <v>34.23</v>
       </c>
       <c r="O3" t="n">
-        <v>401.73</v>
+        <v>0.44</v>
       </c>
       <c r="P3" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
+        <v>413</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>418.85</v>
       </c>
       <c r="R3" t="n">
-        <v>2</v>
-      </c>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
+        <v>405.6</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -658,57 +666,61 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>24.26</v>
+        <v>24.03</v>
       </c>
       <c r="D4" t="n">
-        <v>0.54</v>
+        <v>-0.95</v>
       </c>
       <c r="E4" t="n">
-        <v>24.34</v>
+        <v>24.29</v>
       </c>
       <c r="F4" t="n">
-        <v>25</v>
+        <v>24.85</v>
       </c>
       <c r="G4" t="n">
-        <v>25.62</v>
+        <v>25.47</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.774</v>
+        <v>-0.826</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.647</v>
+        <v>-0.717</v>
       </c>
       <c r="J4" t="n">
-        <v>94.77</v>
+        <v>10.1</v>
       </c>
       <c r="K4" t="n">
-        <v>118.01</v>
+        <v>13.15</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8</v>
+        <v>4.01</v>
       </c>
       <c r="M4" t="n">
-        <v>24.05</v>
+        <v>46.83</v>
       </c>
       <c r="N4" t="n">
-        <v>24.37</v>
+        <v>113.8</v>
       </c>
       <c r="O4" t="n">
-        <v>24.01</v>
+        <v>0.41</v>
       </c>
       <c r="P4" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
+        <v>23.99</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>24.17</v>
       </c>
       <c r="R4" t="n">
-        <v>2</v>
-      </c>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
+        <v>23.88</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -722,57 +734,61 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>77.75</v>
+        <v>80.05</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.19</v>
+        <v>2.96</v>
       </c>
       <c r="E5" t="n">
-        <v>78.44</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>81.01000000000001</v>
+        <v>80.53</v>
       </c>
       <c r="G5" t="n">
-        <v>86.98999999999999</v>
+        <v>85.98</v>
       </c>
       <c r="H5" t="n">
-        <v>-3.881</v>
+        <v>-3.525</v>
       </c>
       <c r="I5" t="n">
-        <v>-3.003</v>
+        <v>-2.823</v>
       </c>
       <c r="J5" t="n">
-        <v>23.07</v>
+        <v>25.62</v>
       </c>
       <c r="K5" t="n">
-        <v>43.6</v>
+        <v>19.32</v>
       </c>
       <c r="L5" t="n">
-        <v>0.53</v>
+        <v>38.22</v>
       </c>
       <c r="M5" t="n">
-        <v>77</v>
+        <v>23.36</v>
       </c>
       <c r="N5" t="n">
-        <v>78.58</v>
+        <v>38.72</v>
       </c>
       <c r="O5" t="n">
-        <v>76.54000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="P5" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
+        <v>76.59999999999999</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>80.97</v>
       </c>
       <c r="R5" t="n">
-        <v>2</v>
-      </c>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
+        <v>76.59999999999999</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -786,57 +802,61 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>598</v>
+        <v>580.9</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.64</v>
+        <v>-2.86</v>
       </c>
       <c r="E6" t="n">
-        <v>608.6799999999999</v>
+        <v>604.9400000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>591.53</v>
+        <v>593.45</v>
       </c>
       <c r="G6" t="n">
-        <v>569.78</v>
+        <v>570.3</v>
       </c>
       <c r="H6" t="n">
-        <v>12.109</v>
+        <v>9.401</v>
       </c>
       <c r="I6" t="n">
-        <v>5.091</v>
+        <v>4.619</v>
       </c>
       <c r="J6" t="n">
-        <v>22.43</v>
+        <v>57.28</v>
       </c>
       <c r="K6" t="n">
-        <v>31.93</v>
+        <v>67.23999999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7</v>
+        <v>37.35</v>
       </c>
       <c r="M6" t="n">
-        <v>598.85</v>
+        <v>11.73</v>
       </c>
       <c r="N6" t="n">
-        <v>609.88</v>
+        <v>30.05</v>
       </c>
       <c r="O6" t="n">
-        <v>588.66</v>
+        <v>0.39</v>
       </c>
       <c r="P6" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
+        <v>585</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>593</v>
       </c>
       <c r="R6" t="n">
-        <v>2</v>
-      </c>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
+        <v>579</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -850,57 +870,61 @@
         </is>
       </c>
       <c r="C7" t="n">
+        <v>7.48</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="E7" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="F7" t="n">
         <v>7.4</v>
       </c>
-      <c r="D7" t="n">
-        <v>-0.27</v>
-      </c>
-      <c r="E7" t="n">
-        <v>7.35</v>
-      </c>
-      <c r="F7" t="n">
-        <v>7.38</v>
-      </c>
       <c r="G7" t="n">
-        <v>7.24</v>
+        <v>7.27</v>
       </c>
       <c r="H7" t="n">
-        <v>0.063</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>0.045</v>
+        <v>0.048</v>
       </c>
       <c r="J7" t="n">
-        <v>279.07</v>
+        <v>59.19</v>
       </c>
       <c r="K7" t="n">
-        <v>348.23</v>
+        <v>60.41</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8</v>
+        <v>56.75</v>
       </c>
       <c r="M7" t="n">
-        <v>7.41</v>
+        <v>158.72</v>
       </c>
       <c r="N7" t="n">
-        <v>7.47</v>
+        <v>337.48</v>
       </c>
       <c r="O7" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="P7" t="n">
         <v>7.37</v>
       </c>
-      <c r="P7" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
+      <c r="Q7" t="n">
+        <v>7.5</v>
       </c>
       <c r="R7" t="n">
-        <v>2</v>
-      </c>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
+        <v>7.36</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -914,57 +938,61 @@
         </is>
       </c>
       <c r="C8" t="n">
+        <v>15.35</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="E8" t="n">
+        <v>15.29</v>
+      </c>
+      <c r="F8" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="G8" t="n">
+        <v>15.74</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.189</v>
+      </c>
+      <c r="J8" t="n">
+        <v>18.11</v>
+      </c>
+      <c r="K8" t="n">
+        <v>24.39</v>
+      </c>
+      <c r="L8" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="M8" t="n">
+        <v>64.59</v>
+      </c>
+      <c r="N8" t="n">
+        <v>161.83</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P8" t="n">
         <v>15.17</v>
       </c>
-      <c r="D8" t="n">
-        <v>-0.59</v>
-      </c>
-      <c r="E8" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="F8" t="n">
-        <v>15.67</v>
-      </c>
-      <c r="G8" t="n">
-        <v>15.75</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.221</v>
-      </c>
-      <c r="J8" t="n">
-        <v>72.44</v>
-      </c>
-      <c r="K8" t="n">
-        <v>173.34</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="M8" t="n">
-        <v>15.16</v>
-      </c>
-      <c r="N8" t="n">
-        <v>15.25</v>
-      </c>
-      <c r="O8" t="n">
-        <v>15.06</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
+      <c r="Q8" t="n">
+        <v>15.46</v>
       </c>
       <c r="R8" t="n">
-        <v>2</v>
-      </c>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
+        <v>15.1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -978,57 +1006,61 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>34.73</v>
+        <v>34.22</v>
       </c>
       <c r="D9" t="n">
-        <v>3.21</v>
+        <v>-1.47</v>
       </c>
       <c r="E9" t="n">
-        <v>34.67</v>
+        <v>34.66</v>
       </c>
       <c r="F9" t="n">
-        <v>36.05</v>
+        <v>35.74</v>
       </c>
       <c r="G9" t="n">
-        <v>37.4</v>
+        <v>37.32</v>
       </c>
       <c r="H9" t="n">
-        <v>0.032</v>
+        <v>-0.08599999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.555</v>
       </c>
       <c r="J9" t="n">
-        <v>86.44</v>
+        <v>19.24</v>
       </c>
       <c r="K9" t="n">
-        <v>188.17</v>
+        <v>20.35</v>
       </c>
       <c r="L9" t="n">
-        <v>0.46</v>
+        <v>17.03</v>
       </c>
       <c r="M9" t="n">
-        <v>32.87</v>
+        <v>40.39</v>
       </c>
       <c r="N9" t="n">
-        <v>34.99</v>
+        <v>177.62</v>
       </c>
       <c r="O9" t="n">
-        <v>32.81</v>
+        <v>0.23</v>
       </c>
       <c r="P9" t="n">
-        <v>7.55</v>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
+        <v>33.78</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>34.62</v>
       </c>
       <c r="R9" t="n">
-        <v>2</v>
-      </c>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
+        <v>33.57</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1042,57 +1074,61 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>220.95</v>
+        <v>215.58</v>
       </c>
       <c r="D10" t="n">
-        <v>1.03</v>
+        <v>-2.43</v>
       </c>
       <c r="E10" t="n">
-        <v>215.47</v>
+        <v>217.18</v>
       </c>
       <c r="F10" t="n">
-        <v>220.88</v>
+        <v>219.05</v>
       </c>
       <c r="G10" t="n">
-        <v>231.87</v>
+        <v>229.71</v>
       </c>
       <c r="H10" t="n">
-        <v>-10.01</v>
+        <v>-9.303000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-9.286</v>
+        <v>-8.539999999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>18.4</v>
+        <v>39.46</v>
       </c>
       <c r="K10" t="n">
-        <v>20.08</v>
+        <v>31.12</v>
       </c>
       <c r="L10" t="n">
-        <v>0.92</v>
+        <v>56.15</v>
       </c>
       <c r="M10" t="n">
-        <v>214.6</v>
+        <v>7.86</v>
       </c>
       <c r="N10" t="n">
-        <v>223.89</v>
+        <v>19.13</v>
       </c>
       <c r="O10" t="n">
-        <v>210.3</v>
+        <v>0.41</v>
       </c>
       <c r="P10" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
+        <v>218.6</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>218.88</v>
       </c>
       <c r="R10" t="n">
-        <v>2</v>
-      </c>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
+        <v>213.07</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1106,57 +1142,61 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>447.41</v>
+        <v>449.85</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.1</v>
+        <v>0.55</v>
       </c>
       <c r="E11" t="n">
-        <v>461.81</v>
+        <v>459.69</v>
       </c>
       <c r="F11" t="n">
-        <v>446</v>
+        <v>449.66</v>
       </c>
       <c r="G11" t="n">
-        <v>417.16</v>
+        <v>420.6</v>
       </c>
       <c r="H11" t="n">
-        <v>20.038</v>
+        <v>19.09</v>
       </c>
       <c r="I11" t="n">
-        <v>14.784</v>
+        <v>15.416</v>
       </c>
       <c r="J11" t="n">
-        <v>29.83</v>
+        <v>65.38</v>
       </c>
       <c r="K11" t="n">
-        <v>46.05</v>
+        <v>71.67</v>
       </c>
       <c r="L11" t="n">
-        <v>0.65</v>
+        <v>52.79</v>
       </c>
       <c r="M11" t="n">
-        <v>446.29</v>
+        <v>12.19</v>
       </c>
       <c r="N11" t="n">
-        <v>461.3</v>
+        <v>43.9</v>
       </c>
       <c r="O11" t="n">
-        <v>440.01</v>
+        <v>0.28</v>
       </c>
       <c r="P11" t="n">
-        <v>3.37</v>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
+        <v>445.2</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>460.58</v>
       </c>
       <c r="R11" t="n">
-        <v>2</v>
-      </c>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
+        <v>445.2</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1170,57 +1210,61 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>317.6</v>
+        <v>310.36</v>
       </c>
       <c r="D12" t="n">
         <v>-2.28</v>
       </c>
       <c r="E12" t="n">
-        <v>311.58</v>
+        <v>313.95</v>
       </c>
       <c r="F12" t="n">
-        <v>307.24</v>
+        <v>307.16</v>
       </c>
       <c r="G12" t="n">
-        <v>319.38</v>
+        <v>317.4</v>
       </c>
       <c r="H12" t="n">
-        <v>6.535</v>
+        <v>4.353</v>
       </c>
       <c r="I12" t="n">
-        <v>9.84</v>
+        <v>7.026</v>
       </c>
       <c r="J12" t="n">
-        <v>28.87</v>
+        <v>53.84</v>
       </c>
       <c r="K12" t="n">
-        <v>36.34</v>
+        <v>52.05</v>
       </c>
       <c r="L12" t="n">
-        <v>0.79</v>
+        <v>57.44</v>
       </c>
       <c r="M12" t="n">
-        <v>311</v>
+        <v>12.62</v>
       </c>
       <c r="N12" t="n">
-        <v>325.85</v>
+        <v>34.25</v>
       </c>
       <c r="O12" t="n">
-        <v>302.25</v>
+        <v>0.37</v>
       </c>
       <c r="P12" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
+        <v>314.16</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>320</v>
       </c>
       <c r="R12" t="n">
-        <v>2</v>
-      </c>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
+        <v>308</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1234,57 +1278,61 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>109.5</v>
+        <v>106.51</v>
       </c>
       <c r="D13" t="n">
-        <v>3.94</v>
+        <v>-2.73</v>
       </c>
       <c r="E13" t="n">
-        <v>111.19</v>
+        <v>109.82</v>
       </c>
       <c r="F13" t="n">
-        <v>113.51</v>
+        <v>112.44</v>
       </c>
       <c r="G13" t="n">
-        <v>113.62</v>
+        <v>114.2</v>
       </c>
       <c r="H13" t="n">
-        <v>5.639</v>
+        <v>4.912</v>
       </c>
       <c r="I13" t="n">
-        <v>7.95</v>
+        <v>7.516</v>
       </c>
       <c r="J13" t="n">
-        <v>98.01000000000001</v>
+        <v>20.86</v>
       </c>
       <c r="K13" t="n">
-        <v>126.32</v>
+        <v>25.36</v>
       </c>
       <c r="L13" t="n">
-        <v>0.78</v>
+        <v>11.86</v>
       </c>
       <c r="M13" t="n">
-        <v>103.18</v>
+        <v>37.65</v>
       </c>
       <c r="N13" t="n">
-        <v>111.24</v>
+        <v>123.69</v>
       </c>
       <c r="O13" t="n">
-        <v>103.18</v>
+        <v>0.3</v>
       </c>
       <c r="P13" t="n">
-        <v>9.75</v>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
+        <v>109</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>110.5</v>
       </c>
       <c r="R13" t="n">
-        <v>2</v>
-      </c>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
+        <v>105.57</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1298,57 +1346,61 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>258.66</v>
+        <v>254.03</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.27</v>
+        <v>-1.79</v>
       </c>
       <c r="E14" t="n">
-        <v>269.22</v>
+        <v>265.36</v>
       </c>
       <c r="F14" t="n">
-        <v>285.34</v>
+        <v>280.13</v>
       </c>
       <c r="G14" t="n">
-        <v>283.12</v>
+        <v>281.17</v>
       </c>
       <c r="H14" t="n">
-        <v>-6.083</v>
+        <v>-8.273</v>
       </c>
       <c r="I14" t="n">
-        <v>-2.9</v>
+        <v>-4.774</v>
       </c>
       <c r="J14" t="n">
-        <v>28.98</v>
+        <v>24.8</v>
       </c>
       <c r="K14" t="n">
-        <v>29.41</v>
+        <v>32.77</v>
       </c>
       <c r="L14" t="n">
-        <v>0.99</v>
+        <v>8.85</v>
       </c>
       <c r="M14" t="n">
-        <v>248.98</v>
+        <v>10.96</v>
       </c>
       <c r="N14" t="n">
-        <v>260.18</v>
+        <v>29.03</v>
       </c>
       <c r="O14" t="n">
-        <v>240.25</v>
+        <v>0.38</v>
       </c>
       <c r="P14" t="n">
-        <v>4.34</v>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
+        <v>252</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>255.88</v>
       </c>
       <c r="R14" t="n">
-        <v>2</v>
-      </c>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
+        <v>250.03</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1362,57 +1414,61 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>238.4</v>
+        <v>230.33</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.24</v>
+        <v>-3.39</v>
       </c>
       <c r="E15" t="n">
-        <v>237.45</v>
+        <v>238.51</v>
       </c>
       <c r="F15" t="n">
-        <v>240.09</v>
+        <v>239.35</v>
       </c>
       <c r="G15" t="n">
-        <v>217.09</v>
+        <v>220.58</v>
       </c>
       <c r="H15" t="n">
-        <v>16.529</v>
+        <v>14.88</v>
       </c>
       <c r="I15" t="n">
-        <v>15.556</v>
+        <v>15.017</v>
       </c>
       <c r="J15" t="n">
-        <v>33.77</v>
+        <v>52.29</v>
       </c>
       <c r="K15" t="n">
-        <v>43.01</v>
+        <v>61.59</v>
       </c>
       <c r="L15" t="n">
-        <v>0.79</v>
+        <v>33.69</v>
       </c>
       <c r="M15" t="n">
-        <v>222.97</v>
+        <v>18.64</v>
       </c>
       <c r="N15" t="n">
-        <v>243.33</v>
+        <v>42.98</v>
       </c>
       <c r="O15" t="n">
-        <v>220</v>
+        <v>0.43</v>
       </c>
       <c r="P15" t="n">
-        <v>7.23</v>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
+        <v>231.21</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>240.58</v>
       </c>
       <c r="R15" t="n">
-        <v>2</v>
-      </c>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
+        <v>228.88</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1426,57 +1482,61 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>44.44</v>
+        <v>44.69</v>
       </c>
       <c r="D16" t="n">
-        <v>-2.03</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>46.69</v>
+        <v>46.01</v>
       </c>
       <c r="F16" t="n">
-        <v>49.94</v>
+        <v>49.85</v>
       </c>
       <c r="G16" t="n">
-        <v>43.39</v>
+        <v>43.87</v>
       </c>
       <c r="H16" t="n">
-        <v>3.292</v>
+        <v>2.838</v>
       </c>
       <c r="I16" t="n">
-        <v>3.605</v>
+        <v>3.364</v>
       </c>
       <c r="J16" t="n">
-        <v>21.85</v>
+        <v>25.39</v>
       </c>
       <c r="K16" t="n">
-        <v>31.45</v>
+        <v>42.23</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6899999999999999</v>
+        <v>-8.279999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>43.46</v>
+        <v>11.19</v>
       </c>
       <c r="N16" t="n">
-        <v>45.26</v>
+        <v>31.35</v>
       </c>
       <c r="O16" t="n">
-        <v>43.09</v>
+        <v>0.36</v>
       </c>
       <c r="P16" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
+        <v>44.05</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>45.32</v>
       </c>
       <c r="R16" t="n">
-        <v>2</v>
-      </c>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
+        <v>43.65</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1490,57 +1550,61 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>21.13</v>
+        <v>20.61</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.66</v>
+        <v>-2.46</v>
       </c>
       <c r="E17" t="n">
-        <v>21.97</v>
+        <v>21.59</v>
       </c>
       <c r="F17" t="n">
-        <v>22.75</v>
+        <v>22.71</v>
       </c>
       <c r="G17" t="n">
-        <v>20.89</v>
+        <v>20.99</v>
       </c>
       <c r="H17" t="n">
-        <v>0.695</v>
+        <v>0.512</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.618</v>
       </c>
       <c r="J17" t="n">
-        <v>27.27</v>
+        <v>20.23</v>
       </c>
       <c r="K17" t="n">
-        <v>40.3</v>
+        <v>36.73</v>
       </c>
       <c r="L17" t="n">
-        <v>0.68</v>
+        <v>-12.77</v>
       </c>
       <c r="M17" t="n">
-        <v>20.59</v>
+        <v>11.06</v>
       </c>
       <c r="N17" t="n">
-        <v>21.42</v>
+        <v>40.02</v>
       </c>
       <c r="O17" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="P17" t="n">
+        <v>20.67</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>21.09</v>
+      </c>
+      <c r="R17" t="n">
         <v>20.36</v>
       </c>
-      <c r="P17" t="n">
-        <v>7.39</v>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="R17" t="n">
-        <v>2</v>
-      </c>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
+      <c r="S17" t="n">
+        <v>3</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1554,57 +1618,61 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>16.79</v>
+        <v>16.12</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.06</v>
+        <v>-3.99</v>
       </c>
       <c r="E18" t="n">
-        <v>18.35</v>
+        <v>17.37</v>
       </c>
       <c r="F18" t="n">
-        <v>18.9</v>
+        <v>18.92</v>
       </c>
       <c r="G18" t="n">
-        <v>16.65</v>
+        <v>16.73</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.757</v>
       </c>
       <c r="I18" t="n">
-        <v>0.946</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>18.08</v>
+        <v>20.82</v>
       </c>
       <c r="K18" t="n">
-        <v>10.9</v>
+        <v>41.51</v>
       </c>
       <c r="L18" t="n">
-        <v>1.66</v>
+        <v>-20.56</v>
       </c>
       <c r="M18" t="n">
-        <v>16.98</v>
+        <v>8.76</v>
       </c>
       <c r="N18" t="n">
-        <v>17</v>
+        <v>11.11</v>
       </c>
       <c r="O18" t="n">
-        <v>16.72</v>
+        <v>0.79</v>
       </c>
       <c r="P18" t="n">
-        <v>9.98</v>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
+        <v>16.28</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>16.52</v>
       </c>
       <c r="R18" t="n">
-        <v>2</v>
-      </c>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
+        <v>16.03</v>
+      </c>
+      <c r="S18" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1618,57 +1686,61 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>37.35</v>
+        <v>38.47</v>
       </c>
       <c r="D19" t="n">
-        <v>0.19</v>
+        <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>36.92</v>
+        <v>37.55</v>
       </c>
       <c r="F19" t="n">
-        <v>37.09</v>
+        <v>37.36</v>
       </c>
       <c r="G19" t="n">
-        <v>37.25</v>
+        <v>37.21</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.277</v>
+        <v>-0.168</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.287</v>
+        <v>-0.267</v>
       </c>
       <c r="J19" t="n">
-        <v>41.91</v>
+        <v>52.63</v>
       </c>
       <c r="K19" t="n">
-        <v>60.28</v>
+        <v>47.95</v>
       </c>
       <c r="L19" t="n">
-        <v>0.7</v>
+        <v>62.01</v>
       </c>
       <c r="M19" t="n">
-        <v>36.31</v>
+        <v>40.38</v>
       </c>
       <c r="N19" t="n">
-        <v>37.96</v>
+        <v>58.98</v>
       </c>
       <c r="O19" t="n">
-        <v>35.97</v>
+        <v>0.68</v>
       </c>
       <c r="P19" t="n">
-        <v>5.83</v>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
+        <v>36.35</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>38.63</v>
       </c>
       <c r="R19" t="n">
-        <v>2</v>
-      </c>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
+        <v>35.74</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1682,57 +1754,61 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>17.43</v>
+        <v>17.35</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4</v>
+        <v>-0.46</v>
       </c>
       <c r="E20" t="n">
-        <v>17.34</v>
+        <v>17.47</v>
       </c>
       <c r="F20" t="n">
         <v>17.56</v>
       </c>
       <c r="G20" t="n">
-        <v>18.18</v>
+        <v>18.07</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.148</v>
+        <v>-0.336</v>
       </c>
       <c r="I20" t="n">
-        <v>0.063</v>
+        <v>-0.213</v>
       </c>
       <c r="J20" t="n">
-        <v>164.11</v>
+        <v>35.8</v>
       </c>
       <c r="K20" t="n">
-        <v>298.27</v>
+        <v>32.49</v>
       </c>
       <c r="L20" t="n">
-        <v>0.55</v>
+        <v>42.44</v>
       </c>
       <c r="M20" t="n">
-        <v>17.31</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="N20" t="n">
-        <v>17.81</v>
+        <v>281.45</v>
       </c>
       <c r="O20" t="n">
-        <v>17.03</v>
+        <v>0.33</v>
       </c>
       <c r="P20" t="n">
-        <v>7.12</v>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
+        <v>17.06</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>17.39</v>
       </c>
       <c r="R20" t="n">
-        <v>2</v>
-      </c>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
+        <v>16.52</v>
+      </c>
+      <c r="S20" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1746,57 +1822,61 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>51.19</v>
+        <v>48.98</v>
       </c>
       <c r="D21" t="n">
-        <v>0.97</v>
+        <v>-4.32</v>
       </c>
       <c r="E21" t="n">
-        <v>50.21</v>
+        <v>50.02</v>
       </c>
       <c r="F21" t="n">
-        <v>50.89</v>
+        <v>50.73</v>
       </c>
       <c r="G21" t="n">
-        <v>52.3</v>
+        <v>51.84</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.427</v>
+        <v>-1.666</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.32</v>
+        <v>-1.558</v>
       </c>
       <c r="J21" t="n">
-        <v>48.43</v>
+        <v>32.06</v>
       </c>
       <c r="K21" t="n">
-        <v>69.22</v>
+        <v>32.87</v>
       </c>
       <c r="L21" t="n">
-        <v>0.7</v>
+        <v>30.43</v>
       </c>
       <c r="M21" t="n">
-        <v>49.85</v>
+        <v>39.99</v>
       </c>
       <c r="N21" t="n">
-        <v>52</v>
+        <v>66.06</v>
       </c>
       <c r="O21" t="n">
-        <v>49.5</v>
+        <v>0.61</v>
       </c>
       <c r="P21" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
+        <v>49</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>49.4</v>
       </c>
       <c r="R21" t="n">
-        <v>2</v>
-      </c>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
+        <v>47.5</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1810,57 +1890,61 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>46.74</v>
+        <v>45.96</v>
       </c>
       <c r="D22" t="n">
-        <v>0.37</v>
+        <v>-1.67</v>
       </c>
       <c r="E22" t="n">
-        <v>46.83</v>
+        <v>46.73</v>
       </c>
       <c r="F22" t="n">
-        <v>48.85</v>
+        <v>48.23</v>
       </c>
       <c r="G22" t="n">
-        <v>50.81</v>
+        <v>50.39</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.36</v>
+        <v>-2.59</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.963</v>
+        <v>-2.282</v>
       </c>
       <c r="J22" t="n">
-        <v>21.08</v>
+        <v>13.15</v>
       </c>
       <c r="K22" t="n">
-        <v>37.91</v>
+        <v>14.24</v>
       </c>
       <c r="L22" t="n">
-        <v>0.5600000000000001</v>
+        <v>10.97</v>
       </c>
       <c r="M22" t="n">
-        <v>45.88</v>
+        <v>14.94</v>
       </c>
       <c r="N22" t="n">
-        <v>46.86</v>
+        <v>35.77</v>
       </c>
       <c r="O22" t="n">
-        <v>45.77</v>
+        <v>0.42</v>
       </c>
       <c r="P22" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
+        <v>45.98</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>46.2</v>
       </c>
       <c r="R22" t="n">
-        <v>2</v>
-      </c>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
+        <v>45.36</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1874,57 +1958,61 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>14.26</v>
+        <v>14.11</v>
       </c>
       <c r="D23" t="n">
-        <v>1.42</v>
+        <v>-1.05</v>
       </c>
       <c r="E23" t="n">
-        <v>14.05</v>
+        <v>14.15</v>
       </c>
       <c r="F23" t="n">
-        <v>14.58</v>
+        <v>14.45</v>
       </c>
       <c r="G23" t="n">
-        <v>15.48</v>
+        <v>15.32</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.26</v>
+        <v>-1.368</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.263</v>
+        <v>-1.458</v>
       </c>
       <c r="J23" t="n">
-        <v>191.02</v>
+        <v>25.53</v>
       </c>
       <c r="K23" t="n">
-        <v>270.9</v>
+        <v>20.62</v>
       </c>
       <c r="L23" t="n">
-        <v>0.71</v>
+        <v>35.35</v>
       </c>
       <c r="M23" t="n">
-        <v>13.85</v>
+        <v>77.55</v>
       </c>
       <c r="N23" t="n">
-        <v>14.49</v>
+        <v>251.05</v>
       </c>
       <c r="O23" t="n">
-        <v>13.85</v>
+        <v>0.31</v>
       </c>
       <c r="P23" t="n">
-        <v>5.49</v>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
+        <v>14.04</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>14.21</v>
       </c>
       <c r="R23" t="n">
-        <v>2</v>
-      </c>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
+        <v>13.92</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1938,57 +2026,61 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>59.37</v>
+        <v>58.24</v>
       </c>
       <c r="D24" t="n">
-        <v>0.47</v>
+        <v>-1.9</v>
       </c>
       <c r="E24" t="n">
-        <v>60.14</v>
+        <v>59.71</v>
       </c>
       <c r="F24" t="n">
-        <v>62.78</v>
+        <v>61.9</v>
       </c>
       <c r="G24" t="n">
-        <v>65.42</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="H24" t="n">
-        <v>-3.28</v>
+        <v>-3.344</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.704</v>
+        <v>-2.743</v>
       </c>
       <c r="J24" t="n">
-        <v>7.67</v>
+        <v>10.7</v>
       </c>
       <c r="K24" t="n">
-        <v>13.79</v>
+        <v>11.34</v>
       </c>
       <c r="L24" t="n">
-        <v>0.5600000000000001</v>
+        <v>9.42</v>
       </c>
       <c r="M24" t="n">
-        <v>58.68</v>
+        <v>5.98</v>
       </c>
       <c r="N24" t="n">
-        <v>59.95</v>
+        <v>13.09</v>
       </c>
       <c r="O24" t="n">
-        <v>58.37</v>
+        <v>0.46</v>
       </c>
       <c r="P24" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
+        <v>58.31</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>58.5</v>
       </c>
       <c r="R24" t="n">
-        <v>2</v>
-      </c>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
+        <v>57.02</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2002,57 +2094,61 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>27.36</v>
+        <v>28.44</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.81</v>
+        <v>3.95</v>
       </c>
       <c r="E25" t="n">
-        <v>27.16</v>
+        <v>27.59</v>
       </c>
       <c r="F25" t="n">
-        <v>28.79</v>
+        <v>28.45</v>
       </c>
       <c r="G25" t="n">
-        <v>30.21</v>
+        <v>30.03</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.592</v>
+        <v>-0.607</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.036</v>
+        <v>-0.191</v>
       </c>
       <c r="J25" t="n">
-        <v>177.46</v>
+        <v>37.67</v>
       </c>
       <c r="K25" t="n">
-        <v>241.92</v>
+        <v>31.95</v>
       </c>
       <c r="L25" t="n">
-        <v>0.73</v>
+        <v>49.12</v>
       </c>
       <c r="M25" t="n">
-        <v>27.02</v>
+        <v>129.6</v>
       </c>
       <c r="N25" t="n">
-        <v>28.43</v>
+        <v>233.31</v>
       </c>
       <c r="O25" t="n">
-        <v>26.8</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="P25" t="n">
-        <v>11.17</v>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
+        <v>27.1</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>28.65</v>
       </c>
       <c r="R25" t="n">
-        <v>2</v>
-      </c>
-      <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
+        <v>27.1</v>
+      </c>
+      <c r="S25" t="n">
+        <v>8.16</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2066,57 +2162,61 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>27.45</v>
+        <v>27.95</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.42</v>
+        <v>1.82</v>
       </c>
       <c r="E26" t="n">
-        <v>27.78</v>
+        <v>27.88</v>
       </c>
       <c r="F26" t="n">
-        <v>28.84</v>
+        <v>28.54</v>
       </c>
       <c r="G26" t="n">
         <v>28.81</v>
       </c>
       <c r="H26" t="n">
-        <v>0.114</v>
+        <v>0.142</v>
       </c>
       <c r="I26" t="n">
-        <v>0.404</v>
+        <v>0.45</v>
       </c>
       <c r="J26" t="n">
-        <v>146.84</v>
+        <v>18.03</v>
       </c>
       <c r="K26" t="n">
-        <v>288.21</v>
+        <v>22.37</v>
       </c>
       <c r="L26" t="n">
-        <v>0.51</v>
+        <v>9.35</v>
       </c>
       <c r="M26" t="n">
-        <v>27.4</v>
+        <v>100.46</v>
       </c>
       <c r="N26" t="n">
-        <v>27.95</v>
+        <v>277.63</v>
       </c>
       <c r="O26" t="n">
-        <v>27.05</v>
+        <v>0.36</v>
       </c>
       <c r="P26" t="n">
-        <v>4.37</v>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
+        <v>27.46</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>28.36</v>
       </c>
       <c r="R26" t="n">
-        <v>2</v>
-      </c>
-      <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
+        <v>27.46</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2130,57 +2230,61 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>137.4</v>
+        <v>133.7</v>
       </c>
       <c r="D27" t="n">
-        <v>-2.9</v>
+        <v>-2.69</v>
       </c>
       <c r="E27" t="n">
-        <v>135.64</v>
+        <v>137.19</v>
       </c>
       <c r="F27" t="n">
-        <v>129.63</v>
+        <v>131.81</v>
       </c>
       <c r="G27" t="n">
-        <v>118.11</v>
+        <v>119.18</v>
       </c>
       <c r="H27" t="n">
-        <v>8.333</v>
+        <v>8.375999999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>5.663</v>
+        <v>6.489</v>
       </c>
       <c r="J27" t="n">
-        <v>9.279999999999999</v>
+        <v>78.12</v>
       </c>
       <c r="K27" t="n">
-        <v>7.53</v>
+        <v>79.42</v>
       </c>
       <c r="L27" t="n">
-        <v>1.23</v>
+        <v>75.51000000000001</v>
       </c>
       <c r="M27" t="n">
-        <v>136</v>
+        <v>4.71</v>
       </c>
       <c r="N27" t="n">
-        <v>143.85</v>
+        <v>7.54</v>
       </c>
       <c r="O27" t="n">
-        <v>135.08</v>
+        <v>0.63</v>
       </c>
       <c r="P27" t="n">
-        <v>10.51</v>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
+        <v>133.58</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>141.41</v>
       </c>
       <c r="R27" t="n">
-        <v>2</v>
-      </c>
-      <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr"/>
+        <v>131.83</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -530,55 +530,55 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>102.72</v>
+        <v>103.46</v>
       </c>
       <c r="D2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.79</v>
       </c>
       <c r="E2" t="n">
-        <v>102.09</v>
+        <v>102.24</v>
       </c>
       <c r="F2" t="n">
-        <v>102.41</v>
+        <v>102.48</v>
       </c>
       <c r="G2" t="n">
-        <v>102.35</v>
+        <v>102.39</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.948</v>
+        <v>-0.889</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.162</v>
+        <v>-1.151</v>
       </c>
       <c r="J2" t="n">
-        <v>40.45</v>
+        <v>45.44</v>
       </c>
       <c r="K2" t="n">
-        <v>35.1</v>
+        <v>36.76</v>
       </c>
       <c r="L2" t="n">
-        <v>51.16</v>
+        <v>62.78</v>
       </c>
       <c r="M2" t="n">
-        <v>4.74</v>
+        <v>12.49</v>
       </c>
       <c r="N2" t="n">
-        <v>13.43</v>
+        <v>13.82</v>
       </c>
       <c r="O2" t="n">
-        <v>0.35</v>
+        <v>0.9</v>
       </c>
       <c r="P2" t="n">
         <v>101.99</v>
       </c>
       <c r="Q2" t="n">
-        <v>102.85</v>
+        <v>103.9</v>
       </c>
       <c r="R2" t="n">
         <v>101.8</v>
       </c>
       <c r="S2" t="n">
-        <v>0.12</v>
+        <v>0.32</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -598,43 +598,43 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>409.96</v>
+        <v>413</v>
       </c>
       <c r="D3" t="n">
-        <v>-1.49</v>
+        <v>-0.76</v>
       </c>
       <c r="E3" t="n">
-        <v>404.69</v>
+        <v>405.3</v>
       </c>
       <c r="F3" t="n">
-        <v>404.6</v>
+        <v>404.9</v>
       </c>
       <c r="G3" t="n">
-        <v>388.27</v>
+        <v>388.42</v>
       </c>
       <c r="H3" t="n">
-        <v>13.447</v>
+        <v>13.69</v>
       </c>
       <c r="I3" t="n">
-        <v>12.726</v>
+        <v>12.774</v>
       </c>
       <c r="J3" t="n">
-        <v>60.33</v>
+        <v>63.28</v>
       </c>
       <c r="K3" t="n">
-        <v>58.3</v>
+        <v>59.29</v>
       </c>
       <c r="L3" t="n">
-        <v>64.37</v>
+        <v>71.27</v>
       </c>
       <c r="M3" t="n">
-        <v>15.03</v>
+        <v>25.35</v>
       </c>
       <c r="N3" t="n">
-        <v>34.23</v>
+        <v>34.75</v>
       </c>
       <c r="O3" t="n">
-        <v>0.44</v>
+        <v>0.73</v>
       </c>
       <c r="P3" t="n">
         <v>413</v>
@@ -646,7 +646,7 @@
         <v>405.6</v>
       </c>
       <c r="S3" t="n">
-        <v>0.35</v>
+        <v>0.6</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -666,43 +666,43 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>24.03</v>
+        <v>24.1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.95</v>
+        <v>-0.66</v>
       </c>
       <c r="E4" t="n">
-        <v>24.29</v>
+        <v>24.3</v>
       </c>
       <c r="F4" t="n">
-        <v>24.85</v>
+        <v>24.86</v>
       </c>
       <c r="G4" t="n">
         <v>25.47</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.826</v>
+        <v>-0.82</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.717</v>
+        <v>-0.716</v>
       </c>
       <c r="J4" t="n">
-        <v>10.1</v>
+        <v>11.19</v>
       </c>
       <c r="K4" t="n">
-        <v>13.15</v>
+        <v>13.51</v>
       </c>
       <c r="L4" t="n">
-        <v>4.01</v>
+        <v>6.56</v>
       </c>
       <c r="M4" t="n">
-        <v>46.83</v>
+        <v>90.95</v>
       </c>
       <c r="N4" t="n">
-        <v>113.8</v>
+        <v>116.01</v>
       </c>
       <c r="O4" t="n">
-        <v>0.41</v>
+        <v>0.78</v>
       </c>
       <c r="P4" t="n">
         <v>23.99</v>
@@ -714,7 +714,7 @@
         <v>23.88</v>
       </c>
       <c r="S4" t="n">
-        <v>0.38</v>
+        <v>0.75</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -734,55 +734,55 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>80.05</v>
+        <v>81.13</v>
       </c>
       <c r="D5" t="n">
-        <v>2.96</v>
+        <v>4.35</v>
       </c>
       <c r="E5" t="n">
-        <v>78.90000000000001</v>
+        <v>79.11</v>
       </c>
       <c r="F5" t="n">
-        <v>80.53</v>
+        <v>80.64</v>
       </c>
       <c r="G5" t="n">
-        <v>85.98</v>
+        <v>86.04000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>-3.525</v>
+        <v>-3.439</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.823</v>
+        <v>-2.805</v>
       </c>
       <c r="J5" t="n">
-        <v>25.62</v>
+        <v>29.21</v>
       </c>
       <c r="K5" t="n">
-        <v>19.32</v>
+        <v>20.52</v>
       </c>
       <c r="L5" t="n">
-        <v>38.22</v>
+        <v>46.59</v>
       </c>
       <c r="M5" t="n">
-        <v>23.36</v>
+        <v>46.83</v>
       </c>
       <c r="N5" t="n">
-        <v>38.72</v>
+        <v>39.89</v>
       </c>
       <c r="O5" t="n">
-        <v>0.6</v>
+        <v>1.17</v>
       </c>
       <c r="P5" t="n">
         <v>76.59999999999999</v>
       </c>
       <c r="Q5" t="n">
-        <v>80.97</v>
+        <v>81.55</v>
       </c>
       <c r="R5" t="n">
         <v>76.59999999999999</v>
       </c>
       <c r="S5" t="n">
-        <v>1.98</v>
+        <v>3.96</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -802,55 +802,55 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>580.9</v>
+        <v>589.08</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.86</v>
+        <v>-1.49</v>
       </c>
       <c r="E6" t="n">
-        <v>604.9400000000001</v>
+        <v>606.5700000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>593.45</v>
+        <v>594.27</v>
       </c>
       <c r="G6" t="n">
-        <v>570.3</v>
+        <v>570.71</v>
       </c>
       <c r="H6" t="n">
-        <v>9.401</v>
+        <v>10.054</v>
       </c>
       <c r="I6" t="n">
-        <v>4.619</v>
+        <v>4.749</v>
       </c>
       <c r="J6" t="n">
-        <v>57.28</v>
+        <v>60.15</v>
       </c>
       <c r="K6" t="n">
-        <v>67.23999999999999</v>
+        <v>68.19</v>
       </c>
       <c r="L6" t="n">
-        <v>37.35</v>
+        <v>44.05</v>
       </c>
       <c r="M6" t="n">
-        <v>11.73</v>
+        <v>20.93</v>
       </c>
       <c r="N6" t="n">
-        <v>30.05</v>
+        <v>30.51</v>
       </c>
       <c r="O6" t="n">
-        <v>0.39</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="P6" t="n">
         <v>585</v>
       </c>
       <c r="Q6" t="n">
-        <v>593</v>
+        <v>595.58</v>
       </c>
       <c r="R6" t="n">
         <v>579</v>
       </c>
       <c r="S6" t="n">
-        <v>1.06</v>
+        <v>1.89</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -870,55 +870,55 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7.48</v>
+        <v>7.57</v>
       </c>
       <c r="D7" t="n">
-        <v>1.08</v>
+        <v>2.3</v>
       </c>
       <c r="E7" t="n">
-        <v>7.39</v>
+        <v>7.41</v>
       </c>
       <c r="F7" t="n">
-        <v>7.4</v>
+        <v>7.41</v>
       </c>
       <c r="G7" t="n">
         <v>7.27</v>
       </c>
       <c r="H7" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.076</v>
       </c>
       <c r="I7" t="n">
-        <v>0.048</v>
+        <v>0.049</v>
       </c>
       <c r="J7" t="n">
-        <v>59.19</v>
+        <v>66.33</v>
       </c>
       <c r="K7" t="n">
-        <v>60.41</v>
+        <v>62.79</v>
       </c>
       <c r="L7" t="n">
-        <v>56.75</v>
+        <v>73.42</v>
       </c>
       <c r="M7" t="n">
-        <v>158.72</v>
+        <v>371.59</v>
       </c>
       <c r="N7" t="n">
-        <v>337.48</v>
+        <v>348.12</v>
       </c>
       <c r="O7" t="n">
-        <v>0.47</v>
+        <v>1.07</v>
       </c>
       <c r="P7" t="n">
         <v>7.37</v>
       </c>
       <c r="Q7" t="n">
-        <v>7.5</v>
+        <v>7.58</v>
       </c>
       <c r="R7" t="n">
         <v>7.36</v>
       </c>
       <c r="S7" t="n">
-        <v>0.06</v>
+        <v>0.14</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -938,10 +938,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>15.35</v>
+        <v>15.37</v>
       </c>
       <c r="D8" t="n">
-        <v>1.19</v>
+        <v>1.32</v>
       </c>
       <c r="E8" t="n">
         <v>15.29</v>
@@ -953,28 +953,28 @@
         <v>15.74</v>
       </c>
       <c r="H8" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I8" t="n">
         <v>0.189</v>
       </c>
       <c r="J8" t="n">
-        <v>18.11</v>
+        <v>18.6</v>
       </c>
       <c r="K8" t="n">
-        <v>24.39</v>
+        <v>24.55</v>
       </c>
       <c r="L8" t="n">
-        <v>5.56</v>
+        <v>6.7</v>
       </c>
       <c r="M8" t="n">
-        <v>64.59</v>
+        <v>97.48999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>161.83</v>
+        <v>163.48</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="P8" t="n">
         <v>15.17</v>
@@ -986,7 +986,7 @@
         <v>15.1</v>
       </c>
       <c r="S8" t="n">
-        <v>0.51</v>
+        <v>0.78</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1006,55 +1006,55 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>34.22</v>
+        <v>35.03</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.47</v>
+        <v>0.86</v>
       </c>
       <c r="E9" t="n">
-        <v>34.66</v>
+        <v>34.82</v>
       </c>
       <c r="F9" t="n">
-        <v>35.74</v>
+        <v>35.82</v>
       </c>
       <c r="G9" t="n">
-        <v>37.32</v>
+        <v>37.36</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.08599999999999999</v>
+        <v>-0.021</v>
       </c>
       <c r="I9" t="n">
-        <v>0.555</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>19.24</v>
+        <v>22.99</v>
       </c>
       <c r="K9" t="n">
-        <v>20.35</v>
+        <v>21.6</v>
       </c>
       <c r="L9" t="n">
-        <v>17.03</v>
+        <v>25.77</v>
       </c>
       <c r="M9" t="n">
-        <v>40.39</v>
+        <v>100.42</v>
       </c>
       <c r="N9" t="n">
-        <v>177.62</v>
+        <v>180.63</v>
       </c>
       <c r="O9" t="n">
-        <v>0.23</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="P9" t="n">
         <v>33.78</v>
       </c>
       <c r="Q9" t="n">
-        <v>34.62</v>
+        <v>35.5</v>
       </c>
       <c r="R9" t="n">
         <v>33.57</v>
       </c>
       <c r="S9" t="n">
-        <v>3.53</v>
+        <v>8.77</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1074,43 +1074,43 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>215.58</v>
+        <v>215.73</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.43</v>
+        <v>-2.36</v>
       </c>
       <c r="E10" t="n">
-        <v>217.18</v>
+        <v>217.21</v>
       </c>
       <c r="F10" t="n">
-        <v>219.05</v>
+        <v>219.06</v>
       </c>
       <c r="G10" t="n">
         <v>229.71</v>
       </c>
       <c r="H10" t="n">
-        <v>-9.303000000000001</v>
+        <v>-9.291</v>
       </c>
       <c r="I10" t="n">
-        <v>-8.539999999999999</v>
+        <v>-8.538</v>
       </c>
       <c r="J10" t="n">
-        <v>39.46</v>
+        <v>39.63</v>
       </c>
       <c r="K10" t="n">
-        <v>31.12</v>
+        <v>31.18</v>
       </c>
       <c r="L10" t="n">
-        <v>56.15</v>
+        <v>56.54</v>
       </c>
       <c r="M10" t="n">
-        <v>7.86</v>
+        <v>14.61</v>
       </c>
       <c r="N10" t="n">
-        <v>19.13</v>
+        <v>19.47</v>
       </c>
       <c r="O10" t="n">
-        <v>0.41</v>
+        <v>0.75</v>
       </c>
       <c r="P10" t="n">
         <v>218.6</v>
@@ -1122,7 +1122,7 @@
         <v>213.07</v>
       </c>
       <c r="S10" t="n">
-        <v>0.34</v>
+        <v>0.63</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1142,55 +1142,55 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>449.85</v>
+        <v>458.38</v>
       </c>
       <c r="D11" t="n">
-        <v>0.55</v>
+        <v>2.45</v>
       </c>
       <c r="E11" t="n">
-        <v>459.69</v>
+        <v>461.4</v>
       </c>
       <c r="F11" t="n">
-        <v>449.66</v>
+        <v>450.51</v>
       </c>
       <c r="G11" t="n">
-        <v>420.6</v>
+        <v>421.03</v>
       </c>
       <c r="H11" t="n">
-        <v>19.09</v>
+        <v>19.77</v>
       </c>
       <c r="I11" t="n">
-        <v>15.416</v>
+        <v>15.552</v>
       </c>
       <c r="J11" t="n">
-        <v>65.38</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>71.67</v>
+        <v>72.68000000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>52.79</v>
+        <v>59.85</v>
       </c>
       <c r="M11" t="n">
-        <v>12.19</v>
+        <v>25.53</v>
       </c>
       <c r="N11" t="n">
-        <v>43.9</v>
+        <v>44.57</v>
       </c>
       <c r="O11" t="n">
-        <v>0.28</v>
+        <v>0.57</v>
       </c>
       <c r="P11" t="n">
         <v>445.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>460.58</v>
+        <v>464</v>
       </c>
       <c r="R11" t="n">
         <v>445.2</v>
       </c>
       <c r="S11" t="n">
-        <v>1.38</v>
+        <v>2.88</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1210,55 +1210,55 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>310.36</v>
+        <v>316.81</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.28</v>
+        <v>-0.25</v>
       </c>
       <c r="E12" t="n">
-        <v>313.95</v>
+        <v>315.24</v>
       </c>
       <c r="F12" t="n">
-        <v>307.16</v>
+        <v>307.8</v>
       </c>
       <c r="G12" t="n">
-        <v>317.4</v>
+        <v>317.72</v>
       </c>
       <c r="H12" t="n">
-        <v>4.353</v>
+        <v>4.867</v>
       </c>
       <c r="I12" t="n">
-        <v>7.026</v>
+        <v>7.129</v>
       </c>
       <c r="J12" t="n">
-        <v>53.84</v>
+        <v>58.28</v>
       </c>
       <c r="K12" t="n">
-        <v>52.05</v>
+        <v>53.52</v>
       </c>
       <c r="L12" t="n">
-        <v>57.44</v>
+        <v>67.78</v>
       </c>
       <c r="M12" t="n">
-        <v>12.62</v>
+        <v>23.11</v>
       </c>
       <c r="N12" t="n">
-        <v>34.25</v>
+        <v>34.78</v>
       </c>
       <c r="O12" t="n">
-        <v>0.37</v>
+        <v>0.66</v>
       </c>
       <c r="P12" t="n">
         <v>314.16</v>
       </c>
       <c r="Q12" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="R12" t="n">
         <v>308</v>
       </c>
       <c r="S12" t="n">
-        <v>1.63</v>
+        <v>2.98</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1278,43 +1278,43 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>106.51</v>
+        <v>106.95</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.73</v>
+        <v>-2.33</v>
       </c>
       <c r="E13" t="n">
-        <v>109.82</v>
+        <v>109.91</v>
       </c>
       <c r="F13" t="n">
-        <v>112.44</v>
+        <v>112.48</v>
       </c>
       <c r="G13" t="n">
-        <v>114.2</v>
+        <v>114.22</v>
       </c>
       <c r="H13" t="n">
-        <v>4.912</v>
+        <v>4.947</v>
       </c>
       <c r="I13" t="n">
-        <v>7.516</v>
+        <v>7.523</v>
       </c>
       <c r="J13" t="n">
-        <v>20.86</v>
+        <v>21.51</v>
       </c>
       <c r="K13" t="n">
-        <v>25.36</v>
+        <v>25.58</v>
       </c>
       <c r="L13" t="n">
-        <v>11.86</v>
+        <v>13.37</v>
       </c>
       <c r="M13" t="n">
-        <v>37.65</v>
+        <v>59.36</v>
       </c>
       <c r="N13" t="n">
-        <v>123.69</v>
+        <v>124.78</v>
       </c>
       <c r="O13" t="n">
-        <v>0.3</v>
+        <v>0.48</v>
       </c>
       <c r="P13" t="n">
         <v>109</v>
@@ -1326,7 +1326,7 @@
         <v>105.57</v>
       </c>
       <c r="S13" t="n">
-        <v>3.75</v>
+        <v>5.91</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1346,55 +1346,55 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>254.03</v>
+        <v>255.85</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.79</v>
+        <v>-1.09</v>
       </c>
       <c r="E14" t="n">
-        <v>265.36</v>
+        <v>265.72</v>
       </c>
       <c r="F14" t="n">
-        <v>280.13</v>
+        <v>280.31</v>
       </c>
       <c r="G14" t="n">
-        <v>281.17</v>
+        <v>281.26</v>
       </c>
       <c r="H14" t="n">
-        <v>-8.273</v>
+        <v>-8.128</v>
       </c>
       <c r="I14" t="n">
-        <v>-4.774</v>
+        <v>-4.745</v>
       </c>
       <c r="J14" t="n">
-        <v>24.8</v>
+        <v>25.63</v>
       </c>
       <c r="K14" t="n">
-        <v>32.77</v>
+        <v>33.05</v>
       </c>
       <c r="L14" t="n">
-        <v>8.85</v>
+        <v>10.78</v>
       </c>
       <c r="M14" t="n">
-        <v>10.96</v>
+        <v>21.47</v>
       </c>
       <c r="N14" t="n">
-        <v>29.03</v>
+        <v>29.56</v>
       </c>
       <c r="O14" t="n">
-        <v>0.38</v>
+        <v>0.73</v>
       </c>
       <c r="P14" t="n">
         <v>252</v>
       </c>
       <c r="Q14" t="n">
-        <v>255.88</v>
+        <v>259.54</v>
       </c>
       <c r="R14" t="n">
         <v>250.03</v>
       </c>
       <c r="S14" t="n">
-        <v>1.64</v>
+        <v>3.21</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1414,43 +1414,43 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>230.33</v>
+        <v>231.99</v>
       </c>
       <c r="D15" t="n">
-        <v>-3.39</v>
+        <v>-2.69</v>
       </c>
       <c r="E15" t="n">
-        <v>238.51</v>
+        <v>238.84</v>
       </c>
       <c r="F15" t="n">
-        <v>239.35</v>
+        <v>239.51</v>
       </c>
       <c r="G15" t="n">
-        <v>220.58</v>
+        <v>220.67</v>
       </c>
       <c r="H15" t="n">
-        <v>14.88</v>
+        <v>15.012</v>
       </c>
       <c r="I15" t="n">
-        <v>15.017</v>
+        <v>15.043</v>
       </c>
       <c r="J15" t="n">
-        <v>52.29</v>
+        <v>53.43</v>
       </c>
       <c r="K15" t="n">
-        <v>61.59</v>
+        <v>61.97</v>
       </c>
       <c r="L15" t="n">
-        <v>33.69</v>
+        <v>36.34</v>
       </c>
       <c r="M15" t="n">
-        <v>18.64</v>
+        <v>30.95</v>
       </c>
       <c r="N15" t="n">
-        <v>42.98</v>
+        <v>43.6</v>
       </c>
       <c r="O15" t="n">
-        <v>0.43</v>
+        <v>0.71</v>
       </c>
       <c r="P15" t="n">
         <v>231.21</v>
@@ -1462,7 +1462,7 @@
         <v>228.88</v>
       </c>
       <c r="S15" t="n">
-        <v>3.99</v>
+        <v>6.62</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1482,43 +1482,43 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>44.69</v>
+        <v>44.26</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5600000000000001</v>
+        <v>-0.41</v>
       </c>
       <c r="E16" t="n">
-        <v>46.01</v>
+        <v>45.92</v>
       </c>
       <c r="F16" t="n">
-        <v>49.85</v>
+        <v>49.8</v>
       </c>
       <c r="G16" t="n">
-        <v>43.87</v>
+        <v>43.85</v>
       </c>
       <c r="H16" t="n">
-        <v>2.838</v>
+        <v>2.804</v>
       </c>
       <c r="I16" t="n">
-        <v>3.364</v>
+        <v>3.357</v>
       </c>
       <c r="J16" t="n">
-        <v>25.39</v>
+        <v>24.59</v>
       </c>
       <c r="K16" t="n">
-        <v>42.23</v>
+        <v>41.96</v>
       </c>
       <c r="L16" t="n">
-        <v>-8.279999999999999</v>
+        <v>-10.14</v>
       </c>
       <c r="M16" t="n">
-        <v>11.19</v>
+        <v>19.21</v>
       </c>
       <c r="N16" t="n">
-        <v>31.35</v>
+        <v>31.76</v>
       </c>
       <c r="O16" t="n">
-        <v>0.36</v>
+        <v>0.6</v>
       </c>
       <c r="P16" t="n">
         <v>44.05</v>
@@ -1530,7 +1530,7 @@
         <v>43.65</v>
       </c>
       <c r="S16" t="n">
-        <v>5.58</v>
+        <v>9.59</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -1550,43 +1550,43 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>20.61</v>
+        <v>20.85</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.46</v>
+        <v>-1.33</v>
       </c>
       <c r="E17" t="n">
-        <v>21.59</v>
+        <v>21.64</v>
       </c>
       <c r="F17" t="n">
-        <v>22.71</v>
+        <v>22.73</v>
       </c>
       <c r="G17" t="n">
-        <v>20.99</v>
+        <v>21</v>
       </c>
       <c r="H17" t="n">
-        <v>0.512</v>
+        <v>0.531</v>
       </c>
       <c r="I17" t="n">
-        <v>0.618</v>
+        <v>0.622</v>
       </c>
       <c r="J17" t="n">
-        <v>20.23</v>
+        <v>21.22</v>
       </c>
       <c r="K17" t="n">
-        <v>36.73</v>
+        <v>37.06</v>
       </c>
       <c r="L17" t="n">
-        <v>-12.77</v>
+        <v>-10.44</v>
       </c>
       <c r="M17" t="n">
-        <v>11.06</v>
+        <v>20.34</v>
       </c>
       <c r="N17" t="n">
-        <v>40.02</v>
+        <v>40.49</v>
       </c>
       <c r="O17" t="n">
-        <v>0.28</v>
+        <v>0.5</v>
       </c>
       <c r="P17" t="n">
         <v>20.67</v>
@@ -1598,7 +1598,7 @@
         <v>20.36</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>5.51</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -1618,43 +1618,43 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>16.12</v>
+        <v>16.2</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.99</v>
+        <v>-3.51</v>
       </c>
       <c r="E18" t="n">
-        <v>17.37</v>
+        <v>17.39</v>
       </c>
       <c r="F18" t="n">
-        <v>18.92</v>
+        <v>18.93</v>
       </c>
       <c r="G18" t="n">
         <v>16.73</v>
       </c>
       <c r="H18" t="n">
-        <v>0.757</v>
+        <v>0.763</v>
       </c>
       <c r="I18" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.945</v>
       </c>
       <c r="J18" t="n">
-        <v>20.82</v>
+        <v>21.1</v>
       </c>
       <c r="K18" t="n">
-        <v>41.51</v>
+        <v>41.6</v>
       </c>
       <c r="L18" t="n">
-        <v>-20.56</v>
+        <v>-19.91</v>
       </c>
       <c r="M18" t="n">
-        <v>8.76</v>
+        <v>15.21</v>
       </c>
       <c r="N18" t="n">
-        <v>11.11</v>
+        <v>11.44</v>
       </c>
       <c r="O18" t="n">
-        <v>0.79</v>
+        <v>1.33</v>
       </c>
       <c r="P18" t="n">
         <v>16.28</v>
@@ -1666,7 +1666,7 @@
         <v>16.03</v>
       </c>
       <c r="S18" t="n">
-        <v>4.83</v>
+        <v>8.4</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -1686,55 +1686,55 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>38.47</v>
+        <v>38.3</v>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>2.54</v>
       </c>
       <c r="E19" t="n">
-        <v>37.55</v>
+        <v>37.52</v>
       </c>
       <c r="F19" t="n">
-        <v>37.36</v>
+        <v>37.35</v>
       </c>
       <c r="G19" t="n">
-        <v>37.21</v>
+        <v>37.2</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.168</v>
+        <v>-0.181</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.267</v>
+        <v>-0.27</v>
       </c>
       <c r="J19" t="n">
-        <v>52.63</v>
+        <v>51.67</v>
       </c>
       <c r="K19" t="n">
-        <v>47.95</v>
+        <v>47.63</v>
       </c>
       <c r="L19" t="n">
-        <v>62.01</v>
+        <v>59.77</v>
       </c>
       <c r="M19" t="n">
-        <v>40.38</v>
+        <v>61.67</v>
       </c>
       <c r="N19" t="n">
-        <v>58.98</v>
+        <v>60.05</v>
       </c>
       <c r="O19" t="n">
-        <v>0.68</v>
+        <v>1.03</v>
       </c>
       <c r="P19" t="n">
         <v>36.35</v>
       </c>
       <c r="Q19" t="n">
-        <v>38.63</v>
+        <v>38.84</v>
       </c>
       <c r="R19" t="n">
         <v>35.74</v>
       </c>
       <c r="S19" t="n">
-        <v>5.62</v>
+        <v>8.58</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -1754,55 +1754,55 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>17.35</v>
+        <v>17.5</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.46</v>
+        <v>0.4</v>
       </c>
       <c r="E20" t="n">
-        <v>17.47</v>
+        <v>17.5</v>
       </c>
       <c r="F20" t="n">
-        <v>17.56</v>
+        <v>17.57</v>
       </c>
       <c r="G20" t="n">
-        <v>18.07</v>
+        <v>18.08</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.336</v>
+        <v>-0.324</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.213</v>
+        <v>-0.21</v>
       </c>
       <c r="J20" t="n">
-        <v>35.8</v>
+        <v>37.57</v>
       </c>
       <c r="K20" t="n">
-        <v>32.49</v>
+        <v>33.07</v>
       </c>
       <c r="L20" t="n">
-        <v>42.44</v>
+        <v>46.56</v>
       </c>
       <c r="M20" t="n">
-        <v>92.90000000000001</v>
+        <v>149.36</v>
       </c>
       <c r="N20" t="n">
-        <v>281.45</v>
+        <v>284.27</v>
       </c>
       <c r="O20" t="n">
-        <v>0.33</v>
+        <v>0.53</v>
       </c>
       <c r="P20" t="n">
         <v>17.06</v>
       </c>
       <c r="Q20" t="n">
-        <v>17.39</v>
+        <v>17.64</v>
       </c>
       <c r="R20" t="n">
         <v>16.52</v>
       </c>
       <c r="S20" t="n">
-        <v>4.03</v>
+        <v>6.48</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -1822,55 +1822,55 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>48.98</v>
+        <v>49.9</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.32</v>
+        <v>-2.52</v>
       </c>
       <c r="E21" t="n">
-        <v>50.02</v>
+        <v>50.2</v>
       </c>
       <c r="F21" t="n">
-        <v>50.73</v>
+        <v>50.82</v>
       </c>
       <c r="G21" t="n">
-        <v>51.84</v>
+        <v>51.89</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.666</v>
+        <v>-1.592</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.558</v>
+        <v>-1.544</v>
       </c>
       <c r="J21" t="n">
-        <v>32.06</v>
+        <v>35.2</v>
       </c>
       <c r="K21" t="n">
-        <v>32.87</v>
+        <v>33.92</v>
       </c>
       <c r="L21" t="n">
-        <v>30.43</v>
+        <v>37.76</v>
       </c>
       <c r="M21" t="n">
-        <v>39.99</v>
+        <v>60.78</v>
       </c>
       <c r="N21" t="n">
-        <v>66.06</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="O21" t="n">
-        <v>0.61</v>
+        <v>0.91</v>
       </c>
       <c r="P21" t="n">
         <v>49</v>
       </c>
       <c r="Q21" t="n">
-        <v>49.4</v>
+        <v>50.13</v>
       </c>
       <c r="R21" t="n">
         <v>47.5</v>
       </c>
       <c r="S21" t="n">
-        <v>3.19</v>
+        <v>4.84</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -1890,55 +1890,55 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>45.96</v>
+        <v>46.4</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.67</v>
+        <v>-0.73</v>
       </c>
       <c r="E22" t="n">
-        <v>46.73</v>
+        <v>46.82</v>
       </c>
       <c r="F22" t="n">
-        <v>48.23</v>
+        <v>48.27</v>
       </c>
       <c r="G22" t="n">
-        <v>50.39</v>
+        <v>50.41</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.59</v>
+        <v>-2.555</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.282</v>
+        <v>-2.275</v>
       </c>
       <c r="J22" t="n">
-        <v>13.15</v>
+        <v>15.48</v>
       </c>
       <c r="K22" t="n">
-        <v>14.24</v>
+        <v>15.02</v>
       </c>
       <c r="L22" t="n">
-        <v>10.97</v>
+        <v>16.42</v>
       </c>
       <c r="M22" t="n">
-        <v>14.94</v>
+        <v>25.7</v>
       </c>
       <c r="N22" t="n">
-        <v>35.77</v>
+        <v>36.31</v>
       </c>
       <c r="O22" t="n">
-        <v>0.42</v>
+        <v>0.71</v>
       </c>
       <c r="P22" t="n">
         <v>45.98</v>
       </c>
       <c r="Q22" t="n">
-        <v>46.2</v>
+        <v>46.42</v>
       </c>
       <c r="R22" t="n">
         <v>45.36</v>
       </c>
       <c r="S22" t="n">
-        <v>0.68</v>
+        <v>1.17</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -1958,55 +1958,55 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>14.11</v>
+        <v>14.4</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.05</v>
+        <v>0.98</v>
       </c>
       <c r="E23" t="n">
-        <v>14.15</v>
+        <v>14.21</v>
       </c>
       <c r="F23" t="n">
-        <v>14.45</v>
+        <v>14.48</v>
       </c>
       <c r="G23" t="n">
-        <v>15.32</v>
+        <v>15.33</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.368</v>
+        <v>-1.345</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.458</v>
+        <v>-1.453</v>
       </c>
       <c r="J23" t="n">
-        <v>25.53</v>
+        <v>30.2</v>
       </c>
       <c r="K23" t="n">
-        <v>20.62</v>
+        <v>22.17</v>
       </c>
       <c r="L23" t="n">
-        <v>35.35</v>
+        <v>46.25</v>
       </c>
       <c r="M23" t="n">
-        <v>77.55</v>
+        <v>152.86</v>
       </c>
       <c r="N23" t="n">
-        <v>251.05</v>
+        <v>254.81</v>
       </c>
       <c r="O23" t="n">
-        <v>0.31</v>
+        <v>0.6</v>
       </c>
       <c r="P23" t="n">
         <v>14.04</v>
       </c>
       <c r="Q23" t="n">
-        <v>14.21</v>
+        <v>14.4</v>
       </c>
       <c r="R23" t="n">
         <v>13.92</v>
       </c>
       <c r="S23" t="n">
-        <v>2.23</v>
+        <v>4.39</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2026,55 +2026,55 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>58.24</v>
+        <v>58.85</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.9</v>
+        <v>-0.88</v>
       </c>
       <c r="E24" t="n">
-        <v>59.71</v>
+        <v>59.83</v>
       </c>
       <c r="F24" t="n">
-        <v>61.9</v>
+        <v>61.96</v>
       </c>
       <c r="G24" t="n">
-        <v>64.84999999999999</v>
+        <v>64.88</v>
       </c>
       <c r="H24" t="n">
-        <v>-3.344</v>
+        <v>-3.295</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.743</v>
+        <v>-2.734</v>
       </c>
       <c r="J24" t="n">
-        <v>10.7</v>
+        <v>12.78</v>
       </c>
       <c r="K24" t="n">
-        <v>11.34</v>
+        <v>12.04</v>
       </c>
       <c r="L24" t="n">
-        <v>9.42</v>
+        <v>14.28</v>
       </c>
       <c r="M24" t="n">
-        <v>5.98</v>
+        <v>9.81</v>
       </c>
       <c r="N24" t="n">
-        <v>13.09</v>
+        <v>13.28</v>
       </c>
       <c r="O24" t="n">
-        <v>0.46</v>
+        <v>0.74</v>
       </c>
       <c r="P24" t="n">
         <v>58.31</v>
       </c>
       <c r="Q24" t="n">
-        <v>58.5</v>
+        <v>58.88</v>
       </c>
       <c r="R24" t="n">
         <v>57.02</v>
       </c>
       <c r="S24" t="n">
-        <v>1.62</v>
+        <v>2.66</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2094,55 +2094,55 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>28.44</v>
+        <v>28.68</v>
       </c>
       <c r="D25" t="n">
-        <v>3.95</v>
+        <v>4.82</v>
       </c>
       <c r="E25" t="n">
-        <v>27.59</v>
+        <v>27.64</v>
       </c>
       <c r="F25" t="n">
-        <v>28.45</v>
+        <v>28.47</v>
       </c>
       <c r="G25" t="n">
-        <v>30.03</v>
+        <v>30.04</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.607</v>
+        <v>-0.588</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.191</v>
+        <v>-0.187</v>
       </c>
       <c r="J25" t="n">
-        <v>37.67</v>
+        <v>38.79</v>
       </c>
       <c r="K25" t="n">
-        <v>31.95</v>
+        <v>32.32</v>
       </c>
       <c r="L25" t="n">
-        <v>49.12</v>
+        <v>51.73</v>
       </c>
       <c r="M25" t="n">
-        <v>129.6</v>
+        <v>235.79</v>
       </c>
       <c r="N25" t="n">
-        <v>233.31</v>
+        <v>238.62</v>
       </c>
       <c r="O25" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.99</v>
       </c>
       <c r="P25" t="n">
         <v>27.1</v>
       </c>
       <c r="Q25" t="n">
-        <v>28.65</v>
+        <v>29.3</v>
       </c>
       <c r="R25" t="n">
         <v>27.1</v>
       </c>
       <c r="S25" t="n">
-        <v>8.16</v>
+        <v>14.84</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -2162,43 +2162,43 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>27.95</v>
+        <v>27.72</v>
       </c>
       <c r="D26" t="n">
-        <v>1.82</v>
+        <v>0.98</v>
       </c>
       <c r="E26" t="n">
-        <v>27.88</v>
+        <v>27.84</v>
       </c>
       <c r="F26" t="n">
-        <v>28.54</v>
+        <v>28.52</v>
       </c>
       <c r="G26" t="n">
-        <v>28.81</v>
+        <v>28.79</v>
       </c>
       <c r="H26" t="n">
-        <v>0.142</v>
+        <v>0.124</v>
       </c>
       <c r="I26" t="n">
-        <v>0.45</v>
+        <v>0.446</v>
       </c>
       <c r="J26" t="n">
-        <v>18.03</v>
+        <v>16.28</v>
       </c>
       <c r="K26" t="n">
-        <v>22.37</v>
+        <v>21.79</v>
       </c>
       <c r="L26" t="n">
-        <v>9.35</v>
+        <v>5.26</v>
       </c>
       <c r="M26" t="n">
-        <v>100.46</v>
+        <v>193.99</v>
       </c>
       <c r="N26" t="n">
-        <v>277.63</v>
+        <v>282.31</v>
       </c>
       <c r="O26" t="n">
-        <v>0.36</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="P26" t="n">
         <v>27.46</v>
@@ -2210,7 +2210,7 @@
         <v>27.46</v>
       </c>
       <c r="S26" t="n">
-        <v>2.99</v>
+        <v>5.77</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -2230,43 +2230,43 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>133.7</v>
+        <v>135.53</v>
       </c>
       <c r="D27" t="n">
-        <v>-2.69</v>
+        <v>-1.36</v>
       </c>
       <c r="E27" t="n">
-        <v>137.19</v>
+        <v>137.55</v>
       </c>
       <c r="F27" t="n">
-        <v>131.81</v>
+        <v>131.99</v>
       </c>
       <c r="G27" t="n">
-        <v>119.18</v>
+        <v>119.27</v>
       </c>
       <c r="H27" t="n">
-        <v>8.375999999999999</v>
+        <v>8.522</v>
       </c>
       <c r="I27" t="n">
-        <v>6.489</v>
+        <v>6.518</v>
       </c>
       <c r="J27" t="n">
-        <v>78.12</v>
+        <v>79.73</v>
       </c>
       <c r="K27" t="n">
-        <v>79.42</v>
+        <v>79.95999999999999</v>
       </c>
       <c r="L27" t="n">
-        <v>75.51000000000001</v>
+        <v>79.27</v>
       </c>
       <c r="M27" t="n">
-        <v>4.71</v>
+        <v>6.94</v>
       </c>
       <c r="N27" t="n">
-        <v>7.54</v>
+        <v>7.65</v>
       </c>
       <c r="O27" t="n">
-        <v>0.63</v>
+        <v>0.91</v>
       </c>
       <c r="P27" t="n">
         <v>133.58</v>
@@ -2278,7 +2278,7 @@
         <v>131.83</v>
       </c>
       <c r="S27" t="n">
-        <v>5.34</v>
+        <v>7.87</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>

--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T27"/>
+  <dimension ref="A1:T39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -530,59 +530,59 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>103.27</v>
+        <v>104.39</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.18</v>
+        <v>1.08</v>
       </c>
       <c r="E2" t="n">
-        <v>102.62</v>
+        <v>103.01</v>
       </c>
       <c r="F2" t="n">
-        <v>102.33</v>
+        <v>102.4</v>
       </c>
       <c r="G2" t="n">
-        <v>102.43</v>
+        <v>102.59</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.441</v>
+        <v>-0.397</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.622</v>
+        <v>-0.73</v>
       </c>
       <c r="J2" t="n">
-        <v>48.98</v>
+        <v>57.83</v>
       </c>
       <c r="K2" t="n">
-        <v>40.83</v>
+        <v>46.5</v>
       </c>
       <c r="L2" t="n">
-        <v>65.28</v>
+        <v>80.48999999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>17.83</v>
+        <v>10.32</v>
       </c>
       <c r="N2" t="n">
-        <v>13.56</v>
+        <v>13.16</v>
       </c>
       <c r="O2" t="n">
-        <v>1.32</v>
+        <v>0.78</v>
       </c>
       <c r="P2" t="n">
-        <v>105</v>
+        <v>103.97</v>
       </c>
       <c r="Q2" t="n">
-        <v>105.8</v>
+        <v>105.18</v>
       </c>
       <c r="R2" t="n">
-        <v>103.27</v>
+        <v>103.39</v>
       </c>
       <c r="S2" t="n">
-        <v>0.46</v>
+        <v>0.27</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -598,59 +598,59 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>401.7</v>
+        <v>405.65</v>
       </c>
       <c r="D3" t="n">
-        <v>-2.74</v>
+        <v>0.98</v>
       </c>
       <c r="E3" t="n">
-        <v>406.24</v>
+        <v>407.81</v>
       </c>
       <c r="F3" t="n">
-        <v>404.57</v>
+        <v>404.93</v>
       </c>
       <c r="G3" t="n">
-        <v>391.31</v>
+        <v>394.64</v>
       </c>
       <c r="H3" t="n">
-        <v>12.29</v>
+        <v>11.808</v>
       </c>
       <c r="I3" t="n">
-        <v>12.133</v>
+        <v>12.137</v>
       </c>
       <c r="J3" t="n">
-        <v>55.7</v>
+        <v>54.49</v>
       </c>
       <c r="K3" t="n">
-        <v>58.1</v>
+        <v>56.9</v>
       </c>
       <c r="L3" t="n">
-        <v>50.92</v>
+        <v>49.69</v>
       </c>
       <c r="M3" t="n">
-        <v>24.93</v>
+        <v>19.47</v>
       </c>
       <c r="N3" t="n">
-        <v>33.99</v>
+        <v>33.71</v>
       </c>
       <c r="O3" t="n">
-        <v>0.73</v>
+        <v>0.58</v>
       </c>
       <c r="P3" t="n">
-        <v>413</v>
+        <v>409.73</v>
       </c>
       <c r="Q3" t="n">
-        <v>416.95</v>
+        <v>409.87</v>
       </c>
       <c r="R3" t="n">
-        <v>401.58</v>
+        <v>396</v>
       </c>
       <c r="S3" t="n">
-        <v>0.59</v>
+        <v>0.46</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -666,59 +666,59 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>24.04</v>
+        <v>24.45</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.25</v>
+        <v>1.71</v>
       </c>
       <c r="E4" t="n">
-        <v>24.24</v>
+        <v>24.2</v>
       </c>
       <c r="F4" t="n">
-        <v>24.67</v>
+        <v>24.52</v>
       </c>
       <c r="G4" t="n">
-        <v>25.34</v>
+        <v>25.25</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.801</v>
+        <v>-0.754</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.701</v>
+        <v>-0.697</v>
       </c>
       <c r="J4" t="n">
-        <v>10.18</v>
+        <v>17.17</v>
       </c>
       <c r="K4" t="n">
-        <v>12.4</v>
+        <v>13.99</v>
       </c>
       <c r="L4" t="n">
-        <v>5.75</v>
+        <v>23.53</v>
       </c>
       <c r="M4" t="n">
-        <v>102.25</v>
+        <v>99.56</v>
       </c>
       <c r="N4" t="n">
-        <v>113.08</v>
+        <v>110.56</v>
       </c>
       <c r="O4" t="n">
         <v>0.9</v>
       </c>
       <c r="P4" t="n">
-        <v>24.1</v>
+        <v>24.43</v>
       </c>
       <c r="Q4" t="n">
-        <v>24.44</v>
+        <v>24.6</v>
       </c>
       <c r="R4" t="n">
-        <v>24.03</v>
+        <v>24.25</v>
       </c>
       <c r="S4" t="n">
-        <v>0.84</v>
+        <v>0.82</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -734,59 +734,59 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>81.86</v>
+        <v>79.75</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9</v>
+        <v>-2.58</v>
       </c>
       <c r="E5" t="n">
-        <v>79.81</v>
+        <v>79.84</v>
       </c>
       <c r="F5" t="n">
-        <v>80.59999999999999</v>
+        <v>80.05</v>
       </c>
       <c r="G5" t="n">
-        <v>85.53</v>
+        <v>84.87</v>
       </c>
       <c r="H5" t="n">
-        <v>-3.076</v>
+        <v>-3.027</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.719</v>
+        <v>-2.784</v>
       </c>
       <c r="J5" t="n">
-        <v>39.19</v>
+        <v>39.51</v>
       </c>
       <c r="K5" t="n">
-        <v>26.74</v>
+        <v>31</v>
       </c>
       <c r="L5" t="n">
-        <v>64.09</v>
+        <v>56.54</v>
       </c>
       <c r="M5" t="n">
-        <v>57.32</v>
+        <v>34.29</v>
       </c>
       <c r="N5" t="n">
-        <v>38.3</v>
+        <v>37.56</v>
       </c>
       <c r="O5" t="n">
-        <v>1.5</v>
+        <v>0.91</v>
       </c>
       <c r="P5" t="n">
-        <v>81.11</v>
+        <v>83</v>
       </c>
       <c r="Q5" t="n">
-        <v>85.45999999999999</v>
+        <v>83.28</v>
       </c>
       <c r="R5" t="n">
-        <v>80.88</v>
+        <v>79.08</v>
       </c>
       <c r="S5" t="n">
-        <v>4.85</v>
+        <v>2.9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -802,59 +802,59 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>569.41</v>
+        <v>598.11</v>
       </c>
       <c r="D6" t="n">
-        <v>-3.34</v>
+        <v>5.04</v>
       </c>
       <c r="E6" t="n">
-        <v>599.8200000000001</v>
+        <v>593.76</v>
       </c>
       <c r="F6" t="n">
-        <v>596.91</v>
+        <v>598.72</v>
       </c>
       <c r="G6" t="n">
-        <v>570.99</v>
+        <v>573.9400000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>5.721</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>2.586</v>
+        <v>7.849</v>
       </c>
       <c r="J6" t="n">
-        <v>45.43</v>
+        <v>46.26</v>
       </c>
       <c r="K6" t="n">
-        <v>60.61</v>
+        <v>55.82</v>
       </c>
       <c r="L6" t="n">
-        <v>15.09</v>
+        <v>27.12</v>
       </c>
       <c r="M6" t="n">
-        <v>26.12</v>
+        <v>21.07</v>
       </c>
       <c r="N6" t="n">
-        <v>29.85</v>
+        <v>29.37</v>
       </c>
       <c r="O6" t="n">
-        <v>0.88</v>
+        <v>0.72</v>
       </c>
       <c r="P6" t="n">
-        <v>571</v>
+        <v>591</v>
       </c>
       <c r="Q6" t="n">
-        <v>585.9</v>
+        <v>599.99</v>
       </c>
       <c r="R6" t="n">
-        <v>555</v>
+        <v>581.2</v>
       </c>
       <c r="S6" t="n">
-        <v>2.36</v>
+        <v>1.91</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -870,59 +870,59 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7.64</v>
+        <v>7.59</v>
       </c>
       <c r="D7" t="n">
-        <v>0.92</v>
+        <v>-0.65</v>
       </c>
       <c r="E7" t="n">
-        <v>7.47</v>
+        <v>7.52</v>
       </c>
       <c r="F7" t="n">
-        <v>7.44</v>
+        <v>7.46</v>
       </c>
       <c r="G7" t="n">
-        <v>7.3</v>
+        <v>7.32</v>
       </c>
       <c r="H7" t="n">
-        <v>0.093</v>
+        <v>0.096</v>
       </c>
       <c r="I7" t="n">
-        <v>0.059</v>
+        <v>0.062</v>
       </c>
       <c r="J7" t="n">
-        <v>74.22</v>
+        <v>75.12</v>
       </c>
       <c r="K7" t="n">
-        <v>66.59999999999999</v>
+        <v>69.44</v>
       </c>
       <c r="L7" t="n">
-        <v>89.45999999999999</v>
+        <v>86.48999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>391.47</v>
+        <v>276.73</v>
       </c>
       <c r="N7" t="n">
-        <v>339.16</v>
+        <v>334.05</v>
       </c>
       <c r="O7" t="n">
-        <v>1.15</v>
+        <v>0.83</v>
       </c>
       <c r="P7" t="n">
-        <v>7.57</v>
+        <v>7.6</v>
       </c>
       <c r="Q7" t="n">
-        <v>7.69</v>
+        <v>7.71</v>
       </c>
       <c r="R7" t="n">
-        <v>7.55</v>
+        <v>7.54</v>
       </c>
       <c r="S7" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -938,59 +938,59 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>15.01</v>
+        <v>15.19</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.34</v>
+        <v>1.2</v>
       </c>
       <c r="E8" t="n">
         <v>15.2</v>
       </c>
       <c r="F8" t="n">
-        <v>15.49</v>
+        <v>15.39</v>
       </c>
       <c r="G8" t="n">
-        <v>15.65</v>
+        <v>15.61</v>
       </c>
       <c r="H8" t="n">
-        <v>0.032</v>
+        <v>0.024</v>
       </c>
       <c r="I8" t="n">
-        <v>0.164</v>
+        <v>0.152</v>
       </c>
       <c r="J8" t="n">
-        <v>12.66</v>
+        <v>15.04</v>
       </c>
       <c r="K8" t="n">
-        <v>20.59</v>
+        <v>18.74</v>
       </c>
       <c r="L8" t="n">
-        <v>-3.2</v>
+        <v>7.63</v>
       </c>
       <c r="M8" t="n">
-        <v>82.81999999999999</v>
+        <v>58.12</v>
       </c>
       <c r="N8" t="n">
-        <v>139.3</v>
+        <v>123.24</v>
       </c>
       <c r="O8" t="n">
-        <v>0.59</v>
+        <v>0.47</v>
       </c>
       <c r="P8" t="n">
-        <v>15.41</v>
+        <v>15.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>15.48</v>
+        <v>15.22</v>
       </c>
       <c r="R8" t="n">
-        <v>15</v>
+        <v>15.03</v>
       </c>
       <c r="S8" t="n">
-        <v>0.66</v>
+        <v>0.46</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -1006,59 +1006,59 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>34.18</v>
+        <v>35.13</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.43</v>
+        <v>2.78</v>
       </c>
       <c r="E9" t="n">
-        <v>34.66</v>
+        <v>34.54</v>
       </c>
       <c r="F9" t="n">
-        <v>35.52</v>
+        <v>35.14</v>
       </c>
       <c r="G9" t="n">
-        <v>37.19</v>
+        <v>37.09</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.09</v>
+        <v>-0.081</v>
       </c>
       <c r="I9" t="n">
-        <v>0.506</v>
+        <v>0.431</v>
       </c>
       <c r="J9" t="n">
-        <v>22.44</v>
+        <v>28.55</v>
       </c>
       <c r="K9" t="n">
-        <v>21.88</v>
+        <v>24.11</v>
       </c>
       <c r="L9" t="n">
-        <v>23.56</v>
+        <v>37.44</v>
       </c>
       <c r="M9" t="n">
-        <v>76.84</v>
+        <v>88.09</v>
       </c>
       <c r="N9" t="n">
-        <v>172.18</v>
+        <v>165.27</v>
       </c>
       <c r="O9" t="n">
-        <v>0.45</v>
+        <v>0.53</v>
       </c>
       <c r="P9" t="n">
-        <v>34.61</v>
+        <v>34.87</v>
       </c>
       <c r="Q9" t="n">
-        <v>35.61</v>
+        <v>35.86</v>
       </c>
       <c r="R9" t="n">
-        <v>34.18</v>
+        <v>34.78</v>
       </c>
       <c r="S9" t="n">
-        <v>6.71</v>
+        <v>7.69</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -1074,59 +1074,59 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>210.26</v>
+        <v>219.37</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.54</v>
+        <v>4.33</v>
       </c>
       <c r="E10" t="n">
-        <v>216.61</v>
+        <v>217</v>
       </c>
       <c r="F10" t="n">
-        <v>217.38</v>
+        <v>216.18</v>
       </c>
       <c r="G10" t="n">
-        <v>228.18</v>
+        <v>227.34</v>
       </c>
       <c r="H10" t="n">
-        <v>-9.759</v>
+        <v>-8.461</v>
       </c>
       <c r="I10" t="n">
-        <v>-8.993</v>
+        <v>-8.073</v>
       </c>
       <c r="J10" t="n">
-        <v>36.12</v>
+        <v>45.92</v>
       </c>
       <c r="K10" t="n">
-        <v>32.82</v>
+        <v>37.19</v>
       </c>
       <c r="L10" t="n">
-        <v>42.71</v>
+        <v>63.37</v>
       </c>
       <c r="M10" t="n">
-        <v>14.48</v>
+        <v>17.32</v>
       </c>
       <c r="N10" t="n">
-        <v>18.59</v>
+        <v>18.54</v>
       </c>
       <c r="O10" t="n">
-        <v>0.78</v>
+        <v>0.93</v>
       </c>
       <c r="P10" t="n">
-        <v>214.56</v>
+        <v>217.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>218.04</v>
+        <v>221.8</v>
       </c>
       <c r="R10" t="n">
-        <v>210.01</v>
+        <v>215</v>
       </c>
       <c r="S10" t="n">
-        <v>0.62</v>
+        <v>0.75</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -1142,59 +1142,59 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>442.84</v>
+        <v>459.76</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.39</v>
+        <v>3.82</v>
       </c>
       <c r="E11" t="n">
-        <v>456.37</v>
+        <v>453.08</v>
       </c>
       <c r="F11" t="n">
-        <v>455.86</v>
+        <v>458.75</v>
       </c>
       <c r="G11" t="n">
-        <v>424.06</v>
+        <v>428.58</v>
       </c>
       <c r="H11" t="n">
-        <v>16.772</v>
+        <v>15.74</v>
       </c>
       <c r="I11" t="n">
-        <v>14.02</v>
+        <v>13.055</v>
       </c>
       <c r="J11" t="n">
-        <v>53.72</v>
+        <v>50.39</v>
       </c>
       <c r="K11" t="n">
-        <v>66.36</v>
+        <v>61.04</v>
       </c>
       <c r="L11" t="n">
-        <v>28.45</v>
+        <v>29.1</v>
       </c>
       <c r="M11" t="n">
-        <v>28.33</v>
+        <v>26.78</v>
       </c>
       <c r="N11" t="n">
-        <v>43.43</v>
+        <v>43.13</v>
       </c>
       <c r="O11" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="P11" t="n">
-        <v>445.65</v>
+        <v>461.53</v>
       </c>
       <c r="Q11" t="n">
-        <v>454.5</v>
+        <v>463</v>
       </c>
       <c r="R11" t="n">
-        <v>434.7</v>
+        <v>444</v>
       </c>
       <c r="S11" t="n">
-        <v>3.2</v>
+        <v>3.02</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -1210,59 +1210,59 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>301.6</v>
+        <v>330.48</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.8</v>
+        <v>9.58</v>
       </c>
       <c r="E12" t="n">
+        <v>318.3</v>
+      </c>
+      <c r="F12" t="n">
+        <v>312.68</v>
+      </c>
+      <c r="G12" t="n">
         <v>315.82</v>
       </c>
-      <c r="F12" t="n">
-        <v>309.96</v>
-      </c>
-      <c r="G12" t="n">
-        <v>316.07</v>
-      </c>
       <c r="H12" t="n">
-        <v>2.125</v>
+        <v>3.964</v>
       </c>
       <c r="I12" t="n">
-        <v>4.49</v>
+        <v>5.051</v>
       </c>
       <c r="J12" t="n">
-        <v>46.48</v>
+        <v>58.46</v>
       </c>
       <c r="K12" t="n">
-        <v>51.18</v>
+        <v>53.61</v>
       </c>
       <c r="L12" t="n">
-        <v>37.09</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>27.06</v>
+        <v>35.99</v>
       </c>
       <c r="N12" t="n">
-        <v>33.9</v>
+        <v>34.26</v>
       </c>
       <c r="O12" t="n">
-        <v>0.8</v>
+        <v>1.05</v>
       </c>
       <c r="P12" t="n">
-        <v>308.6</v>
+        <v>316.67</v>
       </c>
       <c r="Q12" t="n">
-        <v>316</v>
+        <v>332.79</v>
       </c>
       <c r="R12" t="n">
-        <v>298.22</v>
+        <v>312.89</v>
       </c>
       <c r="S12" t="n">
-        <v>3.49</v>
+        <v>4.64</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -1278,59 +1278,59 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>103.5</v>
+        <v>104.25</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.23</v>
+        <v>0.72</v>
       </c>
       <c r="E13" t="n">
-        <v>108.21</v>
+        <v>105.91</v>
       </c>
       <c r="F13" t="n">
-        <v>111.72</v>
+        <v>110.67</v>
       </c>
       <c r="G13" t="n">
-        <v>114.6</v>
+        <v>114.74</v>
       </c>
       <c r="H13" t="n">
-        <v>3.83</v>
+        <v>3.221</v>
       </c>
       <c r="I13" t="n">
-        <v>6.638</v>
+        <v>6.131</v>
       </c>
       <c r="J13" t="n">
-        <v>16.3</v>
+        <v>13.88</v>
       </c>
       <c r="K13" t="n">
-        <v>22.48</v>
+        <v>19.62</v>
       </c>
       <c r="L13" t="n">
-        <v>3.93</v>
+        <v>2.41</v>
       </c>
       <c r="M13" t="n">
-        <v>58.17</v>
+        <v>44.05</v>
       </c>
       <c r="N13" t="n">
-        <v>121.08</v>
+        <v>117.42</v>
       </c>
       <c r="O13" t="n">
-        <v>0.48</v>
+        <v>0.38</v>
       </c>
       <c r="P13" t="n">
-        <v>105.8</v>
+        <v>106.61</v>
       </c>
       <c r="Q13" t="n">
-        <v>106.65</v>
+        <v>106.8</v>
       </c>
       <c r="R13" t="n">
-        <v>102.11</v>
+        <v>103.19</v>
       </c>
       <c r="S13" t="n">
-        <v>5.79</v>
+        <v>4.38</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -1346,59 +1346,59 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>238.1</v>
+        <v>254.72</v>
       </c>
       <c r="D14" t="n">
-        <v>-6.94</v>
+        <v>6.98</v>
       </c>
       <c r="E14" t="n">
-        <v>258.6</v>
+        <v>253.87</v>
       </c>
       <c r="F14" t="n">
-        <v>274.52</v>
+        <v>268.87</v>
       </c>
       <c r="G14" t="n">
-        <v>279.52</v>
+        <v>278.3</v>
       </c>
       <c r="H14" t="n">
-        <v>-10.913</v>
+        <v>-9.536</v>
       </c>
       <c r="I14" t="n">
-        <v>-6.473</v>
+        <v>-4.974</v>
       </c>
       <c r="J14" t="n">
-        <v>17.65</v>
+        <v>20.29</v>
       </c>
       <c r="K14" t="n">
-        <v>27.92</v>
+        <v>25.38</v>
       </c>
       <c r="L14" t="n">
-        <v>-2.88</v>
+        <v>10.12</v>
       </c>
       <c r="M14" t="n">
-        <v>42.76</v>
+        <v>34.67</v>
       </c>
       <c r="N14" t="n">
-        <v>30.03</v>
+        <v>30.13</v>
       </c>
       <c r="O14" t="n">
-        <v>1.42</v>
+        <v>1.15</v>
       </c>
       <c r="P14" t="n">
-        <v>249.9</v>
+        <v>250</v>
       </c>
       <c r="Q14" t="n">
-        <v>252</v>
+        <v>256.1</v>
       </c>
       <c r="R14" t="n">
-        <v>236.86</v>
+        <v>243.7</v>
       </c>
       <c r="S14" t="n">
-        <v>6.4</v>
+        <v>5.19</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -1414,59 +1414,59 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>211.99</v>
+        <v>215.93</v>
       </c>
       <c r="D15" t="n">
-        <v>-8.619999999999999</v>
+        <v>1.86</v>
       </c>
       <c r="E15" t="n">
-        <v>234.94</v>
+        <v>227.46</v>
       </c>
       <c r="F15" t="n">
-        <v>237.14</v>
+        <v>232.92</v>
       </c>
       <c r="G15" t="n">
-        <v>223.93</v>
+        <v>225.93</v>
       </c>
       <c r="H15" t="n">
-        <v>12.362</v>
+        <v>11.523</v>
       </c>
       <c r="I15" t="n">
-        <v>14.535</v>
+        <v>15.233</v>
       </c>
       <c r="J15" t="n">
-        <v>37.39</v>
+        <v>29.21</v>
       </c>
       <c r="K15" t="n">
-        <v>53.78</v>
+        <v>45.6</v>
       </c>
       <c r="L15" t="n">
-        <v>4.62</v>
+        <v>-3.56</v>
       </c>
       <c r="M15" t="n">
-        <v>42.37</v>
+        <v>40.65</v>
       </c>
       <c r="N15" t="n">
-        <v>44.17</v>
+        <v>44.34</v>
       </c>
       <c r="O15" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="P15" t="n">
-        <v>220.02</v>
+        <v>228</v>
       </c>
       <c r="Q15" t="n">
-        <v>220.08</v>
+        <v>232.88</v>
       </c>
       <c r="R15" t="n">
-        <v>209.2</v>
+        <v>210.67</v>
       </c>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -1482,59 +1482,59 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>41.7</v>
+        <v>42.93</v>
       </c>
       <c r="D16" t="n">
-        <v>-5.78</v>
+        <v>2.95</v>
       </c>
       <c r="E16" t="n">
-        <v>44.74</v>
+        <v>43.74</v>
       </c>
       <c r="F16" t="n">
-        <v>48.88</v>
+        <v>47.07</v>
       </c>
       <c r="G16" t="n">
-        <v>44.36</v>
+        <v>44.79</v>
       </c>
       <c r="H16" t="n">
-        <v>2.147</v>
+        <v>1.984</v>
       </c>
       <c r="I16" t="n">
-        <v>2.996</v>
+        <v>3.028</v>
       </c>
       <c r="J16" t="n">
-        <v>16.92</v>
+        <v>14.43</v>
       </c>
       <c r="K16" t="n">
-        <v>33.61</v>
+        <v>27.22</v>
       </c>
       <c r="L16" t="n">
-        <v>-16.47</v>
+        <v>-11.16</v>
       </c>
       <c r="M16" t="n">
-        <v>25.05</v>
+        <v>25.01</v>
       </c>
       <c r="N16" t="n">
-        <v>32.11</v>
+        <v>32.02</v>
       </c>
       <c r="O16" t="n">
         <v>0.78</v>
       </c>
       <c r="P16" t="n">
-        <v>43.02</v>
+        <v>45.27</v>
       </c>
       <c r="Q16" t="n">
-        <v>43.19</v>
+        <v>45.3</v>
       </c>
       <c r="R16" t="n">
-        <v>41.4</v>
+        <v>42.52</v>
       </c>
       <c r="S16" t="n">
-        <v>12.5</v>
+        <v>12.48</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -1550,59 +1550,59 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>19.83</v>
+        <v>20.13</v>
       </c>
       <c r="D17" t="n">
-        <v>-4.89</v>
+        <v>1.51</v>
       </c>
       <c r="E17" t="n">
-        <v>21.1</v>
+        <v>20.64</v>
       </c>
       <c r="F17" t="n">
-        <v>22.65</v>
+        <v>22.18</v>
       </c>
       <c r="G17" t="n">
-        <v>21.13</v>
+        <v>21.25</v>
       </c>
       <c r="H17" t="n">
-        <v>0.289</v>
+        <v>0.33</v>
       </c>
       <c r="I17" t="n">
-        <v>0.494</v>
+        <v>0.66</v>
       </c>
       <c r="J17" t="n">
-        <v>14.5</v>
+        <v>11.3</v>
       </c>
       <c r="K17" t="n">
-        <v>29.54</v>
+        <v>23.46</v>
       </c>
       <c r="L17" t="n">
-        <v>-15.59</v>
+        <v>-13.01</v>
       </c>
       <c r="M17" t="n">
-        <v>28.03</v>
+        <v>27.69</v>
       </c>
       <c r="N17" t="n">
-        <v>40.85</v>
+        <v>41.43</v>
       </c>
       <c r="O17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="P17" t="n">
-        <v>20.42</v>
+        <v>20.76</v>
       </c>
       <c r="Q17" t="n">
-        <v>20.67</v>
+        <v>21.12</v>
       </c>
       <c r="R17" t="n">
-        <v>19.74</v>
+        <v>20.07</v>
       </c>
       <c r="S17" t="n">
-        <v>7.6</v>
+        <v>7.51</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -1618,59 +1618,59 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>15.93</v>
+        <v>15.98</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.67</v>
+        <v>0.31</v>
       </c>
       <c r="E18" t="n">
-        <v>16.78</v>
+        <v>16.44</v>
       </c>
       <c r="F18" t="n">
-        <v>18.77</v>
+        <v>18.44</v>
       </c>
       <c r="G18" t="n">
-        <v>16.83</v>
+        <v>16.94</v>
       </c>
       <c r="H18" t="n">
-        <v>0.553</v>
+        <v>0.401</v>
       </c>
       <c r="I18" t="n">
-        <v>0.844</v>
+        <v>0.755</v>
       </c>
       <c r="J18" t="n">
-        <v>14.4</v>
+        <v>10.11</v>
       </c>
       <c r="K18" t="n">
-        <v>32.54</v>
+        <v>25.06</v>
       </c>
       <c r="L18" t="n">
-        <v>-21.86</v>
+        <v>-19.79</v>
       </c>
       <c r="M18" t="n">
-        <v>12.57</v>
+        <v>8.06</v>
       </c>
       <c r="N18" t="n">
-        <v>11.86</v>
+        <v>12.13</v>
       </c>
       <c r="O18" t="n">
-        <v>1.06</v>
+        <v>0.66</v>
       </c>
       <c r="P18" t="n">
-        <v>16.15</v>
+        <v>16.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>16.33</v>
+        <v>16.17</v>
       </c>
       <c r="R18" t="n">
-        <v>15.83</v>
+        <v>15.86</v>
       </c>
       <c r="S18" t="n">
-        <v>6.94</v>
+        <v>4.45</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -1686,59 +1686,59 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>38.33</v>
+        <v>38.41</v>
       </c>
       <c r="D19" t="n">
-        <v>0.08</v>
+        <v>0.21</v>
       </c>
       <c r="E19" t="n">
-        <v>37.91</v>
+        <v>37.93</v>
       </c>
       <c r="F19" t="n">
-        <v>37.66</v>
+        <v>37.62</v>
       </c>
       <c r="G19" t="n">
-        <v>37.32</v>
+        <v>37.43</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.142</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.294</v>
+        <v>-0.274</v>
       </c>
       <c r="J19" t="n">
-        <v>55.18</v>
+        <v>61.11</v>
       </c>
       <c r="K19" t="n">
-        <v>50.15</v>
+        <v>53.8</v>
       </c>
       <c r="L19" t="n">
-        <v>65.26000000000001</v>
+        <v>75.72</v>
       </c>
       <c r="M19" t="n">
-        <v>57.49</v>
+        <v>57.68</v>
       </c>
       <c r="N19" t="n">
-        <v>59.41</v>
+        <v>60.37</v>
       </c>
       <c r="O19" t="n">
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
       <c r="P19" t="n">
-        <v>38.3</v>
+        <v>39.16</v>
       </c>
       <c r="Q19" t="n">
-        <v>39.32</v>
+        <v>39.57</v>
       </c>
       <c r="R19" t="n">
-        <v>37.95</v>
+        <v>38.29</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -1754,59 +1754,59 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>16.9</v>
+        <v>17.7</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.43</v>
+        <v>4.73</v>
       </c>
       <c r="E20" t="n">
+        <v>17.41</v>
+      </c>
+      <c r="F20" t="n">
         <v>17.49</v>
       </c>
-      <c r="F20" t="n">
-        <v>17.57</v>
-      </c>
       <c r="G20" t="n">
-        <v>18.02</v>
+        <v>18</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.356</v>
+        <v>-0.342</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.223</v>
+        <v>-0.268</v>
       </c>
       <c r="J20" t="n">
-        <v>31.53</v>
+        <v>36.92</v>
       </c>
       <c r="K20" t="n">
-        <v>32.56</v>
+        <v>34.01</v>
       </c>
       <c r="L20" t="n">
-        <v>29.46</v>
+        <v>42.73</v>
       </c>
       <c r="M20" t="n">
-        <v>148.21</v>
+        <v>224.64</v>
       </c>
       <c r="N20" t="n">
-        <v>274.03</v>
+        <v>274.71</v>
       </c>
       <c r="O20" t="n">
-        <v>0.54</v>
+        <v>0.82</v>
       </c>
       <c r="P20" t="n">
-        <v>17.31</v>
+        <v>17.61</v>
       </c>
       <c r="Q20" t="n">
-        <v>17.79</v>
+        <v>18.2</v>
       </c>
       <c r="R20" t="n">
-        <v>16.87</v>
+        <v>17.33</v>
       </c>
       <c r="S20" t="n">
-        <v>6.43</v>
+        <v>9.74</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -1822,59 +1822,59 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>49</v>
+        <v>51.03</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.8</v>
+        <v>4.14</v>
       </c>
       <c r="E21" t="n">
-        <v>50.33</v>
+        <v>50.36</v>
       </c>
       <c r="F21" t="n">
-        <v>50.86</v>
+        <v>50.95</v>
       </c>
       <c r="G21" t="n">
-        <v>51.72</v>
+        <v>51.66</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.611</v>
+        <v>-1.31</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.503</v>
+        <v>-1.256</v>
       </c>
       <c r="J21" t="n">
-        <v>30.66</v>
+        <v>35.38</v>
       </c>
       <c r="K21" t="n">
-        <v>32.83</v>
+        <v>33.68</v>
       </c>
       <c r="L21" t="n">
-        <v>26.33</v>
+        <v>38.77</v>
       </c>
       <c r="M21" t="n">
-        <v>42.11</v>
+        <v>52.1</v>
       </c>
       <c r="N21" t="n">
-        <v>63.86</v>
+        <v>63.83</v>
       </c>
       <c r="O21" t="n">
-        <v>0.66</v>
+        <v>0.82</v>
       </c>
       <c r="P21" t="n">
-        <v>50.03</v>
+        <v>50.85</v>
       </c>
       <c r="Q21" t="n">
-        <v>51.25</v>
+        <v>52.22</v>
       </c>
       <c r="R21" t="n">
-        <v>48.99</v>
+        <v>50.08</v>
       </c>
       <c r="S21" t="n">
-        <v>3.36</v>
+        <v>4.15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -1890,59 +1890,59 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>46.21</v>
+        <v>46.85</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.41</v>
+        <v>1.38</v>
       </c>
       <c r="E22" t="n">
-        <v>46.7</v>
+        <v>46.55</v>
       </c>
       <c r="F22" t="n">
-        <v>47.78</v>
+        <v>47.3</v>
       </c>
       <c r="G22" t="n">
-        <v>50.11</v>
+        <v>49.87</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.479</v>
+        <v>-2.261</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.222</v>
+        <v>-2.055</v>
       </c>
       <c r="J22" t="n">
-        <v>15.33</v>
+        <v>19.3</v>
       </c>
       <c r="K22" t="n">
-        <v>15.12</v>
+        <v>16.52</v>
       </c>
       <c r="L22" t="n">
-        <v>15.74</v>
+        <v>24.86</v>
       </c>
       <c r="M22" t="n">
-        <v>24.87</v>
+        <v>23.45</v>
       </c>
       <c r="N22" t="n">
-        <v>34.29</v>
+        <v>33.26</v>
       </c>
       <c r="O22" t="n">
-        <v>0.73</v>
+        <v>0.71</v>
       </c>
       <c r="P22" t="n">
-        <v>46.4</v>
+        <v>47.25</v>
       </c>
       <c r="Q22" t="n">
-        <v>47.15</v>
+        <v>47.36</v>
       </c>
       <c r="R22" t="n">
-        <v>46.06</v>
+        <v>46.55</v>
       </c>
       <c r="S22" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -1958,59 +1958,59 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>14.8</v>
+        <v>14.47</v>
       </c>
       <c r="D23" t="n">
-        <v>2.78</v>
+        <v>-2.23</v>
       </c>
       <c r="E23" t="n">
-        <v>14.39</v>
+        <v>14.4</v>
       </c>
       <c r="F23" t="n">
-        <v>14.44</v>
+        <v>14.34</v>
       </c>
       <c r="G23" t="n">
-        <v>15.25</v>
+        <v>15.16</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.238</v>
+        <v>-1.061</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.406</v>
+        <v>-1.205</v>
       </c>
       <c r="J23" t="n">
-        <v>44.75</v>
+        <v>48.21</v>
       </c>
       <c r="K23" t="n">
-        <v>29.7</v>
+        <v>35.87</v>
       </c>
       <c r="L23" t="n">
-        <v>74.86</v>
+        <v>72.88</v>
       </c>
       <c r="M23" t="n">
-        <v>485.86</v>
+        <v>341.55</v>
       </c>
       <c r="N23" t="n">
-        <v>257.82</v>
+        <v>262.77</v>
       </c>
       <c r="O23" t="n">
-        <v>1.88</v>
+        <v>1.3</v>
       </c>
       <c r="P23" t="n">
-        <v>14.34</v>
+        <v>15.15</v>
       </c>
       <c r="Q23" t="n">
-        <v>15.26</v>
+        <v>15.23</v>
       </c>
       <c r="R23" t="n">
         <v>14.33</v>
       </c>
       <c r="S23" t="n">
-        <v>13.96</v>
+        <v>9.81</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -2026,59 +2026,59 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>58.42</v>
+        <v>59.21</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.73</v>
+        <v>1.35</v>
       </c>
       <c r="E24" t="n">
-        <v>59.38</v>
+        <v>58.99</v>
       </c>
       <c r="F24" t="n">
-        <v>61.25</v>
+        <v>60.51</v>
       </c>
       <c r="G24" t="n">
-        <v>64.51000000000001</v>
+        <v>64.20999999999999</v>
       </c>
       <c r="H24" t="n">
-        <v>-3.29</v>
+        <v>-3.067</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.755</v>
+        <v>-2.599</v>
       </c>
       <c r="J24" t="n">
-        <v>13.86</v>
+        <v>17.58</v>
       </c>
       <c r="K24" t="n">
-        <v>12.64</v>
+        <v>14.29</v>
       </c>
       <c r="L24" t="n">
-        <v>16.28</v>
+        <v>24.15</v>
       </c>
       <c r="M24" t="n">
-        <v>8.1</v>
+        <v>7.11</v>
       </c>
       <c r="N24" t="n">
-        <v>12.73</v>
+        <v>12.53</v>
       </c>
       <c r="O24" t="n">
-        <v>0.64</v>
+        <v>0.57</v>
       </c>
       <c r="P24" t="n">
-        <v>59.05</v>
+        <v>59.92</v>
       </c>
       <c r="Q24" t="n">
-        <v>59.88</v>
+        <v>60</v>
       </c>
       <c r="R24" t="n">
-        <v>58.1</v>
+        <v>59.13</v>
       </c>
       <c r="S24" t="n">
-        <v>2.2</v>
+        <v>1.93</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -2094,59 +2094,59 @@
         </is>
       </c>
       <c r="C25" t="n">
+        <v>28.01</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-1.58</v>
+      </c>
+      <c r="E25" t="n">
+        <v>28.13</v>
+      </c>
+      <c r="F25" t="n">
+        <v>27.93</v>
+      </c>
+      <c r="G25" t="n">
+        <v>29.95</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-0.701</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-0.496</v>
+      </c>
+      <c r="J25" t="n">
+        <v>47.52</v>
+      </c>
+      <c r="K25" t="n">
+        <v>40.09</v>
+      </c>
+      <c r="L25" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="M25" t="n">
+        <v>176.48</v>
+      </c>
+      <c r="N25" t="n">
+        <v>239.72</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="P25" t="n">
         <v>28.46</v>
       </c>
-      <c r="D25" t="n">
-        <v>-0.77</v>
-      </c>
-      <c r="E25" t="n">
-        <v>27.94</v>
-      </c>
-      <c r="F25" t="n">
-        <v>28.27</v>
-      </c>
-      <c r="G25" t="n">
-        <v>30.01</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-0.639</v>
-      </c>
-      <c r="I25" t="n">
-        <v>-0.365</v>
-      </c>
-      <c r="J25" t="n">
-        <v>44.47</v>
-      </c>
-      <c r="K25" t="n">
-        <v>36.37</v>
-      </c>
-      <c r="L25" t="n">
-        <v>60.68</v>
-      </c>
-      <c r="M25" t="n">
-        <v>250.43</v>
-      </c>
-      <c r="N25" t="n">
-        <v>239.03</v>
-      </c>
-      <c r="O25" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="P25" t="n">
-        <v>28.67</v>
-      </c>
       <c r="Q25" t="n">
-        <v>29.78</v>
+        <v>28.8</v>
       </c>
       <c r="R25" t="n">
-        <v>28.2</v>
+        <v>27.16</v>
       </c>
       <c r="S25" t="n">
-        <v>15.76</v>
+        <v>11.11</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -2162,59 +2162,59 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>26.3</v>
+        <v>25.31</v>
       </c>
       <c r="D26" t="n">
-        <v>-5.12</v>
+        <v>-3.76</v>
       </c>
       <c r="E26" t="n">
-        <v>27.58</v>
+        <v>26.98</v>
       </c>
       <c r="F26" t="n">
-        <v>28.29</v>
+        <v>27.72</v>
       </c>
       <c r="G26" t="n">
-        <v>28.79</v>
+        <v>28.71</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.008</v>
+        <v>-0.201</v>
       </c>
       <c r="I26" t="n">
-        <v>0.408</v>
+        <v>0.319</v>
       </c>
       <c r="J26" t="n">
-        <v>12.79</v>
+        <v>10.15</v>
       </c>
       <c r="K26" t="n">
-        <v>18.78</v>
+        <v>15.9</v>
       </c>
       <c r="L26" t="n">
-        <v>0.79</v>
+        <v>-1.37</v>
       </c>
       <c r="M26" t="n">
-        <v>263.14</v>
+        <v>190.8</v>
       </c>
       <c r="N26" t="n">
-        <v>282.45</v>
+        <v>281.4</v>
       </c>
       <c r="O26" t="n">
-        <v>0.93</v>
+        <v>0.68</v>
       </c>
       <c r="P26" t="n">
-        <v>27.75</v>
+        <v>26.53</v>
       </c>
       <c r="Q26" t="n">
-        <v>27.98</v>
+        <v>26.61</v>
       </c>
       <c r="R26" t="n">
-        <v>26</v>
+        <v>25.05</v>
       </c>
       <c r="S26" t="n">
-        <v>7.82</v>
+        <v>5.67</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
@@ -2230,59 +2230,875 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>148.03</v>
+        <v>153.48</v>
       </c>
       <c r="D27" t="n">
-        <v>9.220000000000001</v>
+        <v>3.68</v>
       </c>
       <c r="E27" t="n">
-        <v>140.38</v>
+        <v>143.19</v>
       </c>
       <c r="F27" t="n">
-        <v>135.96</v>
+        <v>138.31</v>
       </c>
       <c r="G27" t="n">
-        <v>121.5</v>
+        <v>123.98</v>
       </c>
       <c r="H27" t="n">
-        <v>9.287000000000001</v>
+        <v>10.569</v>
       </c>
       <c r="I27" t="n">
-        <v>6.971</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="J27" t="n">
-        <v>78.91</v>
+        <v>80.81999999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>79.61</v>
+        <v>80.02</v>
       </c>
       <c r="L27" t="n">
-        <v>77.53</v>
+        <v>82.42</v>
       </c>
       <c r="M27" t="n">
-        <v>14.32</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="N27" t="n">
-        <v>8.109999999999999</v>
+        <v>8.42</v>
       </c>
       <c r="O27" t="n">
-        <v>1.77</v>
+        <v>1.09</v>
       </c>
       <c r="P27" t="n">
-        <v>138.01</v>
+        <v>150.99</v>
       </c>
       <c r="Q27" t="n">
-        <v>156.78</v>
+        <v>159.88</v>
       </c>
       <c r="R27" t="n">
-        <v>138.01</v>
+        <v>147.72</v>
       </c>
       <c r="S27" t="n">
-        <v>16.23</v>
+        <v>10.44</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>601899</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>紫金矿业</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>34.04</v>
+      </c>
+      <c r="D28" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="E28" t="n">
+        <v>32.82</v>
+      </c>
+      <c r="F28" t="n">
+        <v>32.41</v>
+      </c>
+      <c r="G28" t="n">
+        <v>34.34</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-1.257</v>
+      </c>
+      <c r="I28" t="n">
+        <v>-1.292</v>
+      </c>
+      <c r="J28" t="n">
+        <v>64.62</v>
+      </c>
+      <c r="K28" t="n">
+        <v>48.53</v>
+      </c>
+      <c r="L28" t="n">
+        <v>96.8</v>
+      </c>
+      <c r="M28" t="n">
+        <v>280.32</v>
+      </c>
+      <c r="N28" t="n">
+        <v>305.69</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="P28" t="n">
+        <v>33.86</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>34.58</v>
+      </c>
+      <c r="R28" t="n">
+        <v>33.62</v>
+      </c>
+      <c r="S28" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>600219</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>南山铝业</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="E29" t="n">
+        <v>6.13</v>
+      </c>
+      <c r="F29" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="G29" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="H29" t="n">
+        <v>-0.253</v>
+      </c>
+      <c r="I29" t="n">
+        <v>-0.206</v>
+      </c>
+      <c r="J29" t="n">
+        <v>43.78</v>
+      </c>
+      <c r="K29" t="n">
+        <v>32.31</v>
+      </c>
+      <c r="L29" t="n">
+        <v>66.70999999999999</v>
+      </c>
+      <c r="M29" t="n">
+        <v>192.68</v>
+      </c>
+      <c r="N29" t="n">
+        <v>293.38</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="P29" t="n">
+        <v>6.23</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>6.26</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="S29" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>601939</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>建设银行</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>9.460000000000001</v>
+      </c>
+      <c r="D30" t="n">
+        <v>-1.97</v>
+      </c>
+      <c r="E30" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="F30" t="n">
+        <v>9.41</v>
+      </c>
+      <c r="G30" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.146</v>
+      </c>
+      <c r="J30" t="n">
+        <v>79.28</v>
+      </c>
+      <c r="K30" t="n">
+        <v>83.48</v>
+      </c>
+      <c r="L30" t="n">
+        <v>70.87</v>
+      </c>
+      <c r="M30" t="n">
+        <v>99.28</v>
+      </c>
+      <c r="N30" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="P30" t="n">
+        <v>9.58</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>9.67</v>
+      </c>
+      <c r="R30" t="n">
+        <v>9.44</v>
+      </c>
+      <c r="S30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>600048</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>保利发展</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="E31" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="F31" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="G31" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="H31" t="n">
+        <v>-0.216</v>
+      </c>
+      <c r="I31" t="n">
+        <v>-0.184</v>
+      </c>
+      <c r="J31" t="n">
+        <v>12.53</v>
+      </c>
+      <c r="K31" t="n">
+        <v>11.01</v>
+      </c>
+      <c r="L31" t="n">
+        <v>15.59</v>
+      </c>
+      <c r="M31" t="n">
+        <v>59.09</v>
+      </c>
+      <c r="N31" t="n">
+        <v>114.12</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="P31" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="R31" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>600941</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>中国移动</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>93.7</v>
+      </c>
+      <c r="D32" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="E32" t="n">
+        <v>93.64</v>
+      </c>
+      <c r="F32" t="n">
+        <v>94.40000000000001</v>
+      </c>
+      <c r="G32" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="H32" t="n">
+        <v>-0.302</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.103</v>
+      </c>
+      <c r="J32" t="n">
+        <v>20.33</v>
+      </c>
+      <c r="K32" t="n">
+        <v>22.79</v>
+      </c>
+      <c r="L32" t="n">
+        <v>15.41</v>
+      </c>
+      <c r="M32" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="N32" t="n">
+        <v>10.52</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="P32" t="n">
+        <v>94.15000000000001</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>94.31999999999999</v>
+      </c>
+      <c r="R32" t="n">
+        <v>93.58</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>002352</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>顺丰控股</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>38.04</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="n">
+        <v>37.32</v>
+      </c>
+      <c r="F33" t="n">
+        <v>36.74</v>
+      </c>
+      <c r="G33" t="n">
+        <v>37.03</v>
+      </c>
+      <c r="H33" t="n">
+        <v>-0.046</v>
+      </c>
+      <c r="I33" t="n">
+        <v>-0.202</v>
+      </c>
+      <c r="J33" t="n">
+        <v>70.83</v>
+      </c>
+      <c r="K33" t="n">
+        <v>57.68</v>
+      </c>
+      <c r="L33" t="n">
+        <v>97.13</v>
+      </c>
+      <c r="M33" t="n">
+        <v>21.36</v>
+      </c>
+      <c r="N33" t="n">
+        <v>22.84</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="P33" t="n">
+        <v>38.42</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>38.66</v>
+      </c>
+      <c r="R33" t="n">
+        <v>37.92</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>603803</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>瑞斯康达</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>13.68</v>
+      </c>
+      <c r="D34" t="n">
+        <v>9.970000000000001</v>
+      </c>
+      <c r="E34" t="n">
+        <v>13.57</v>
+      </c>
+      <c r="F34" t="n">
+        <v>14.07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>12.92</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.9429999999999999</v>
+      </c>
+      <c r="J34" t="n">
+        <v>36.89</v>
+      </c>
+      <c r="K34" t="n">
+        <v>50.87</v>
+      </c>
+      <c r="L34" t="n">
+        <v>8.92</v>
+      </c>
+      <c r="M34" t="n">
+        <v>84.48999999999999</v>
+      </c>
+      <c r="N34" t="n">
+        <v>79.39</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="P34" t="n">
+        <v>13.06</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>13.68</v>
+      </c>
+      <c r="R34" t="n">
+        <v>13.06</v>
+      </c>
+      <c r="S34" t="n">
+        <v>19.89</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>002624</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>完美世界</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>19.33</v>
+      </c>
+      <c r="D35" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="E35" t="n">
+        <v>18.23</v>
+      </c>
+      <c r="F35" t="n">
+        <v>17.99</v>
+      </c>
+      <c r="G35" t="n">
+        <v>18.97</v>
+      </c>
+      <c r="H35" t="n">
+        <v>-0.429</v>
+      </c>
+      <c r="I35" t="n">
+        <v>-0.383</v>
+      </c>
+      <c r="J35" t="n">
+        <v>59.65</v>
+      </c>
+      <c r="K35" t="n">
+        <v>41.33</v>
+      </c>
+      <c r="L35" t="n">
+        <v>96.3</v>
+      </c>
+      <c r="M35" t="n">
+        <v>69.78</v>
+      </c>
+      <c r="N35" t="n">
+        <v>49.86</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P35" t="n">
+        <v>17.95</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>19.33</v>
+      </c>
+      <c r="R35" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="S35" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>002558</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>巨人网络</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>34.69</v>
+      </c>
+      <c r="D36" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="E36" t="n">
+        <v>32.33</v>
+      </c>
+      <c r="F36" t="n">
+        <v>32.17</v>
+      </c>
+      <c r="G36" t="n">
+        <v>33.78</v>
+      </c>
+      <c r="H36" t="n">
+        <v>-1.653</v>
+      </c>
+      <c r="I36" t="n">
+        <v>-1.884</v>
+      </c>
+      <c r="J36" t="n">
+        <v>46.81</v>
+      </c>
+      <c r="K36" t="n">
+        <v>28.71</v>
+      </c>
+      <c r="L36" t="n">
+        <v>83.02</v>
+      </c>
+      <c r="M36" t="n">
+        <v>55.21</v>
+      </c>
+      <c r="N36" t="n">
+        <v>41.13</v>
+      </c>
+      <c r="O36" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P36" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>34.69</v>
+      </c>
+      <c r="R36" t="n">
+        <v>31.95</v>
+      </c>
+      <c r="S36" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>601088</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>中国神华</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>47.09</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="E37" t="n">
+        <v>47.37</v>
+      </c>
+      <c r="F37" t="n">
+        <v>48.11</v>
+      </c>
+      <c r="G37" t="n">
+        <v>47.83</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1.343</v>
+      </c>
+      <c r="J37" t="n">
+        <v>25.83</v>
+      </c>
+      <c r="K37" t="n">
+        <v>35.08</v>
+      </c>
+      <c r="L37" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="M37" t="n">
+        <v>26.75</v>
+      </c>
+      <c r="N37" t="n">
+        <v>44.47</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="P37" t="n">
+        <v>46.33</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>47.48</v>
+      </c>
+      <c r="R37" t="n">
+        <v>45.87</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>600963</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>岳阳林纸</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="D38" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="E38" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="F38" t="n">
+        <v>4.79</v>
+      </c>
+      <c r="G38" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="H38" t="n">
+        <v>-0.301</v>
+      </c>
+      <c r="I38" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="J38" t="n">
+        <v>39.18</v>
+      </c>
+      <c r="K38" t="n">
+        <v>27.65</v>
+      </c>
+      <c r="L38" t="n">
+        <v>62.24</v>
+      </c>
+      <c r="M38" t="n">
+        <v>25.95</v>
+      </c>
+      <c r="N38" t="n">
+        <v>44.91</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="P38" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="R38" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="S38" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>601877</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>正泰电器</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>32.74</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="E39" t="n">
+        <v>33.41</v>
+      </c>
+      <c r="F39" t="n">
+        <v>34.12</v>
+      </c>
+      <c r="G39" t="n">
+        <v>35.82</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.616</v>
+      </c>
+      <c r="J39" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="K39" t="n">
+        <v>20.13</v>
+      </c>
+      <c r="L39" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="M39" t="n">
+        <v>24.89</v>
+      </c>
+      <c r="N39" t="n">
+        <v>57.23</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="P39" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="R39" t="n">
+        <v>32.32</v>
+      </c>
+      <c r="S39" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>

--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -530,59 +530,59 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>104.39</v>
+        <v>105</v>
       </c>
       <c r="D2" t="n">
-        <v>1.08</v>
+        <v>0.58</v>
       </c>
       <c r="E2" t="n">
-        <v>103.01</v>
+        <v>103.75</v>
       </c>
       <c r="F2" t="n">
-        <v>102.4</v>
+        <v>102.65</v>
       </c>
       <c r="G2" t="n">
-        <v>102.59</v>
+        <v>102.77</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.397</v>
+        <v>-0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.73</v>
+        <v>-0.624</v>
       </c>
       <c r="J2" t="n">
-        <v>57.83</v>
+        <v>67.26000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>46.5</v>
+        <v>53.42</v>
       </c>
       <c r="L2" t="n">
-        <v>80.48999999999999</v>
+        <v>94.94</v>
       </c>
       <c r="M2" t="n">
-        <v>12.27</v>
+        <v>15.18</v>
       </c>
       <c r="N2" t="n">
-        <v>13.26</v>
+        <v>13.52</v>
       </c>
       <c r="O2" t="n">
-        <v>0.93</v>
+        <v>1.12</v>
       </c>
       <c r="P2" t="n">
-        <v>103.97</v>
+        <v>104</v>
       </c>
       <c r="Q2" t="n">
-        <v>105.18</v>
+        <v>105.26</v>
       </c>
       <c r="R2" t="n">
-        <v>103.39</v>
+        <v>103.88</v>
       </c>
       <c r="S2" t="n">
-        <v>0.32</v>
+        <v>0.39</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
     </row>
@@ -598,59 +598,59 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>405.71</v>
+        <v>401.17</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>-1.12</v>
       </c>
       <c r="E3" t="n">
-        <v>407.82</v>
+        <v>407.55</v>
       </c>
       <c r="F3" t="n">
-        <v>404.94</v>
+        <v>405</v>
       </c>
       <c r="G3" t="n">
-        <v>394.65</v>
+        <v>397.19</v>
       </c>
       <c r="H3" t="n">
-        <v>11.813</v>
+        <v>10.894</v>
       </c>
       <c r="I3" t="n">
-        <v>12.138</v>
+        <v>11.889</v>
       </c>
       <c r="J3" t="n">
-        <v>54.55</v>
+        <v>50.72</v>
       </c>
       <c r="K3" t="n">
-        <v>56.91</v>
+        <v>54.85</v>
       </c>
       <c r="L3" t="n">
-        <v>49.82</v>
+        <v>42.46</v>
       </c>
       <c r="M3" t="n">
-        <v>23.17</v>
+        <v>22.31</v>
       </c>
       <c r="N3" t="n">
-        <v>33.9</v>
+        <v>33.46</v>
       </c>
       <c r="O3" t="n">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
       <c r="P3" t="n">
-        <v>409.73</v>
+        <v>407.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>409.87</v>
+        <v>411.99</v>
       </c>
       <c r="R3" t="n">
-        <v>396</v>
+        <v>397.2</v>
       </c>
       <c r="S3" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
     </row>
@@ -666,59 +666,59 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>24.51</v>
+        <v>24.13</v>
       </c>
       <c r="D4" t="n">
-        <v>1.96</v>
+        <v>-1.55</v>
       </c>
       <c r="E4" t="n">
         <v>24.21</v>
       </c>
       <c r="F4" t="n">
-        <v>24.53</v>
+        <v>24.38</v>
       </c>
       <c r="G4" t="n">
-        <v>25.25</v>
+        <v>25.15</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.749</v>
+        <v>-0.741</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.696</v>
+        <v>-0.705</v>
       </c>
       <c r="J4" t="n">
-        <v>18.26</v>
+        <v>19.62</v>
       </c>
       <c r="K4" t="n">
-        <v>14.36</v>
+        <v>16.11</v>
       </c>
       <c r="L4" t="n">
-        <v>26.08</v>
+        <v>26.63</v>
       </c>
       <c r="M4" t="n">
-        <v>117.15</v>
+        <v>78.87</v>
       </c>
       <c r="N4" t="n">
-        <v>111.44</v>
+        <v>111.29</v>
       </c>
       <c r="O4" t="n">
-        <v>1.05</v>
+        <v>0.71</v>
       </c>
       <c r="P4" t="n">
-        <v>24.43</v>
+        <v>24.47</v>
       </c>
       <c r="Q4" t="n">
-        <v>24.6</v>
+        <v>24.47</v>
       </c>
       <c r="R4" t="n">
-        <v>24.25</v>
+        <v>24.08</v>
       </c>
       <c r="S4" t="n">
-        <v>0.96</v>
+        <v>0.65</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
     </row>
@@ -734,59 +734,59 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>79.94</v>
+        <v>78.29000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>-2.35</v>
+        <v>-2.06</v>
       </c>
       <c r="E5" t="n">
-        <v>79.87</v>
+        <v>79.79000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>80.06</v>
+        <v>79.51000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>84.88</v>
+        <v>84.11</v>
       </c>
       <c r="H5" t="n">
-        <v>-3.012</v>
+        <v>-3.056</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.781</v>
+        <v>-2.836</v>
       </c>
       <c r="J5" t="n">
-        <v>40.17</v>
+        <v>35.06</v>
       </c>
       <c r="K5" t="n">
-        <v>31.22</v>
+        <v>32.5</v>
       </c>
       <c r="L5" t="n">
-        <v>58.08</v>
+        <v>40.19</v>
       </c>
       <c r="M5" t="n">
-        <v>39.2</v>
+        <v>23.26</v>
       </c>
       <c r="N5" t="n">
-        <v>37.81</v>
+        <v>36.14</v>
       </c>
       <c r="O5" t="n">
-        <v>1.04</v>
+        <v>0.64</v>
       </c>
       <c r="P5" t="n">
-        <v>83</v>
+        <v>79.95</v>
       </c>
       <c r="Q5" t="n">
-        <v>83.28</v>
+        <v>80.68000000000001</v>
       </c>
       <c r="R5" t="n">
-        <v>79.08</v>
+        <v>78</v>
       </c>
       <c r="S5" t="n">
-        <v>3.31</v>
+        <v>1.97</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
     </row>
@@ -802,59 +802,59 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>601.87</v>
+        <v>582</v>
       </c>
       <c r="D6" t="n">
-        <v>5.7</v>
+        <v>-3.3</v>
       </c>
       <c r="E6" t="n">
-        <v>594.51</v>
+        <v>588.0700000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>599.1</v>
+        <v>599.78</v>
       </c>
       <c r="G6" t="n">
-        <v>574.13</v>
+        <v>575.38</v>
       </c>
       <c r="H6" t="n">
-        <v>9.75</v>
+        <v>8.476000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>7.909</v>
+        <v>8.023</v>
       </c>
       <c r="J6" t="n">
-        <v>47.65</v>
+        <v>41.77</v>
       </c>
       <c r="K6" t="n">
-        <v>56.29</v>
+        <v>51.45</v>
       </c>
       <c r="L6" t="n">
-        <v>30.37</v>
+        <v>22.4</v>
       </c>
       <c r="M6" t="n">
-        <v>25.54</v>
+        <v>17.73</v>
       </c>
       <c r="N6" t="n">
-        <v>29.59</v>
+        <v>28.59</v>
       </c>
       <c r="O6" t="n">
-        <v>0.86</v>
+        <v>0.62</v>
       </c>
       <c r="P6" t="n">
-        <v>591</v>
+        <v>593.01</v>
       </c>
       <c r="Q6" t="n">
-        <v>602</v>
+        <v>596.77</v>
       </c>
       <c r="R6" t="n">
-        <v>581.2</v>
+        <v>578.6900000000001</v>
       </c>
       <c r="S6" t="n">
-        <v>2.31</v>
+        <v>1.6</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
     </row>
@@ -870,59 +870,59 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7.58</v>
+        <v>7.63</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.79</v>
+        <v>0.66</v>
       </c>
       <c r="E7" t="n">
-        <v>7.52</v>
+        <v>7.56</v>
       </c>
       <c r="F7" t="n">
         <v>7.46</v>
       </c>
       <c r="G7" t="n">
-        <v>7.32</v>
+        <v>7.35</v>
       </c>
       <c r="H7" t="n">
-        <v>0.096</v>
+        <v>0.104</v>
       </c>
       <c r="I7" t="n">
-        <v>0.061</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>74.48</v>
+        <v>77.86</v>
       </c>
       <c r="K7" t="n">
-        <v>69.23</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>84.98999999999999</v>
+        <v>89.37</v>
       </c>
       <c r="M7" t="n">
-        <v>330.87</v>
+        <v>275.75</v>
       </c>
       <c r="N7" t="n">
-        <v>336.76</v>
+        <v>337.33</v>
       </c>
       <c r="O7" t="n">
-        <v>0.98</v>
+        <v>0.82</v>
       </c>
       <c r="P7" t="n">
-        <v>7.6</v>
+        <v>7.57</v>
       </c>
       <c r="Q7" t="n">
-        <v>7.71</v>
+        <v>7.69</v>
       </c>
       <c r="R7" t="n">
-        <v>7.54</v>
+        <v>7.56</v>
       </c>
       <c r="S7" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
     </row>
@@ -938,59 +938,59 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>15.18</v>
+        <v>15.2</v>
       </c>
       <c r="D8" t="n">
-        <v>1.13</v>
+        <v>0.13</v>
       </c>
       <c r="E8" t="n">
-        <v>15.2</v>
+        <v>15.19</v>
       </c>
       <c r="F8" t="n">
-        <v>15.38</v>
+        <v>15.31</v>
       </c>
       <c r="G8" t="n">
-        <v>15.61</v>
+        <v>15.58</v>
       </c>
       <c r="H8" t="n">
-        <v>0.024</v>
+        <v>0.007</v>
       </c>
       <c r="I8" t="n">
-        <v>0.152</v>
+        <v>0.123</v>
       </c>
       <c r="J8" t="n">
-        <v>14.69</v>
+        <v>19.32</v>
       </c>
       <c r="K8" t="n">
-        <v>18.62</v>
+        <v>18.85</v>
       </c>
       <c r="L8" t="n">
-        <v>6.82</v>
+        <v>20.24</v>
       </c>
       <c r="M8" t="n">
-        <v>67.61</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>123.72</v>
+        <v>113.76</v>
       </c>
       <c r="O8" t="n">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="P8" t="n">
         <v>15.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>15.22</v>
+        <v>15.31</v>
       </c>
       <c r="R8" t="n">
-        <v>15.03</v>
+        <v>15.09</v>
       </c>
       <c r="S8" t="n">
-        <v>0.54</v>
+        <v>0.51</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
     </row>
@@ -1006,59 +1006,59 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>35.23</v>
+        <v>33.44</v>
       </c>
       <c r="D9" t="n">
-        <v>3.07</v>
+        <v>-5.08</v>
       </c>
       <c r="E9" t="n">
-        <v>34.56</v>
+        <v>34.52</v>
       </c>
       <c r="F9" t="n">
-        <v>35.15</v>
+        <v>34.68</v>
       </c>
       <c r="G9" t="n">
-        <v>37.09</v>
+        <v>36.99</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.073</v>
+        <v>-0.231</v>
       </c>
       <c r="I9" t="n">
-        <v>0.433</v>
+        <v>0.3</v>
       </c>
       <c r="J9" t="n">
-        <v>29.14</v>
+        <v>25.48</v>
       </c>
       <c r="K9" t="n">
-        <v>24.3</v>
+        <v>24.69</v>
       </c>
       <c r="L9" t="n">
-        <v>38.81</v>
+        <v>27.04</v>
       </c>
       <c r="M9" t="n">
-        <v>102.57</v>
+        <v>87.87</v>
       </c>
       <c r="N9" t="n">
-        <v>165.99</v>
+        <v>161.29</v>
       </c>
       <c r="O9" t="n">
-        <v>0.62</v>
+        <v>0.54</v>
       </c>
       <c r="P9" t="n">
-        <v>34.87</v>
+        <v>34.91</v>
       </c>
       <c r="Q9" t="n">
-        <v>35.86</v>
+        <v>35</v>
       </c>
       <c r="R9" t="n">
-        <v>34.78</v>
+        <v>33.35</v>
       </c>
       <c r="S9" t="n">
-        <v>8.949999999999999</v>
+        <v>7.67</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
     </row>
@@ -1074,59 +1074,59 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>220.31</v>
+        <v>213</v>
       </c>
       <c r="D10" t="n">
-        <v>4.78</v>
+        <v>-3.32</v>
       </c>
       <c r="E10" t="n">
-        <v>217.19</v>
+        <v>216.05</v>
       </c>
       <c r="F10" t="n">
-        <v>216.27</v>
+        <v>215.31</v>
       </c>
       <c r="G10" t="n">
-        <v>227.39</v>
+        <v>225.89</v>
       </c>
       <c r="H10" t="n">
-        <v>-8.385999999999999</v>
+        <v>-8.369999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>-8.058</v>
+        <v>-8.119999999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>47.17</v>
+        <v>44.79</v>
       </c>
       <c r="K10" t="n">
-        <v>37.61</v>
+        <v>40</v>
       </c>
       <c r="L10" t="n">
-        <v>66.29000000000001</v>
+        <v>54.38</v>
       </c>
       <c r="M10" t="n">
-        <v>19.68</v>
+        <v>13.01</v>
       </c>
       <c r="N10" t="n">
-        <v>18.65</v>
+        <v>18.23</v>
       </c>
       <c r="O10" t="n">
-        <v>1.06</v>
+        <v>0.71</v>
       </c>
       <c r="P10" t="n">
-        <v>217.1</v>
+        <v>219</v>
       </c>
       <c r="Q10" t="n">
-        <v>221.8</v>
+        <v>219.24</v>
       </c>
       <c r="R10" t="n">
-        <v>215</v>
+        <v>211.3</v>
       </c>
       <c r="S10" t="n">
-        <v>0.85</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
     </row>
@@ -1142,59 +1142,59 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>460.6</v>
+        <v>447.49</v>
       </c>
       <c r="D11" t="n">
-        <v>4.01</v>
+        <v>-2.85</v>
       </c>
       <c r="E11" t="n">
-        <v>453.25</v>
+        <v>451.34</v>
       </c>
       <c r="F11" t="n">
-        <v>458.83</v>
+        <v>459.54</v>
       </c>
       <c r="G11" t="n">
-        <v>428.62</v>
+        <v>430.93</v>
       </c>
       <c r="H11" t="n">
-        <v>15.807</v>
+        <v>14.745</v>
       </c>
       <c r="I11" t="n">
-        <v>13.068</v>
+        <v>13.404</v>
       </c>
       <c r="J11" t="n">
-        <v>50.88</v>
+        <v>41.36</v>
       </c>
       <c r="K11" t="n">
-        <v>61.2</v>
+        <v>54.59</v>
       </c>
       <c r="L11" t="n">
-        <v>30.24</v>
+        <v>14.91</v>
       </c>
       <c r="M11" t="n">
-        <v>31.26</v>
+        <v>21.81</v>
       </c>
       <c r="N11" t="n">
-        <v>43.36</v>
+        <v>40.97</v>
       </c>
       <c r="O11" t="n">
-        <v>0.72</v>
+        <v>0.53</v>
       </c>
       <c r="P11" t="n">
-        <v>461.53</v>
+        <v>453.11</v>
       </c>
       <c r="Q11" t="n">
-        <v>463</v>
+        <v>460.98</v>
       </c>
       <c r="R11" t="n">
-        <v>444</v>
+        <v>442.8</v>
       </c>
       <c r="S11" t="n">
-        <v>3.53</v>
+        <v>2.46</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
     </row>
@@ -1210,59 +1210,59 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>333.33</v>
+        <v>322.8</v>
       </c>
       <c r="D12" t="n">
-        <v>10.52</v>
+        <v>-3.16</v>
       </c>
       <c r="E12" t="n">
-        <v>318.87</v>
+        <v>318.43</v>
       </c>
       <c r="F12" t="n">
-        <v>312.96</v>
+        <v>314.44</v>
       </c>
       <c r="G12" t="n">
-        <v>315.96</v>
+        <v>315.36</v>
       </c>
       <c r="H12" t="n">
-        <v>4.191</v>
+        <v>4.454</v>
       </c>
       <c r="I12" t="n">
-        <v>5.097</v>
+        <v>4.968</v>
       </c>
       <c r="J12" t="n">
-        <v>60.42</v>
+        <v>62.48</v>
       </c>
       <c r="K12" t="n">
-        <v>54.26</v>
+        <v>57</v>
       </c>
       <c r="L12" t="n">
-        <v>72.75</v>
+        <v>73.44</v>
       </c>
       <c r="M12" t="n">
-        <v>42.2</v>
+        <v>28.19</v>
       </c>
       <c r="N12" t="n">
-        <v>34.57</v>
+        <v>34.34</v>
       </c>
       <c r="O12" t="n">
-        <v>1.22</v>
+        <v>0.82</v>
       </c>
       <c r="P12" t="n">
-        <v>316.67</v>
+        <v>329.11</v>
       </c>
       <c r="Q12" t="n">
-        <v>334.88</v>
+        <v>336.05</v>
       </c>
       <c r="R12" t="n">
-        <v>312.89</v>
+        <v>320</v>
       </c>
       <c r="S12" t="n">
-        <v>5.44</v>
+        <v>3.63</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
     </row>
@@ -1278,59 +1278,59 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>104.74</v>
+        <v>100.34</v>
       </c>
       <c r="D13" t="n">
-        <v>1.2</v>
+        <v>-4.2</v>
       </c>
       <c r="E13" t="n">
-        <v>106.01</v>
+        <v>105.01</v>
       </c>
       <c r="F13" t="n">
-        <v>110.72</v>
+        <v>108.75</v>
       </c>
       <c r="G13" t="n">
-        <v>114.76</v>
+        <v>114.45</v>
       </c>
       <c r="H13" t="n">
-        <v>3.26</v>
+        <v>2.301</v>
       </c>
       <c r="I13" t="n">
-        <v>6.139</v>
+        <v>5.371</v>
       </c>
       <c r="J13" t="n">
-        <v>14.57</v>
+        <v>10.56</v>
       </c>
       <c r="K13" t="n">
-        <v>19.85</v>
+        <v>16.75</v>
       </c>
       <c r="L13" t="n">
-        <v>4.02</v>
+        <v>-1.83</v>
       </c>
       <c r="M13" t="n">
-        <v>51.71</v>
+        <v>59.44</v>
       </c>
       <c r="N13" t="n">
-        <v>117.8</v>
+        <v>113.01</v>
       </c>
       <c r="O13" t="n">
-        <v>0.44</v>
+        <v>0.53</v>
       </c>
       <c r="P13" t="n">
-        <v>106.61</v>
+        <v>104.05</v>
       </c>
       <c r="Q13" t="n">
-        <v>106.8</v>
+        <v>105.4</v>
       </c>
       <c r="R13" t="n">
-        <v>103.19</v>
+        <v>99.87</v>
       </c>
       <c r="S13" t="n">
-        <v>5.14</v>
+        <v>5.91</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
     </row>
@@ -1346,59 +1346,59 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>255</v>
+        <v>246.99</v>
       </c>
       <c r="D14" t="n">
-        <v>7.1</v>
+        <v>-3.14</v>
       </c>
       <c r="E14" t="n">
-        <v>253.92</v>
+        <v>250.92</v>
       </c>
       <c r="F14" t="n">
-        <v>268.9</v>
+        <v>263.23</v>
       </c>
       <c r="G14" t="n">
-        <v>278.32</v>
+        <v>276.53</v>
       </c>
       <c r="H14" t="n">
-        <v>-9.513</v>
+        <v>-10.432</v>
       </c>
       <c r="I14" t="n">
-        <v>-4.969</v>
+        <v>-6.062</v>
       </c>
       <c r="J14" t="n">
-        <v>20.43</v>
+        <v>20.52</v>
       </c>
       <c r="K14" t="n">
-        <v>25.42</v>
+        <v>23.79</v>
       </c>
       <c r="L14" t="n">
-        <v>10.43</v>
+        <v>13.97</v>
       </c>
       <c r="M14" t="n">
-        <v>38.8</v>
+        <v>25.3</v>
       </c>
       <c r="N14" t="n">
-        <v>30.34</v>
+        <v>30.33</v>
       </c>
       <c r="O14" t="n">
-        <v>1.28</v>
+        <v>0.83</v>
       </c>
       <c r="P14" t="n">
-        <v>250</v>
+        <v>257.86</v>
       </c>
       <c r="Q14" t="n">
-        <v>256.1</v>
+        <v>259.8</v>
       </c>
       <c r="R14" t="n">
-        <v>243.7</v>
+        <v>245.6</v>
       </c>
       <c r="S14" t="n">
-        <v>5.81</v>
+        <v>3.79</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
     </row>
@@ -1414,59 +1414,59 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>215.6</v>
+        <v>210.82</v>
       </c>
       <c r="D15" t="n">
-        <v>1.7</v>
+        <v>-2.22</v>
       </c>
       <c r="E15" t="n">
-        <v>227.39</v>
+        <v>221.76</v>
       </c>
       <c r="F15" t="n">
-        <v>232.89</v>
+        <v>229.65</v>
       </c>
       <c r="G15" t="n">
-        <v>225.91</v>
+        <v>226.88</v>
       </c>
       <c r="H15" t="n">
-        <v>11.497</v>
+        <v>9.393000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>15.228</v>
+        <v>14.061</v>
       </c>
       <c r="J15" t="n">
-        <v>29</v>
+        <v>20.36</v>
       </c>
       <c r="K15" t="n">
-        <v>45.53</v>
+        <v>37.14</v>
       </c>
       <c r="L15" t="n">
-        <v>-4.05</v>
+        <v>-13.18</v>
       </c>
       <c r="M15" t="n">
-        <v>44.14</v>
+        <v>29.64</v>
       </c>
       <c r="N15" t="n">
-        <v>44.51</v>
+        <v>41.44</v>
       </c>
       <c r="O15" t="n">
-        <v>0.99</v>
+        <v>0.72</v>
       </c>
       <c r="P15" t="n">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="Q15" t="n">
-        <v>232.88</v>
+        <v>222.91</v>
       </c>
       <c r="R15" t="n">
-        <v>210.67</v>
+        <v>210.75</v>
       </c>
       <c r="S15" t="n">
-        <v>9.380000000000001</v>
+        <v>6.29</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
     </row>
@@ -1482,59 +1482,59 @@
         </is>
       </c>
       <c r="C16" t="n">
+        <v>42.21</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-2.18</v>
+      </c>
+      <c r="E16" t="n">
         <v>43.15</v>
       </c>
-      <c r="D16" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="E16" t="n">
-        <v>43.78</v>
-      </c>
       <c r="F16" t="n">
-        <v>47.09</v>
+        <v>45.69</v>
       </c>
       <c r="G16" t="n">
-        <v>44.8</v>
+        <v>45.12</v>
       </c>
       <c r="H16" t="n">
-        <v>2.002</v>
+        <v>1.626</v>
       </c>
       <c r="I16" t="n">
-        <v>3.032</v>
+        <v>2.751</v>
       </c>
       <c r="J16" t="n">
-        <v>14.88</v>
+        <v>12.78</v>
       </c>
       <c r="K16" t="n">
-        <v>27.37</v>
+        <v>22.51</v>
       </c>
       <c r="L16" t="n">
-        <v>-10.1</v>
+        <v>-6.68</v>
       </c>
       <c r="M16" t="n">
-        <v>28.68</v>
+        <v>21.57</v>
       </c>
       <c r="N16" t="n">
-        <v>32.2</v>
+        <v>31.9</v>
       </c>
       <c r="O16" t="n">
-        <v>0.89</v>
+        <v>0.68</v>
       </c>
       <c r="P16" t="n">
-        <v>45.27</v>
+        <v>44.52</v>
       </c>
       <c r="Q16" t="n">
-        <v>45.3</v>
+        <v>44.83</v>
       </c>
       <c r="R16" t="n">
-        <v>42.52</v>
+        <v>41.91</v>
       </c>
       <c r="S16" t="n">
-        <v>14.31</v>
+        <v>10.76</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
     </row>
@@ -1550,59 +1550,59 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>20.18</v>
+        <v>19.3</v>
       </c>
       <c r="D17" t="n">
-        <v>1.77</v>
+        <v>-4.36</v>
       </c>
       <c r="E17" t="n">
-        <v>20.65</v>
+        <v>20.26</v>
       </c>
       <c r="F17" t="n">
-        <v>22.18</v>
+        <v>21.47</v>
       </c>
       <c r="G17" t="n">
-        <v>21.25</v>
+        <v>21.31</v>
       </c>
       <c r="H17" t="n">
-        <v>0.334</v>
+        <v>0.154</v>
       </c>
       <c r="I17" t="n">
-        <v>0.661</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>11.51</v>
+        <v>8.4</v>
       </c>
       <c r="K17" t="n">
-        <v>23.53</v>
+        <v>18.49</v>
       </c>
       <c r="L17" t="n">
-        <v>-12.52</v>
+        <v>-11.76</v>
       </c>
       <c r="M17" t="n">
-        <v>31.12</v>
+        <v>33.04</v>
       </c>
       <c r="N17" t="n">
-        <v>41.6</v>
+        <v>42.45</v>
       </c>
       <c r="O17" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="P17" t="n">
-        <v>20.76</v>
+        <v>20.74</v>
       </c>
       <c r="Q17" t="n">
-        <v>21.12</v>
+        <v>20.79</v>
       </c>
       <c r="R17" t="n">
-        <v>20.07</v>
+        <v>19.2</v>
       </c>
       <c r="S17" t="n">
-        <v>8.44</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
     </row>
@@ -1618,59 +1618,59 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>16.18</v>
+        <v>15.47</v>
       </c>
       <c r="D18" t="n">
-        <v>1.57</v>
+        <v>-4.39</v>
       </c>
       <c r="E18" t="n">
-        <v>16.48</v>
+        <v>16.11</v>
       </c>
       <c r="F18" t="n">
-        <v>18.46</v>
+        <v>17.88</v>
       </c>
       <c r="G18" t="n">
-        <v>16.95</v>
+        <v>17.01</v>
       </c>
       <c r="H18" t="n">
-        <v>0.417</v>
+        <v>0.25</v>
       </c>
       <c r="I18" t="n">
-        <v>0.758</v>
+        <v>0.656</v>
       </c>
       <c r="J18" t="n">
-        <v>10.79</v>
+        <v>7.42</v>
       </c>
       <c r="K18" t="n">
-        <v>25.29</v>
+        <v>19.33</v>
       </c>
       <c r="L18" t="n">
-        <v>-18.2</v>
+        <v>-16.4</v>
       </c>
       <c r="M18" t="n">
-        <v>11.21</v>
+        <v>11.76</v>
       </c>
       <c r="N18" t="n">
-        <v>12.29</v>
+        <v>12.68</v>
       </c>
       <c r="O18" t="n">
-        <v>0.91</v>
+        <v>0.93</v>
       </c>
       <c r="P18" t="n">
-        <v>16.1</v>
+        <v>15.94</v>
       </c>
       <c r="Q18" t="n">
-        <v>16.2</v>
+        <v>15.99</v>
       </c>
       <c r="R18" t="n">
-        <v>15.86</v>
+        <v>15.4</v>
       </c>
       <c r="S18" t="n">
-        <v>6.19</v>
+        <v>6.49</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
     </row>
@@ -1686,59 +1686,59 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>38.77</v>
+        <v>36.46</v>
       </c>
       <c r="D19" t="n">
-        <v>1.15</v>
+        <v>-5.96</v>
       </c>
       <c r="E19" t="n">
-        <v>38.01</v>
+        <v>37.84</v>
       </c>
       <c r="F19" t="n">
-        <v>37.66</v>
+        <v>37.35</v>
       </c>
       <c r="G19" t="n">
-        <v>37.45</v>
+        <v>37.44</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.056</v>
+        <v>-0.158</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.268</v>
+        <v>-0.246</v>
       </c>
       <c r="J19" t="n">
-        <v>63.44</v>
+        <v>54.52</v>
       </c>
       <c r="K19" t="n">
-        <v>54.58</v>
+        <v>54.56</v>
       </c>
       <c r="L19" t="n">
-        <v>81.17</v>
+        <v>54.43</v>
       </c>
       <c r="M19" t="n">
-        <v>66.36</v>
+        <v>52.41</v>
       </c>
       <c r="N19" t="n">
-        <v>60.81</v>
+        <v>60.96</v>
       </c>
       <c r="O19" t="n">
-        <v>1.09</v>
+        <v>0.86</v>
       </c>
       <c r="P19" t="n">
-        <v>39.16</v>
+        <v>38.05</v>
       </c>
       <c r="Q19" t="n">
-        <v>39.57</v>
+        <v>38.1</v>
       </c>
       <c r="R19" t="n">
-        <v>38.29</v>
+        <v>36.31</v>
       </c>
       <c r="S19" t="n">
-        <v>9.24</v>
+        <v>7.3</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
     </row>
@@ -1754,59 +1754,59 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>17.73</v>
+        <v>16.55</v>
       </c>
       <c r="D20" t="n">
-        <v>4.91</v>
+        <v>-6.66</v>
       </c>
       <c r="E20" t="n">
-        <v>17.41</v>
+        <v>17.22</v>
       </c>
       <c r="F20" t="n">
+        <v>17.29</v>
+      </c>
+      <c r="G20" t="n">
+        <v>17.94</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-0.401</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-0.295</v>
+      </c>
+      <c r="J20" t="n">
+        <v>27.53</v>
+      </c>
+      <c r="K20" t="n">
+        <v>31.93</v>
+      </c>
+      <c r="L20" t="n">
+        <v>18.73</v>
+      </c>
+      <c r="M20" t="n">
+        <v>222.55</v>
+      </c>
+      <c r="N20" t="n">
+        <v>273.85</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="P20" t="n">
+        <v>17.46</v>
+      </c>
+      <c r="Q20" t="n">
         <v>17.5</v>
       </c>
-      <c r="G20" t="n">
-        <v>18.01</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-0.339</v>
-      </c>
-      <c r="I20" t="n">
-        <v>-0.268</v>
-      </c>
-      <c r="J20" t="n">
-        <v>37.27</v>
-      </c>
-      <c r="K20" t="n">
-        <v>34.13</v>
-      </c>
-      <c r="L20" t="n">
-        <v>43.55</v>
-      </c>
-      <c r="M20" t="n">
-        <v>250.46</v>
-      </c>
-      <c r="N20" t="n">
-        <v>276</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="P20" t="n">
-        <v>17.61</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>18.2</v>
-      </c>
       <c r="R20" t="n">
-        <v>17.33</v>
+        <v>16.32</v>
       </c>
       <c r="S20" t="n">
-        <v>10.86</v>
+        <v>9.65</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
     </row>
@@ -1822,59 +1822,59 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>51.2</v>
+        <v>47.79</v>
       </c>
       <c r="D21" t="n">
-        <v>4.49</v>
+        <v>-6.66</v>
       </c>
       <c r="E21" t="n">
-        <v>50.4</v>
+        <v>49.82</v>
       </c>
       <c r="F21" t="n">
-        <v>50.96</v>
+        <v>50.26</v>
       </c>
       <c r="G21" t="n">
-        <v>51.67</v>
+        <v>51.43</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.296</v>
+        <v>-1.454</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.253</v>
+        <v>-1.293</v>
       </c>
       <c r="J21" t="n">
-        <v>35.99</v>
+        <v>28.46</v>
       </c>
       <c r="K21" t="n">
-        <v>33.89</v>
+        <v>32.08</v>
       </c>
       <c r="L21" t="n">
-        <v>40.2</v>
+        <v>21.24</v>
       </c>
       <c r="M21" t="n">
-        <v>60.4</v>
+        <v>65.18000000000001</v>
       </c>
       <c r="N21" t="n">
-        <v>64.25</v>
+        <v>65.01000000000001</v>
       </c>
       <c r="O21" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="P21" t="n">
-        <v>50.85</v>
+        <v>50.51</v>
       </c>
       <c r="Q21" t="n">
-        <v>52.22</v>
+        <v>50.66</v>
       </c>
       <c r="R21" t="n">
-        <v>50.08</v>
+        <v>47.47</v>
       </c>
       <c r="S21" t="n">
-        <v>4.82</v>
+        <v>5.2</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
     </row>
@@ -1890,59 +1890,59 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>47.01</v>
+        <v>45.88</v>
       </c>
       <c r="D22" t="n">
-        <v>1.73</v>
+        <v>-2.4</v>
       </c>
       <c r="E22" t="n">
-        <v>46.59</v>
+        <v>46.45</v>
       </c>
       <c r="F22" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
       <c r="G22" t="n">
-        <v>49.88</v>
+        <v>49.56</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.248</v>
+        <v>-2.255</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.053</v>
+        <v>-2.093</v>
       </c>
       <c r="J22" t="n">
-        <v>20.27</v>
+        <v>18.78</v>
       </c>
       <c r="K22" t="n">
-        <v>16.84</v>
+        <v>17.49</v>
       </c>
       <c r="L22" t="n">
-        <v>27.14</v>
+        <v>21.38</v>
       </c>
       <c r="M22" t="n">
-        <v>27.4</v>
+        <v>25.13</v>
       </c>
       <c r="N22" t="n">
-        <v>33.46</v>
+        <v>32.91</v>
       </c>
       <c r="O22" t="n">
-        <v>0.82</v>
+        <v>0.76</v>
       </c>
       <c r="P22" t="n">
-        <v>47.25</v>
+        <v>46.71</v>
       </c>
       <c r="Q22" t="n">
-        <v>47.36</v>
+        <v>46.71</v>
       </c>
       <c r="R22" t="n">
-        <v>46.55</v>
+        <v>45.78</v>
       </c>
       <c r="S22" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
     </row>
@@ -1958,59 +1958,59 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>14.59</v>
+        <v>13.86</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.42</v>
+        <v>-5</v>
       </c>
       <c r="E23" t="n">
-        <v>14.42</v>
+        <v>14.38</v>
       </c>
       <c r="F23" t="n">
-        <v>14.35</v>
+        <v>14.24</v>
       </c>
       <c r="G23" t="n">
-        <v>15.16</v>
+        <v>15.02</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.051</v>
+        <v>-1.043</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.203</v>
+        <v>-1.171</v>
       </c>
       <c r="J23" t="n">
-        <v>50.48</v>
+        <v>40.47</v>
       </c>
       <c r="K23" t="n">
-        <v>36.63</v>
+        <v>37.91</v>
       </c>
       <c r="L23" t="n">
-        <v>78.18000000000001</v>
+        <v>45.6</v>
       </c>
       <c r="M23" t="n">
-        <v>391.04</v>
+        <v>292.66</v>
       </c>
       <c r="N23" t="n">
-        <v>265.24</v>
+        <v>266.47</v>
       </c>
       <c r="O23" t="n">
-        <v>1.47</v>
+        <v>1.1</v>
       </c>
       <c r="P23" t="n">
-        <v>15.15</v>
+        <v>14.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>15.23</v>
+        <v>14.4</v>
       </c>
       <c r="R23" t="n">
-        <v>14.33</v>
+        <v>13.77</v>
       </c>
       <c r="S23" t="n">
-        <v>11.24</v>
+        <v>8.41</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
     </row>
@@ -2026,59 +2026,59 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>59.43</v>
+        <v>57.59</v>
       </c>
       <c r="D24" t="n">
-        <v>1.73</v>
+        <v>-3.1</v>
       </c>
       <c r="E24" t="n">
-        <v>59.03</v>
+        <v>58.73</v>
       </c>
       <c r="F24" t="n">
-        <v>60.53</v>
+        <v>59.77</v>
       </c>
       <c r="G24" t="n">
-        <v>64.22</v>
+        <v>63.79</v>
       </c>
       <c r="H24" t="n">
-        <v>-3.05</v>
+        <v>-3.127</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.595</v>
+        <v>-2.702</v>
       </c>
       <c r="J24" t="n">
-        <v>18.42</v>
+        <v>15.34</v>
       </c>
       <c r="K24" t="n">
-        <v>14.57</v>
+        <v>14.83</v>
       </c>
       <c r="L24" t="n">
-        <v>26.11</v>
+        <v>16.36</v>
       </c>
       <c r="M24" t="n">
-        <v>8.300000000000001</v>
+        <v>8.84</v>
       </c>
       <c r="N24" t="n">
-        <v>12.59</v>
+        <v>12.52</v>
       </c>
       <c r="O24" t="n">
-        <v>0.66</v>
+        <v>0.71</v>
       </c>
       <c r="P24" t="n">
-        <v>59.92</v>
+        <v>59.1</v>
       </c>
       <c r="Q24" t="n">
-        <v>60</v>
+        <v>59.4</v>
       </c>
       <c r="R24" t="n">
-        <v>59.13</v>
+        <v>57.21</v>
       </c>
       <c r="S24" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
     </row>
@@ -2094,59 +2094,59 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>27.84</v>
+        <v>27.03</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.18</v>
+        <v>-2.91</v>
       </c>
       <c r="E25" t="n">
-        <v>28.1</v>
+        <v>27.87</v>
       </c>
       <c r="F25" t="n">
-        <v>27.91</v>
+        <v>27.58</v>
       </c>
       <c r="G25" t="n">
-        <v>29.94</v>
+        <v>29.71</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.714</v>
+        <v>-0.784</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.499</v>
+        <v>-0.556</v>
       </c>
       <c r="J25" t="n">
-        <v>46.57</v>
+        <v>45.86</v>
       </c>
       <c r="K25" t="n">
-        <v>39.77</v>
+        <v>41.8</v>
       </c>
       <c r="L25" t="n">
-        <v>60.17</v>
+        <v>53.98</v>
       </c>
       <c r="M25" t="n">
-        <v>200.34</v>
+        <v>123.74</v>
       </c>
       <c r="N25" t="n">
-        <v>240.91</v>
+        <v>231.52</v>
       </c>
       <c r="O25" t="n">
-        <v>0.83</v>
+        <v>0.53</v>
       </c>
       <c r="P25" t="n">
-        <v>28.46</v>
+        <v>27.79</v>
       </c>
       <c r="Q25" t="n">
-        <v>28.8</v>
+        <v>28.21</v>
       </c>
       <c r="R25" t="n">
-        <v>27.16</v>
+        <v>26.91</v>
       </c>
       <c r="S25" t="n">
-        <v>12.61</v>
+        <v>7.79</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
     </row>
@@ -2162,59 +2162,59 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>25.42</v>
+        <v>24.01</v>
       </c>
       <c r="D26" t="n">
-        <v>-3.35</v>
+        <v>-5.55</v>
       </c>
       <c r="E26" t="n">
-        <v>27</v>
+        <v>26.18</v>
       </c>
       <c r="F26" t="n">
-        <v>27.73</v>
+        <v>27.15</v>
       </c>
       <c r="G26" t="n">
-        <v>28.71</v>
+        <v>28.51</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.192</v>
+        <v>-0.469</v>
       </c>
       <c r="I26" t="n">
-        <v>0.321</v>
+        <v>0.163</v>
       </c>
       <c r="J26" t="n">
-        <v>10.83</v>
+        <v>7.93</v>
       </c>
       <c r="K26" t="n">
-        <v>16.13</v>
+        <v>13.4</v>
       </c>
       <c r="L26" t="n">
-        <v>0.23</v>
+        <v>-3.01</v>
       </c>
       <c r="M26" t="n">
-        <v>221.1</v>
+        <v>234.58</v>
       </c>
       <c r="N26" t="n">
-        <v>282.91</v>
+        <v>282.57</v>
       </c>
       <c r="O26" t="n">
-        <v>0.78</v>
+        <v>0.83</v>
       </c>
       <c r="P26" t="n">
-        <v>26.53</v>
+        <v>25.4</v>
       </c>
       <c r="Q26" t="n">
-        <v>26.61</v>
+        <v>25.69</v>
       </c>
       <c r="R26" t="n">
-        <v>25.05</v>
+        <v>23.9</v>
       </c>
       <c r="S26" t="n">
-        <v>6.57</v>
+        <v>6.97</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
     </row>
@@ -2230,59 +2230,59 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>153.33</v>
+        <v>150.5</v>
       </c>
       <c r="D27" t="n">
-        <v>3.58</v>
+        <v>-1.85</v>
       </c>
       <c r="E27" t="n">
-        <v>143.16</v>
+        <v>144.96</v>
       </c>
       <c r="F27" t="n">
-        <v>138.29</v>
+        <v>139.82</v>
       </c>
       <c r="G27" t="n">
-        <v>123.97</v>
+        <v>126.28</v>
       </c>
       <c r="H27" t="n">
-        <v>10.557</v>
+        <v>10.968</v>
       </c>
       <c r="I27" t="n">
-        <v>8.028</v>
+        <v>8.616</v>
       </c>
       <c r="J27" t="n">
-        <v>80.7</v>
+        <v>79.62</v>
       </c>
       <c r="K27" t="n">
-        <v>79.98</v>
+        <v>79.86</v>
       </c>
       <c r="L27" t="n">
-        <v>82.14</v>
+        <v>79.15000000000001</v>
       </c>
       <c r="M27" t="n">
-        <v>10.47</v>
+        <v>6.86</v>
       </c>
       <c r="N27" t="n">
-        <v>8.49</v>
+        <v>8.67</v>
       </c>
       <c r="O27" t="n">
-        <v>1.23</v>
+        <v>0.79</v>
       </c>
       <c r="P27" t="n">
-        <v>150.99</v>
+        <v>152.85</v>
       </c>
       <c r="Q27" t="n">
-        <v>159.88</v>
+        <v>158</v>
       </c>
       <c r="R27" t="n">
-        <v>147.72</v>
+        <v>149.36</v>
       </c>
       <c r="S27" t="n">
-        <v>11.86</v>
+        <v>7.77</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
     </row>
@@ -2298,59 +2298,59 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>34.15</v>
+        <v>33.12</v>
       </c>
       <c r="D28" t="n">
-        <v>4.37</v>
+        <v>-3.02</v>
       </c>
       <c r="E28" t="n">
-        <v>32.84</v>
+        <v>33.05</v>
       </c>
       <c r="F28" t="n">
-        <v>32.42</v>
+        <v>32.5</v>
       </c>
       <c r="G28" t="n">
-        <v>34.34</v>
+        <v>34.11</v>
       </c>
       <c r="H28" t="n">
-        <v>-1.249</v>
+        <v>-1.179</v>
       </c>
       <c r="I28" t="n">
-        <v>-1.29</v>
+        <v>-1.268</v>
       </c>
       <c r="J28" t="n">
-        <v>65.39</v>
+        <v>66.73999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>48.79</v>
+        <v>54.77</v>
       </c>
       <c r="L28" t="n">
-        <v>98.59</v>
+        <v>90.69</v>
       </c>
       <c r="M28" t="n">
-        <v>323.7</v>
+        <v>258.94</v>
       </c>
       <c r="N28" t="n">
-        <v>307.86</v>
+        <v>307.77</v>
       </c>
       <c r="O28" t="n">
-        <v>1.05</v>
+        <v>0.84</v>
       </c>
       <c r="P28" t="n">
-        <v>33.86</v>
+        <v>33.99</v>
       </c>
       <c r="Q28" t="n">
-        <v>34.58</v>
+        <v>33.99</v>
       </c>
       <c r="R28" t="n">
-        <v>33.62</v>
+        <v>32.7</v>
       </c>
       <c r="S28" t="n">
-        <v>1.57</v>
+        <v>1.26</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
     </row>
@@ -2366,59 +2366,59 @@
         </is>
       </c>
       <c r="C29" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="E29" t="n">
         <v>6.17</v>
       </c>
-      <c r="D29" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="E29" t="n">
+      <c r="F29" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="G29" t="n">
+        <v>6.59</v>
+      </c>
+      <c r="H29" t="n">
+        <v>-0.242</v>
+      </c>
+      <c r="I29" t="n">
+        <v>-0.213</v>
+      </c>
+      <c r="J29" t="n">
+        <v>48.2</v>
+      </c>
+      <c r="K29" t="n">
+        <v>37.77</v>
+      </c>
+      <c r="L29" t="n">
+        <v>69.05</v>
+      </c>
+      <c r="M29" t="n">
+        <v>231.29</v>
+      </c>
+      <c r="N29" t="n">
+        <v>284.97</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="P29" t="n">
+        <v>6.24</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="R29" t="n">
         <v>6.14</v>
       </c>
-      <c r="F29" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="G29" t="n">
-        <v>6.67</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-0.252</v>
-      </c>
-      <c r="I29" t="n">
-        <v>-0.206</v>
-      </c>
-      <c r="J29" t="n">
-        <v>44.52</v>
-      </c>
-      <c r="K29" t="n">
-        <v>32.56</v>
-      </c>
-      <c r="L29" t="n">
-        <v>68.44</v>
-      </c>
-      <c r="M29" t="n">
-        <v>223.03</v>
-      </c>
-      <c r="N29" t="n">
-        <v>294.9</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="P29" t="n">
-        <v>6.23</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>6.26</v>
-      </c>
-      <c r="R29" t="n">
-        <v>6.06</v>
-      </c>
       <c r="S29" t="n">
-        <v>1.94</v>
+        <v>2.01</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
     </row>
@@ -2434,59 +2434,59 @@
         </is>
       </c>
       <c r="C30" t="n">
+        <v>9.58</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="E30" t="n">
+        <v>9.52</v>
+      </c>
+      <c r="F30" t="n">
+        <v>9.43</v>
+      </c>
+      <c r="G30" t="n">
+        <v>9.279999999999999</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.171</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.151</v>
+      </c>
+      <c r="J30" t="n">
+        <v>79.95</v>
+      </c>
+      <c r="K30" t="n">
+        <v>82.18000000000001</v>
+      </c>
+      <c r="L30" t="n">
+        <v>75.48999999999999</v>
+      </c>
+      <c r="M30" t="n">
+        <v>86.42</v>
+      </c>
+      <c r="N30" t="n">
+        <v>100.82</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="P30" t="n">
         <v>9.449999999999999</v>
       </c>
-      <c r="D30" t="n">
-        <v>-2.07</v>
-      </c>
-      <c r="E30" t="n">
-        <v>9.49</v>
-      </c>
-      <c r="F30" t="n">
-        <v>9.41</v>
-      </c>
-      <c r="G30" t="n">
-        <v>9.25</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0.146</v>
-      </c>
-      <c r="J30" t="n">
-        <v>78.69</v>
-      </c>
-      <c r="K30" t="n">
-        <v>83.29000000000001</v>
-      </c>
-      <c r="L30" t="n">
-        <v>69.5</v>
-      </c>
-      <c r="M30" t="n">
-        <v>122.94</v>
-      </c>
-      <c r="N30" t="n">
-        <v>101.39</v>
-      </c>
-      <c r="O30" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="P30" t="n">
-        <v>9.58</v>
-      </c>
       <c r="Q30" t="n">
-        <v>9.67</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="R30" t="n">
-        <v>9.43</v>
+        <v>9.42</v>
       </c>
       <c r="S30" t="n">
-        <v>1.28</v>
+        <v>0.9</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
     </row>
@@ -2502,59 +2502,59 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>5.89</v>
+        <v>5.7</v>
       </c>
       <c r="D31" t="n">
-        <v>1.2</v>
+        <v>-3.23</v>
       </c>
       <c r="E31" t="n">
-        <v>5.86</v>
+        <v>5.83</v>
       </c>
       <c r="F31" t="n">
-        <v>5.96</v>
+        <v>5.91</v>
       </c>
       <c r="G31" t="n">
-        <v>6.2</v>
+        <v>6.16</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.215</v>
+        <v>-0.225</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.184</v>
+        <v>-0.192</v>
       </c>
       <c r="J31" t="n">
-        <v>13.84</v>
+        <v>10.78</v>
       </c>
       <c r="K31" t="n">
-        <v>11.44</v>
+        <v>11.22</v>
       </c>
       <c r="L31" t="n">
-        <v>18.64</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="M31" t="n">
-        <v>69.5</v>
+        <v>125.86</v>
       </c>
       <c r="N31" t="n">
-        <v>114.64</v>
+        <v>115.6</v>
       </c>
       <c r="O31" t="n">
-        <v>0.61</v>
+        <v>1.09</v>
       </c>
       <c r="P31" t="n">
-        <v>5.88</v>
+        <v>5.87</v>
       </c>
       <c r="Q31" t="n">
-        <v>5.91</v>
+        <v>5.87</v>
       </c>
       <c r="R31" t="n">
-        <v>5.83</v>
+        <v>5.68</v>
       </c>
       <c r="S31" t="n">
-        <v>0.58</v>
+        <v>1.05</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
     </row>
@@ -2570,59 +2570,59 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>93.84999999999999</v>
+        <v>93.28</v>
       </c>
       <c r="D32" t="n">
-        <v>0.06</v>
+        <v>-0.61</v>
       </c>
       <c r="E32" t="n">
-        <v>93.67</v>
+        <v>93.55</v>
       </c>
       <c r="F32" t="n">
-        <v>94.42</v>
+        <v>93.89</v>
       </c>
       <c r="G32" t="n">
-        <v>95.51000000000001</v>
+        <v>95.39</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.29</v>
+        <v>-0.365</v>
       </c>
       <c r="I32" t="n">
-        <v>0.105</v>
+        <v>0.011</v>
       </c>
       <c r="J32" t="n">
-        <v>21.15</v>
+        <v>23.89</v>
       </c>
       <c r="K32" t="n">
-        <v>23.06</v>
+        <v>23.34</v>
       </c>
       <c r="L32" t="n">
-        <v>17.33</v>
+        <v>25</v>
       </c>
       <c r="M32" t="n">
-        <v>7.48</v>
+        <v>6.1</v>
       </c>
       <c r="N32" t="n">
-        <v>10.6</v>
+        <v>10.32</v>
       </c>
       <c r="O32" t="n">
-        <v>0.71</v>
+        <v>0.59</v>
       </c>
       <c r="P32" t="n">
-        <v>94.15000000000001</v>
+        <v>93.83</v>
       </c>
       <c r="Q32" t="n">
-        <v>94.31999999999999</v>
+        <v>93.83</v>
       </c>
       <c r="R32" t="n">
-        <v>93.58</v>
+        <v>93</v>
       </c>
       <c r="S32" t="n">
-        <v>0.83</v>
+        <v>0.68</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
     </row>
@@ -2638,59 +2638,59 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>38.09</v>
+        <v>38.14</v>
       </c>
       <c r="D33" t="n">
         <v>0.13</v>
       </c>
       <c r="E33" t="n">
-        <v>37.33</v>
+        <v>37.62</v>
       </c>
       <c r="F33" t="n">
-        <v>36.74</v>
+        <v>36.9</v>
       </c>
       <c r="G33" t="n">
-        <v>37.03</v>
+        <v>37.1</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.042</v>
+        <v>0.042</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.201</v>
+        <v>-0.153</v>
       </c>
       <c r="J33" t="n">
-        <v>71.3</v>
+        <v>75.98</v>
       </c>
       <c r="K33" t="n">
-        <v>57.84</v>
+        <v>63.89</v>
       </c>
       <c r="L33" t="n">
-        <v>98.23</v>
+        <v>100.18</v>
       </c>
       <c r="M33" t="n">
-        <v>25.91</v>
+        <v>25.93</v>
       </c>
       <c r="N33" t="n">
-        <v>23.07</v>
+        <v>23.31</v>
       </c>
       <c r="O33" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="P33" t="n">
-        <v>38.42</v>
+        <v>38.11</v>
       </c>
       <c r="Q33" t="n">
-        <v>38.66</v>
+        <v>38.35</v>
       </c>
       <c r="R33" t="n">
-        <v>37.92</v>
+        <v>37.75</v>
       </c>
       <c r="S33" t="n">
         <v>0.54</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
     </row>
@@ -2706,59 +2706,59 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>13.68</v>
+        <v>13.26</v>
       </c>
       <c r="D34" t="n">
-        <v>9.970000000000001</v>
+        <v>-3.07</v>
       </c>
       <c r="E34" t="n">
-        <v>13.57</v>
+        <v>13.33</v>
       </c>
       <c r="F34" t="n">
-        <v>14.07</v>
+        <v>14</v>
       </c>
       <c r="G34" t="n">
-        <v>12.92</v>
+        <v>13.08</v>
       </c>
       <c r="H34" t="n">
-        <v>0.83</v>
+        <v>0.751</v>
       </c>
       <c r="I34" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.904</v>
       </c>
       <c r="J34" t="n">
-        <v>36.89</v>
+        <v>32.48</v>
       </c>
       <c r="K34" t="n">
-        <v>50.87</v>
+        <v>44.74</v>
       </c>
       <c r="L34" t="n">
-        <v>8.92</v>
+        <v>7.97</v>
       </c>
       <c r="M34" t="n">
-        <v>85.15000000000001</v>
+        <v>91.23</v>
       </c>
       <c r="N34" t="n">
-        <v>79.43000000000001</v>
+        <v>83.38</v>
       </c>
       <c r="O34" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="P34" t="n">
-        <v>13.06</v>
+        <v>13.78</v>
       </c>
       <c r="Q34" t="n">
-        <v>13.68</v>
+        <v>14.55</v>
       </c>
       <c r="R34" t="n">
-        <v>13.06</v>
+        <v>13.24</v>
       </c>
       <c r="S34" t="n">
-        <v>20.04</v>
+        <v>21.47</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
     </row>
@@ -2774,59 +2774,59 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>19.33</v>
+        <v>19.59</v>
       </c>
       <c r="D35" t="n">
-        <v>10.02</v>
+        <v>1.35</v>
       </c>
       <c r="E35" t="n">
-        <v>18.23</v>
+        <v>18.53</v>
       </c>
       <c r="F35" t="n">
-        <v>17.99</v>
+        <v>18.1</v>
       </c>
       <c r="G35" t="n">
-        <v>18.97</v>
+        <v>18.95</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.429</v>
+        <v>-0.307</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.383</v>
+        <v>-0.368</v>
       </c>
       <c r="J35" t="n">
-        <v>59.65</v>
+        <v>67.19</v>
       </c>
       <c r="K35" t="n">
-        <v>41.33</v>
+        <v>49.95</v>
       </c>
       <c r="L35" t="n">
-        <v>96.3</v>
+        <v>101.66</v>
       </c>
       <c r="M35" t="n">
-        <v>70.78</v>
+        <v>105.65</v>
       </c>
       <c r="N35" t="n">
-        <v>49.91</v>
+        <v>52.35</v>
       </c>
       <c r="O35" t="n">
-        <v>1.42</v>
+        <v>2.02</v>
       </c>
       <c r="P35" t="n">
-        <v>17.95</v>
+        <v>19.93</v>
       </c>
       <c r="Q35" t="n">
-        <v>19.33</v>
+        <v>20.22</v>
       </c>
       <c r="R35" t="n">
-        <v>17.8</v>
+        <v>19.38</v>
       </c>
       <c r="S35" t="n">
-        <v>3.87</v>
+        <v>5.78</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
     </row>
@@ -2842,59 +2842,59 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>34.69</v>
+        <v>34.05</v>
       </c>
       <c r="D36" t="n">
-        <v>9.99</v>
+        <v>-1.84</v>
       </c>
       <c r="E36" t="n">
-        <v>32.33</v>
+        <v>32.77</v>
       </c>
       <c r="F36" t="n">
-        <v>32.17</v>
+        <v>32.29</v>
       </c>
       <c r="G36" t="n">
-        <v>33.78</v>
+        <v>33.71</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.653</v>
+        <v>-1.448</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.884</v>
+        <v>-1.797</v>
       </c>
       <c r="J36" t="n">
-        <v>46.81</v>
+        <v>55.47</v>
       </c>
       <c r="K36" t="n">
-        <v>28.71</v>
+        <v>37.63</v>
       </c>
       <c r="L36" t="n">
-        <v>83.02</v>
+        <v>91.15000000000001</v>
       </c>
       <c r="M36" t="n">
-        <v>55.96</v>
+        <v>61.66</v>
       </c>
       <c r="N36" t="n">
-        <v>41.17</v>
+        <v>42.19</v>
       </c>
       <c r="O36" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="P36" t="n">
-        <v>32.3</v>
+        <v>35.02</v>
       </c>
       <c r="Q36" t="n">
-        <v>34.69</v>
+        <v>35.28</v>
       </c>
       <c r="R36" t="n">
-        <v>31.95</v>
+        <v>33.51</v>
       </c>
       <c r="S36" t="n">
-        <v>2.94</v>
+        <v>3.24</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
     </row>
@@ -2910,59 +2910,59 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>46.62</v>
+        <v>47.69</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.28</v>
+        <v>2.3</v>
       </c>
       <c r="E37" t="n">
         <v>47.28</v>
       </c>
       <c r="F37" t="n">
-        <v>48.06</v>
+        <v>47.88</v>
       </c>
       <c r="G37" t="n">
-        <v>47.81</v>
+        <v>47.9</v>
       </c>
       <c r="H37" t="n">
-        <v>0.892</v>
+        <v>0.841</v>
       </c>
       <c r="I37" t="n">
-        <v>1.335</v>
+        <v>1.236</v>
       </c>
       <c r="J37" t="n">
-        <v>22.35</v>
+        <v>28.35</v>
       </c>
       <c r="K37" t="n">
-        <v>33.92</v>
+        <v>32.06</v>
       </c>
       <c r="L37" t="n">
-        <v>-0.78</v>
+        <v>20.93</v>
       </c>
       <c r="M37" t="n">
-        <v>33.59</v>
+        <v>32.24</v>
       </c>
       <c r="N37" t="n">
-        <v>44.81</v>
+        <v>43.86</v>
       </c>
       <c r="O37" t="n">
-        <v>0.75</v>
+        <v>0.74</v>
       </c>
       <c r="P37" t="n">
-        <v>46.33</v>
+        <v>46.68</v>
       </c>
       <c r="Q37" t="n">
-        <v>47.48</v>
+        <v>47.9</v>
       </c>
       <c r="R37" t="n">
-        <v>45.87</v>
+        <v>46.68</v>
       </c>
       <c r="S37" t="n">
         <v>0.2</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
     </row>
@@ -2978,59 +2978,59 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>4.84</v>
+        <v>4.72</v>
       </c>
       <c r="D38" t="n">
-        <v>2.33</v>
+        <v>-2.48</v>
       </c>
       <c r="E38" t="n">
-        <v>4.8</v>
+        <v>4.81</v>
       </c>
       <c r="F38" t="n">
-        <v>4.79</v>
+        <v>4.76</v>
       </c>
       <c r="G38" t="n">
-        <v>5.28</v>
+        <v>5.21</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.302</v>
+        <v>-0.299</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.27</v>
+        <v>-0.276</v>
       </c>
       <c r="J38" t="n">
-        <v>38.6</v>
+        <v>42.4</v>
       </c>
       <c r="K38" t="n">
-        <v>27.46</v>
+        <v>32.44</v>
       </c>
       <c r="L38" t="n">
-        <v>60.89</v>
+        <v>62.33</v>
       </c>
       <c r="M38" t="n">
-        <v>29.31</v>
+        <v>22.88</v>
       </c>
       <c r="N38" t="n">
-        <v>45.08</v>
+        <v>43.42</v>
       </c>
       <c r="O38" t="n">
-        <v>0.65</v>
+        <v>0.53</v>
       </c>
       <c r="P38" t="n">
-        <v>4.8</v>
+        <v>4.83</v>
       </c>
       <c r="Q38" t="n">
         <v>4.92</v>
       </c>
       <c r="R38" t="n">
-        <v>4.78</v>
+        <v>4.67</v>
       </c>
       <c r="S38" t="n">
-        <v>1.67</v>
+        <v>1.3</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
     </row>
@@ -3046,59 +3046,59 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>32.87</v>
+        <v>31.75</v>
       </c>
       <c r="D39" t="n">
-        <v>0.67</v>
+        <v>-3.41</v>
       </c>
       <c r="E39" t="n">
-        <v>33.44</v>
+        <v>32.88</v>
       </c>
       <c r="F39" t="n">
-        <v>34.14</v>
+        <v>33.89</v>
       </c>
       <c r="G39" t="n">
-        <v>35.83</v>
+        <v>35.73</v>
       </c>
       <c r="H39" t="n">
-        <v>0.013</v>
+        <v>-0.187</v>
       </c>
       <c r="I39" t="n">
-        <v>0.618</v>
+        <v>0.457</v>
       </c>
       <c r="J39" t="n">
-        <v>16.63</v>
+        <v>12.46</v>
       </c>
       <c r="K39" t="n">
-        <v>20.51</v>
+        <v>17.82</v>
       </c>
       <c r="L39" t="n">
-        <v>8.869999999999999</v>
+        <v>1.73</v>
       </c>
       <c r="M39" t="n">
-        <v>29.59</v>
+        <v>28.68</v>
       </c>
       <c r="N39" t="n">
-        <v>57.46</v>
+        <v>56.79</v>
       </c>
       <c r="O39" t="n">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
       <c r="P39" t="n">
-        <v>33.3</v>
+        <v>32.8</v>
       </c>
       <c r="Q39" t="n">
-        <v>33.4</v>
+        <v>33.05</v>
       </c>
       <c r="R39" t="n">
-        <v>32.32</v>
+        <v>31.56</v>
       </c>
       <c r="S39" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
     </row>

--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -530,59 +530,59 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>103.49</v>
+        <v>102.6</v>
       </c>
       <c r="D2" t="n">
-        <v>-1.44</v>
+        <v>-1.53</v>
       </c>
       <c r="E2" t="n">
-        <v>103.92</v>
+        <v>103.68</v>
       </c>
       <c r="F2" t="n">
-        <v>102.76</v>
+        <v>103.34</v>
       </c>
       <c r="G2" t="n">
-        <v>102.83</v>
+        <v>103.03</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.165</v>
+        <v>-0.08</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.532</v>
+        <v>-0.257</v>
       </c>
       <c r="J2" t="n">
-        <v>64.8</v>
+        <v>55.75</v>
       </c>
       <c r="K2" t="n">
-        <v>57.21</v>
+        <v>58.48</v>
       </c>
       <c r="L2" t="n">
-        <v>79.98</v>
+        <v>50.29</v>
       </c>
       <c r="M2" t="n">
-        <v>8.31</v>
+        <v>9.85</v>
       </c>
       <c r="N2" t="n">
-        <v>13.37</v>
+        <v>12.77</v>
       </c>
       <c r="O2" t="n">
-        <v>0.62</v>
+        <v>0.77</v>
       </c>
       <c r="P2" t="n">
-        <v>104.97</v>
+        <v>103.38</v>
       </c>
       <c r="Q2" t="n">
-        <v>104.97</v>
+        <v>103.69</v>
       </c>
       <c r="R2" t="n">
-        <v>103.29</v>
+        <v>102.5</v>
       </c>
       <c r="S2" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-09</t>
         </is>
       </c>
     </row>
@@ -598,59 +598,59 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>386.46</v>
+        <v>389.99</v>
       </c>
       <c r="D3" t="n">
-        <v>-3.67</v>
+        <v>-0.33</v>
       </c>
       <c r="E3" t="n">
-        <v>401.61</v>
+        <v>390.7</v>
       </c>
       <c r="F3" t="n">
-        <v>402.35</v>
+        <v>399.26</v>
       </c>
       <c r="G3" t="n">
-        <v>398.78</v>
+        <v>400.54</v>
       </c>
       <c r="H3" t="n">
-        <v>8.877000000000001</v>
+        <v>4.838</v>
       </c>
       <c r="I3" t="n">
-        <v>11.287</v>
+        <v>8.253</v>
       </c>
       <c r="J3" t="n">
-        <v>35.13</v>
+        <v>25.06</v>
       </c>
       <c r="K3" t="n">
-        <v>48.28</v>
+        <v>32.36</v>
       </c>
       <c r="L3" t="n">
-        <v>8.83</v>
+        <v>10.45</v>
       </c>
       <c r="M3" t="n">
-        <v>24.75</v>
+        <v>25.96</v>
       </c>
       <c r="N3" t="n">
-        <v>33.65</v>
+        <v>30.63</v>
       </c>
       <c r="O3" t="n">
-        <v>0.74</v>
+        <v>0.85</v>
       </c>
       <c r="P3" t="n">
-        <v>400</v>
+        <v>394.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>400.8</v>
+        <v>394.28</v>
       </c>
       <c r="R3" t="n">
-        <v>385.13</v>
+        <v>386.66</v>
       </c>
       <c r="S3" t="n">
-        <v>0.58</v>
+        <v>0.61</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-09</t>
         </is>
       </c>
     </row>
@@ -666,59 +666,59 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>23.98</v>
+        <v>24.15</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.62</v>
+        <v>-2.23</v>
       </c>
       <c r="E4" t="n">
-        <v>24.15</v>
+        <v>24.18</v>
       </c>
       <c r="F4" t="n">
-        <v>24.25</v>
+        <v>24.19</v>
       </c>
       <c r="G4" t="n">
-        <v>25.03</v>
+        <v>24.76</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.738</v>
+        <v>-0.653</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.711</v>
+        <v>-0.717</v>
       </c>
       <c r="J4" t="n">
-        <v>16.51</v>
+        <v>40.28</v>
       </c>
       <c r="K4" t="n">
-        <v>16.24</v>
+        <v>29.76</v>
       </c>
       <c r="L4" t="n">
-        <v>17.05</v>
+        <v>61.32</v>
       </c>
       <c r="M4" t="n">
-        <v>71.02</v>
+        <v>98.73999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>110.95</v>
+        <v>111.79</v>
       </c>
       <c r="O4" t="n">
-        <v>0.64</v>
+        <v>0.88</v>
       </c>
       <c r="P4" t="n">
-        <v>24.22</v>
+        <v>24.48</v>
       </c>
       <c r="Q4" t="n">
-        <v>24.26</v>
+        <v>24.48</v>
       </c>
       <c r="R4" t="n">
-        <v>23.95</v>
+        <v>24.1</v>
       </c>
       <c r="S4" t="n">
-        <v>0.58</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-09</t>
         </is>
       </c>
     </row>
@@ -734,59 +734,59 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>76.84999999999999</v>
+        <v>79.13</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.84</v>
+        <v>-2.08</v>
       </c>
       <c r="E5" t="n">
-        <v>79.61</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>79.03</v>
+        <v>78.98</v>
       </c>
       <c r="G5" t="n">
-        <v>83.28</v>
+        <v>81.06</v>
       </c>
       <c r="H5" t="n">
-        <v>-3.171</v>
+        <v>-2.899</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.903</v>
+        <v>-3.039</v>
       </c>
       <c r="J5" t="n">
-        <v>26.63</v>
+        <v>35.35</v>
       </c>
       <c r="K5" t="n">
-        <v>30.54</v>
+        <v>30.99</v>
       </c>
       <c r="L5" t="n">
-        <v>18.79</v>
+        <v>44.09</v>
       </c>
       <c r="M5" t="n">
-        <v>28.09</v>
+        <v>27.72</v>
       </c>
       <c r="N5" t="n">
-        <v>35.14</v>
+        <v>33.8</v>
       </c>
       <c r="O5" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="P5" t="n">
-        <v>79.40000000000001</v>
+        <v>79.20999999999999</v>
       </c>
       <c r="Q5" t="n">
-        <v>80.28</v>
+        <v>80.33</v>
       </c>
       <c r="R5" t="n">
-        <v>76.8</v>
+        <v>77.84</v>
       </c>
       <c r="S5" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-09</t>
         </is>
       </c>
     </row>
@@ -802,59 +802,59 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>606.52</v>
+        <v>693.02</v>
       </c>
       <c r="D6" t="n">
-        <v>4.21</v>
+        <v>0.71</v>
       </c>
       <c r="E6" t="n">
-        <v>589.78</v>
+        <v>637.84</v>
       </c>
       <c r="F6" t="n">
-        <v>599.23</v>
+        <v>616.1799999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>578.4299999999999</v>
+        <v>597.08</v>
       </c>
       <c r="H6" t="n">
-        <v>9.337999999999999</v>
+        <v>22.225</v>
       </c>
       <c r="I6" t="n">
-        <v>8.286</v>
+        <v>12.057</v>
       </c>
       <c r="J6" t="n">
-        <v>46.93</v>
+        <v>78.45999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>49.94</v>
+        <v>64.7</v>
       </c>
       <c r="L6" t="n">
-        <v>40.9</v>
+        <v>105.97</v>
       </c>
       <c r="M6" t="n">
-        <v>29.03</v>
+        <v>24.96</v>
       </c>
       <c r="N6" t="n">
-        <v>28.94</v>
+        <v>29.18</v>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="P6" t="n">
-        <v>600</v>
+        <v>682</v>
       </c>
       <c r="Q6" t="n">
-        <v>625</v>
+        <v>700</v>
       </c>
       <c r="R6" t="n">
-        <v>594.35</v>
+        <v>678.01</v>
       </c>
       <c r="S6" t="n">
-        <v>2.63</v>
+        <v>2.26</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-09</t>
         </is>
       </c>
     </row>
@@ -870,59 +870,59 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7.5</v>
+        <v>7.33</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.7</v>
+        <v>0.14</v>
       </c>
       <c r="E7" t="n">
-        <v>7.58</v>
+        <v>7.44</v>
       </c>
       <c r="F7" t="n">
-        <v>7.46</v>
+        <v>7.48</v>
       </c>
       <c r="G7" t="n">
-        <v>7.37</v>
+        <v>7.41</v>
       </c>
       <c r="H7" t="n">
-        <v>0.099</v>
+        <v>0.047</v>
       </c>
       <c r="I7" t="n">
-        <v>0.076</v>
+        <v>0.06</v>
       </c>
       <c r="J7" t="n">
-        <v>71.78</v>
+        <v>40.98</v>
       </c>
       <c r="K7" t="n">
-        <v>71.98999999999999</v>
+        <v>54.9</v>
       </c>
       <c r="L7" t="n">
-        <v>71.34</v>
+        <v>13.13</v>
       </c>
       <c r="M7" t="n">
-        <v>245.3</v>
+        <v>253.05</v>
       </c>
       <c r="N7" t="n">
-        <v>338.78</v>
+        <v>344.02</v>
       </c>
       <c r="O7" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="P7" t="n">
-        <v>7.62</v>
+        <v>7.32</v>
       </c>
       <c r="Q7" t="n">
-        <v>7.64</v>
+        <v>7.35</v>
       </c>
       <c r="R7" t="n">
-        <v>7.48</v>
+        <v>7.26</v>
       </c>
       <c r="S7" t="n">
         <v>0.09</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-09</t>
         </is>
       </c>
     </row>
@@ -938,59 +938,59 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>15.04</v>
+        <v>15.2</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.05</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>15.16</v>
+        <v>15.15</v>
       </c>
       <c r="F8" t="n">
-        <v>15.23</v>
+        <v>15.17</v>
       </c>
       <c r="G8" t="n">
-        <v>15.55</v>
+        <v>15.49</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.018</v>
+        <v>-0.059</v>
       </c>
       <c r="I8" t="n">
-        <v>0.095</v>
+        <v>0.001</v>
       </c>
       <c r="J8" t="n">
-        <v>17.16</v>
+        <v>35.48</v>
       </c>
       <c r="K8" t="n">
-        <v>18.29</v>
+        <v>26.93</v>
       </c>
       <c r="L8" t="n">
-        <v>14.91</v>
+        <v>52.6</v>
       </c>
       <c r="M8" t="n">
-        <v>66.29000000000001</v>
+        <v>57.73</v>
       </c>
       <c r="N8" t="n">
-        <v>109.63</v>
+        <v>97.31999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="P8" t="n">
-        <v>15.21</v>
+        <v>15.15</v>
       </c>
       <c r="Q8" t="n">
-        <v>15.25</v>
+        <v>15.22</v>
       </c>
       <c r="R8" t="n">
-        <v>14.95</v>
+        <v>15.08</v>
       </c>
       <c r="S8" t="n">
-        <v>0.53</v>
+        <v>0.46</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-09</t>
         </is>
       </c>
     </row>
@@ -1006,59 +1006,59 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>33.57</v>
+        <v>35.88</v>
       </c>
       <c r="D9" t="n">
-        <v>0.39</v>
+        <v>-0.88</v>
       </c>
       <c r="E9" t="n">
-        <v>34.29</v>
+        <v>34.58</v>
       </c>
       <c r="F9" t="n">
-        <v>34.48</v>
+        <v>34.57</v>
       </c>
       <c r="G9" t="n">
-        <v>36.72</v>
+        <v>35.72</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.342</v>
+        <v>-0.248</v>
       </c>
       <c r="I9" t="n">
-        <v>0.172</v>
+        <v>-0.151</v>
       </c>
       <c r="J9" t="n">
-        <v>24.28</v>
+        <v>61.09</v>
       </c>
       <c r="K9" t="n">
-        <v>24.56</v>
+        <v>42.48</v>
       </c>
       <c r="L9" t="n">
-        <v>23.74</v>
+        <v>98.31</v>
       </c>
       <c r="M9" t="n">
-        <v>65.97</v>
+        <v>92.06</v>
       </c>
       <c r="N9" t="n">
-        <v>154.38</v>
+        <v>122.49</v>
       </c>
       <c r="O9" t="n">
-        <v>0.43</v>
+        <v>0.75</v>
       </c>
       <c r="P9" t="n">
-        <v>33.92</v>
+        <v>35.61</v>
       </c>
       <c r="Q9" t="n">
-        <v>34.31</v>
+        <v>36.46</v>
       </c>
       <c r="R9" t="n">
-        <v>33.22</v>
+        <v>35.61</v>
       </c>
       <c r="S9" t="n">
-        <v>5.76</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-09</t>
         </is>
       </c>
     </row>
@@ -1074,59 +1074,59 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>213.77</v>
+        <v>227</v>
       </c>
       <c r="D10" t="n">
-        <v>0.36</v>
+        <v>-0.66</v>
       </c>
       <c r="E10" t="n">
-        <v>214.61</v>
+        <v>219.96</v>
       </c>
       <c r="F10" t="n">
-        <v>215.04</v>
+        <v>218.58</v>
       </c>
       <c r="G10" t="n">
-        <v>224.49</v>
+        <v>221.63</v>
       </c>
       <c r="H10" t="n">
-        <v>-8.201000000000001</v>
+        <v>-5.211</v>
       </c>
       <c r="I10" t="n">
-        <v>-8.135999999999999</v>
+        <v>-7.103</v>
       </c>
       <c r="J10" t="n">
-        <v>44.24</v>
+        <v>63.95</v>
       </c>
       <c r="K10" t="n">
-        <v>41.41</v>
+        <v>52.72</v>
       </c>
       <c r="L10" t="n">
-        <v>49.89</v>
+        <v>86.42</v>
       </c>
       <c r="M10" t="n">
-        <v>11.71</v>
+        <v>19.64</v>
       </c>
       <c r="N10" t="n">
-        <v>18.09</v>
+        <v>18.43</v>
       </c>
       <c r="O10" t="n">
-        <v>0.65</v>
+        <v>1.07</v>
       </c>
       <c r="P10" t="n">
-        <v>214.07</v>
+        <v>225</v>
       </c>
       <c r="Q10" t="n">
-        <v>218.17</v>
+        <v>230.36</v>
       </c>
       <c r="R10" t="n">
-        <v>213.22</v>
+        <v>223.66</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5</v>
+        <v>0.84</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-09</t>
         </is>
       </c>
     </row>
@@ -1142,59 +1142,59 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>455.3</v>
+        <v>490</v>
       </c>
       <c r="D11" t="n">
-        <v>1.75</v>
+        <v>-2.29</v>
       </c>
       <c r="E11" t="n">
-        <v>452.92</v>
+        <v>470.6</v>
       </c>
       <c r="F11" t="n">
-        <v>457.37</v>
+        <v>461.92</v>
       </c>
       <c r="G11" t="n">
-        <v>433.6</v>
+        <v>447.38</v>
       </c>
       <c r="H11" t="n">
-        <v>14.367</v>
+        <v>19.834</v>
       </c>
       <c r="I11" t="n">
-        <v>13.596</v>
+        <v>17.004</v>
       </c>
       <c r="J11" t="n">
-        <v>39.56</v>
+        <v>67.37</v>
       </c>
       <c r="K11" t="n">
-        <v>49.58</v>
+        <v>56.45</v>
       </c>
       <c r="L11" t="n">
-        <v>19.52</v>
+        <v>89.22</v>
       </c>
       <c r="M11" t="n">
-        <v>33.64</v>
+        <v>29.84</v>
       </c>
       <c r="N11" t="n">
-        <v>40.63</v>
+        <v>39.86</v>
       </c>
       <c r="O11" t="n">
-        <v>0.83</v>
+        <v>0.75</v>
       </c>
       <c r="P11" t="n">
-        <v>457</v>
+        <v>491.3</v>
       </c>
       <c r="Q11" t="n">
-        <v>469</v>
+        <v>497.8</v>
       </c>
       <c r="R11" t="n">
-        <v>454.05</v>
+        <v>488</v>
       </c>
       <c r="S11" t="n">
-        <v>3.8</v>
+        <v>3.37</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-09</t>
         </is>
       </c>
     </row>
@@ -1210,59 +1210,59 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>333.86</v>
+        <v>346.9</v>
       </c>
       <c r="D12" t="n">
-        <v>3.43</v>
+        <v>2.94</v>
       </c>
       <c r="E12" t="n">
-        <v>321.68</v>
+        <v>331.58</v>
       </c>
       <c r="F12" t="n">
-        <v>316.63</v>
+        <v>325.23</v>
       </c>
       <c r="G12" t="n">
-        <v>315.91</v>
+        <v>317.05</v>
       </c>
       <c r="H12" t="n">
-        <v>5.491</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>5.073</v>
+        <v>7.34</v>
       </c>
       <c r="J12" t="n">
-        <v>68.47</v>
+        <v>71.48</v>
       </c>
       <c r="K12" t="n">
-        <v>60.82</v>
+        <v>65.69</v>
       </c>
       <c r="L12" t="n">
-        <v>83.76000000000001</v>
+        <v>83.06</v>
       </c>
       <c r="M12" t="n">
-        <v>31.92</v>
+        <v>48.49</v>
       </c>
       <c r="N12" t="n">
-        <v>34.28</v>
+        <v>35.53</v>
       </c>
       <c r="O12" t="n">
-        <v>0.93</v>
+        <v>1.36</v>
       </c>
       <c r="P12" t="n">
-        <v>337.68</v>
+        <v>337.02</v>
       </c>
       <c r="Q12" t="n">
-        <v>344.4</v>
+        <v>359.71</v>
       </c>
       <c r="R12" t="n">
-        <v>333.6</v>
+        <v>331.13</v>
       </c>
       <c r="S12" t="n">
-        <v>4.11</v>
+        <v>6.25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-09</t>
         </is>
       </c>
     </row>
@@ -1278,59 +1278,59 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>103.54</v>
+        <v>114.93</v>
       </c>
       <c r="D13" t="n">
-        <v>3.19</v>
+        <v>4.09</v>
       </c>
       <c r="E13" t="n">
-        <v>103.81</v>
+        <v>106.68</v>
       </c>
       <c r="F13" t="n">
-        <v>107.5</v>
+        <v>106.35</v>
       </c>
       <c r="G13" t="n">
-        <v>113.89</v>
+        <v>111.52</v>
       </c>
       <c r="H13" t="n">
-        <v>1.779</v>
+        <v>1.885</v>
       </c>
       <c r="I13" t="n">
-        <v>4.653</v>
+        <v>2.961</v>
       </c>
       <c r="J13" t="n">
-        <v>13.63</v>
+        <v>56.01</v>
       </c>
       <c r="K13" t="n">
-        <v>15.71</v>
+        <v>35.19</v>
       </c>
       <c r="L13" t="n">
-        <v>9.460000000000001</v>
+        <v>97.66</v>
       </c>
       <c r="M13" t="n">
-        <v>68.51000000000001</v>
+        <v>111.23</v>
       </c>
       <c r="N13" t="n">
-        <v>109.95</v>
+        <v>104.18</v>
       </c>
       <c r="O13" t="n">
-        <v>0.62</v>
+        <v>1.07</v>
       </c>
       <c r="P13" t="n">
-        <v>102.4</v>
+        <v>108.21</v>
       </c>
       <c r="Q13" t="n">
-        <v>105.84</v>
+        <v>117.85</v>
       </c>
       <c r="R13" t="n">
-        <v>101.66</v>
+        <v>107.77</v>
       </c>
       <c r="S13" t="n">
-        <v>6.82</v>
+        <v>11.07</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-09</t>
         </is>
       </c>
     </row>
@@ -1346,59 +1346,59 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>249.1</v>
+        <v>250.49</v>
       </c>
       <c r="D14" t="n">
-        <v>0.85</v>
+        <v>-2.14</v>
       </c>
       <c r="E14" t="n">
-        <v>249.01</v>
+        <v>250.44</v>
       </c>
       <c r="F14" t="n">
-        <v>259.12</v>
+        <v>252.18</v>
       </c>
       <c r="G14" t="n">
-        <v>274.73</v>
+        <v>270.38</v>
       </c>
       <c r="H14" t="n">
-        <v>-10.865</v>
+        <v>-10.086</v>
       </c>
       <c r="I14" t="n">
-        <v>-7.022</v>
+        <v>-8.201000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>22.01</v>
+        <v>43.21</v>
       </c>
       <c r="K14" t="n">
-        <v>23.2</v>
+        <v>32.65</v>
       </c>
       <c r="L14" t="n">
-        <v>19.65</v>
+        <v>64.33</v>
       </c>
       <c r="M14" t="n">
-        <v>19.75</v>
+        <v>44.47</v>
       </c>
       <c r="N14" t="n">
-        <v>30.27</v>
+        <v>33.58</v>
       </c>
       <c r="O14" t="n">
-        <v>0.65</v>
+        <v>1.32</v>
       </c>
       <c r="P14" t="n">
-        <v>250.99</v>
+        <v>250</v>
       </c>
       <c r="Q14" t="n">
-        <v>254.6</v>
+        <v>253.49</v>
       </c>
       <c r="R14" t="n">
-        <v>247.5</v>
+        <v>243.9</v>
       </c>
       <c r="S14" t="n">
-        <v>2.96</v>
+        <v>6.66</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-09</t>
         </is>
       </c>
     </row>
@@ -1414,59 +1414,59 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>210.29</v>
+        <v>227.52</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.25</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>216.14</v>
+        <v>219.15</v>
       </c>
       <c r="F15" t="n">
-        <v>226.79</v>
+        <v>223.27</v>
       </c>
       <c r="G15" t="n">
-        <v>226.93</v>
+        <v>228.44</v>
       </c>
       <c r="H15" t="n">
-        <v>7.595</v>
+        <v>7.069</v>
       </c>
       <c r="I15" t="n">
-        <v>12.768</v>
+        <v>10.344</v>
       </c>
       <c r="J15" t="n">
-        <v>14.27</v>
+        <v>36.59</v>
       </c>
       <c r="K15" t="n">
-        <v>29.52</v>
+        <v>29.36</v>
       </c>
       <c r="L15" t="n">
-        <v>-16.22</v>
+        <v>51.06</v>
       </c>
       <c r="M15" t="n">
-        <v>21.49</v>
+        <v>32.44</v>
       </c>
       <c r="N15" t="n">
-        <v>39.76</v>
+        <v>38.58</v>
       </c>
       <c r="O15" t="n">
-        <v>0.54</v>
+        <v>0.84</v>
       </c>
       <c r="P15" t="n">
-        <v>213.6</v>
+        <v>224</v>
       </c>
       <c r="Q15" t="n">
-        <v>217.55</v>
+        <v>231.18</v>
       </c>
       <c r="R15" t="n">
-        <v>210.2</v>
+        <v>220.42</v>
       </c>
       <c r="S15" t="n">
-        <v>4.56</v>
+        <v>6.89</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-09</t>
         </is>
       </c>
     </row>
@@ -1482,59 +1482,59 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>41.45</v>
+        <v>48.1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.8</v>
+        <v>3.62</v>
       </c>
       <c r="E16" t="n">
-        <v>42.55</v>
+        <v>44.06</v>
       </c>
       <c r="F16" t="n">
-        <v>44.62</v>
+        <v>43.92</v>
       </c>
       <c r="G16" t="n">
-        <v>45.26</v>
+        <v>46.26</v>
       </c>
       <c r="H16" t="n">
-        <v>1.253</v>
+        <v>1.461</v>
       </c>
       <c r="I16" t="n">
-        <v>2.451</v>
+        <v>1.988</v>
       </c>
       <c r="J16" t="n">
-        <v>9.050000000000001</v>
+        <v>57.08</v>
       </c>
       <c r="K16" t="n">
-        <v>18.02</v>
+        <v>34.14</v>
       </c>
       <c r="L16" t="n">
-        <v>-8.9</v>
+        <v>102.94</v>
       </c>
       <c r="M16" t="n">
-        <v>13.92</v>
+        <v>40.05</v>
       </c>
       <c r="N16" t="n">
-        <v>30.93</v>
+        <v>31.94</v>
       </c>
       <c r="O16" t="n">
-        <v>0.45</v>
+        <v>1.25</v>
       </c>
       <c r="P16" t="n">
-        <v>43.88</v>
+        <v>44.94</v>
       </c>
       <c r="Q16" t="n">
-        <v>43.88</v>
+        <v>48.42</v>
       </c>
       <c r="R16" t="n">
-        <v>41.3</v>
+        <v>44.94</v>
       </c>
       <c r="S16" t="n">
-        <v>6.95</v>
+        <v>19.98</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-09</t>
         </is>
       </c>
     </row>
@@ -1550,59 +1550,59 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>18.68</v>
+        <v>21.88</v>
       </c>
       <c r="D17" t="n">
-        <v>-3.21</v>
+        <v>2.43</v>
       </c>
       <c r="E17" t="n">
-        <v>19.77</v>
+        <v>20.21</v>
       </c>
       <c r="F17" t="n">
-        <v>20.87</v>
+        <v>20.43</v>
       </c>
       <c r="G17" t="n">
-        <v>21.28</v>
+        <v>21.43</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.037</v>
+        <v>0.057</v>
       </c>
       <c r="I17" t="n">
-        <v>0.44</v>
+        <v>0.188</v>
       </c>
       <c r="J17" t="n">
-        <v>5.6</v>
+        <v>50.24</v>
       </c>
       <c r="K17" t="n">
-        <v>14.19</v>
+        <v>29.95</v>
       </c>
       <c r="L17" t="n">
-        <v>-11.58</v>
+        <v>90.83</v>
       </c>
       <c r="M17" t="n">
-        <v>19.77</v>
+        <v>46.1</v>
       </c>
       <c r="N17" t="n">
-        <v>41.88</v>
+        <v>45.34</v>
       </c>
       <c r="O17" t="n">
-        <v>0.47</v>
+        <v>1.02</v>
       </c>
       <c r="P17" t="n">
-        <v>19.69</v>
+        <v>21.02</v>
       </c>
       <c r="Q17" t="n">
-        <v>19.73</v>
+        <v>22.42</v>
       </c>
       <c r="R17" t="n">
-        <v>18.68</v>
+        <v>20.95</v>
       </c>
       <c r="S17" t="n">
-        <v>5.36</v>
+        <v>12.5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-09</t>
         </is>
       </c>
     </row>
@@ -1618,59 +1618,59 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>14.82</v>
+        <v>15.58</v>
       </c>
       <c r="D18" t="n">
-        <v>-4.2</v>
+        <v>-0.19</v>
       </c>
       <c r="E18" t="n">
-        <v>15.72</v>
+        <v>15.34</v>
       </c>
       <c r="F18" t="n">
-        <v>17.03</v>
+        <v>15.91</v>
       </c>
       <c r="G18" t="n">
-        <v>17.02</v>
+        <v>17.15</v>
       </c>
       <c r="H18" t="n">
-        <v>0.064</v>
+        <v>-0.151</v>
       </c>
       <c r="I18" t="n">
-        <v>0.538</v>
+        <v>0.226</v>
       </c>
       <c r="J18" t="n">
-        <v>5.4</v>
+        <v>22.63</v>
       </c>
       <c r="K18" t="n">
-        <v>14.69</v>
+        <v>16.53</v>
       </c>
       <c r="L18" t="n">
-        <v>-13.17</v>
+        <v>34.83</v>
       </c>
       <c r="M18" t="n">
-        <v>10.6</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="N18" t="n">
-        <v>13.08</v>
+        <v>14.06</v>
       </c>
       <c r="O18" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.63</v>
       </c>
       <c r="P18" t="n">
-        <v>15.49</v>
+        <v>15.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>15.52</v>
+        <v>15.79</v>
       </c>
       <c r="R18" t="n">
-        <v>14.74</v>
+        <v>15.37</v>
       </c>
       <c r="S18" t="n">
-        <v>5.85</v>
+        <v>4.91</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-09</t>
         </is>
       </c>
     </row>
@@ -1686,59 +1686,59 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>36.65</v>
+        <v>39</v>
       </c>
       <c r="D19" t="n">
-        <v>0.52</v>
+        <v>-0.64</v>
       </c>
       <c r="E19" t="n">
-        <v>37.7</v>
+        <v>37.41</v>
       </c>
       <c r="F19" t="n">
-        <v>37.31</v>
+        <v>37.71</v>
       </c>
       <c r="G19" t="n">
-        <v>37.45</v>
+        <v>37.34</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.22</v>
+        <v>0.107</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.241</v>
+        <v>-0.012</v>
       </c>
       <c r="J19" t="n">
-        <v>49.85</v>
+        <v>63.21</v>
       </c>
       <c r="K19" t="n">
-        <v>52.99</v>
+        <v>53.63</v>
       </c>
       <c r="L19" t="n">
-        <v>43.58</v>
+        <v>82.38</v>
       </c>
       <c r="M19" t="n">
-        <v>48.13</v>
+        <v>83.55</v>
       </c>
       <c r="N19" t="n">
-        <v>61.66</v>
+        <v>61.44</v>
       </c>
       <c r="O19" t="n">
-        <v>0.78</v>
+        <v>1.36</v>
       </c>
       <c r="P19" t="n">
-        <v>37</v>
+        <v>38.98</v>
       </c>
       <c r="Q19" t="n">
-        <v>37.8</v>
+        <v>39.69</v>
       </c>
       <c r="R19" t="n">
-        <v>35.87</v>
+        <v>38.61</v>
       </c>
       <c r="S19" t="n">
-        <v>6.7</v>
+        <v>11.63</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-09</t>
         </is>
       </c>
     </row>
@@ -1754,59 +1754,59 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>16.55</v>
+        <v>17.95</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>-2.55</v>
       </c>
       <c r="E20" t="n">
-        <v>17.05</v>
+        <v>17.1</v>
       </c>
       <c r="F20" t="n">
-        <v>17.19</v>
+        <v>17.26</v>
       </c>
       <c r="G20" t="n">
-        <v>17.87</v>
+        <v>17.5</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.446</v>
+        <v>-0.124</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.325</v>
+        <v>-0.102</v>
       </c>
       <c r="J20" t="n">
-        <v>21.03</v>
+        <v>54.93</v>
       </c>
       <c r="K20" t="n">
-        <v>28.3</v>
+        <v>38.41</v>
       </c>
       <c r="L20" t="n">
-        <v>6.5</v>
+        <v>87.95</v>
       </c>
       <c r="M20" t="n">
-        <v>148.19</v>
+        <v>194.11</v>
       </c>
       <c r="N20" t="n">
-        <v>270.78</v>
+        <v>226.36</v>
       </c>
       <c r="O20" t="n">
-        <v>0.55</v>
+        <v>0.86</v>
       </c>
       <c r="P20" t="n">
-        <v>16.88</v>
+        <v>17.7</v>
       </c>
       <c r="Q20" t="n">
-        <v>16.97</v>
+        <v>18.08</v>
       </c>
       <c r="R20" t="n">
-        <v>16.32</v>
+        <v>17.62</v>
       </c>
       <c r="S20" t="n">
-        <v>6.43</v>
+        <v>8.42</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-09</t>
         </is>
       </c>
     </row>
@@ -1822,59 +1822,59 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>46.42</v>
+        <v>50.46</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.87</v>
+        <v>-3.7</v>
       </c>
       <c r="E21" t="n">
         <v>48.86</v>
       </c>
       <c r="F21" t="n">
-        <v>49.54</v>
+        <v>49.63</v>
       </c>
       <c r="G21" t="n">
-        <v>51.09</v>
+        <v>50.34</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.669</v>
+        <v>-1.201</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.369</v>
+        <v>-1.333</v>
       </c>
       <c r="J21" t="n">
-        <v>20.39</v>
+        <v>52.18</v>
       </c>
       <c r="K21" t="n">
-        <v>28.18</v>
+        <v>38.27</v>
       </c>
       <c r="L21" t="n">
-        <v>4.8</v>
+        <v>79.98999999999999</v>
       </c>
       <c r="M21" t="n">
-        <v>37.83</v>
+        <v>51.29</v>
       </c>
       <c r="N21" t="n">
-        <v>64.8</v>
+        <v>62.04</v>
       </c>
       <c r="O21" t="n">
-        <v>0.58</v>
+        <v>0.83</v>
       </c>
       <c r="P21" t="n">
-        <v>47.98</v>
+        <v>50.85</v>
       </c>
       <c r="Q21" t="n">
-        <v>48.09</v>
+        <v>51.5</v>
       </c>
       <c r="R21" t="n">
-        <v>46.13</v>
+        <v>50.32</v>
       </c>
       <c r="S21" t="n">
-        <v>3.02</v>
+        <v>4.09</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-09</t>
         </is>
       </c>
     </row>
@@ -1890,59 +1890,59 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>45.72</v>
+        <v>47.21</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.35</v>
+        <v>-1.46</v>
       </c>
       <c r="E22" t="n">
-        <v>46.24</v>
+        <v>46.46</v>
       </c>
       <c r="F22" t="n">
-        <v>46.54</v>
+        <v>46.52</v>
       </c>
       <c r="G22" t="n">
-        <v>49.22</v>
+        <v>48.24</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.247</v>
+        <v>-1.844</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.124</v>
+        <v>-2.046</v>
       </c>
       <c r="J22" t="n">
-        <v>17.16</v>
+        <v>52.57</v>
       </c>
       <c r="K22" t="n">
-        <v>17.38</v>
+        <v>34.28</v>
       </c>
       <c r="L22" t="n">
-        <v>16.71</v>
+        <v>89.14</v>
       </c>
       <c r="M22" t="n">
-        <v>18.7</v>
+        <v>30.25</v>
       </c>
       <c r="N22" t="n">
-        <v>32.29</v>
+        <v>30.39</v>
       </c>
       <c r="O22" t="n">
-        <v>0.58</v>
+        <v>1</v>
       </c>
       <c r="P22" t="n">
-        <v>46.02</v>
+        <v>47.26</v>
       </c>
       <c r="Q22" t="n">
-        <v>46.27</v>
+        <v>47.41</v>
       </c>
       <c r="R22" t="n">
-        <v>45.62</v>
+        <v>46.8</v>
       </c>
       <c r="S22" t="n">
-        <v>0.85</v>
+        <v>1.38</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-09</t>
         </is>
       </c>
     </row>
@@ -1958,59 +1958,59 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>13.37</v>
+        <v>16.66</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.54</v>
+        <v>2.15</v>
       </c>
       <c r="E23" t="n">
-        <v>14.2</v>
+        <v>14.76</v>
       </c>
       <c r="F23" t="n">
-        <v>14.13</v>
+        <v>14.59</v>
       </c>
       <c r="G23" t="n">
-        <v>14.87</v>
+        <v>14.7</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.064</v>
+        <v>-0.433</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.15</v>
+        <v>-0.747</v>
       </c>
       <c r="J23" t="n">
-        <v>28.01</v>
+        <v>63.33</v>
       </c>
       <c r="K23" t="n">
-        <v>34.61</v>
+        <v>45.72</v>
       </c>
       <c r="L23" t="n">
-        <v>14.8</v>
+        <v>98.54000000000001</v>
       </c>
       <c r="M23" t="n">
-        <v>217.37</v>
+        <v>865.0700000000001</v>
       </c>
       <c r="N23" t="n">
-        <v>267.49</v>
+        <v>295.99</v>
       </c>
       <c r="O23" t="n">
-        <v>0.8100000000000001</v>
+        <v>2.92</v>
       </c>
       <c r="P23" t="n">
-        <v>13.97</v>
+        <v>16.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>14.02</v>
+        <v>16.95</v>
       </c>
       <c r="R23" t="n">
-        <v>13.31</v>
+        <v>16.14</v>
       </c>
       <c r="S23" t="n">
-        <v>6.25</v>
+        <v>24.86</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-09</t>
         </is>
       </c>
     </row>
@@ -2026,59 +2026,59 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>56.88</v>
+        <v>59.68</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.23</v>
+        <v>-2.63</v>
       </c>
       <c r="E24" t="n">
-        <v>58.23</v>
+        <v>58.43</v>
       </c>
       <c r="F24" t="n">
-        <v>59.19</v>
+        <v>58.73</v>
       </c>
       <c r="G24" t="n">
-        <v>63.31</v>
+        <v>61.65</v>
       </c>
       <c r="H24" t="n">
-        <v>-3.208</v>
+        <v>-2.809</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.803</v>
+        <v>-3.023</v>
       </c>
       <c r="J24" t="n">
-        <v>10.36</v>
+        <v>47.5</v>
       </c>
       <c r="K24" t="n">
-        <v>13.34</v>
+        <v>29.48</v>
       </c>
       <c r="L24" t="n">
-        <v>4.39</v>
+        <v>83.54000000000001</v>
       </c>
       <c r="M24" t="n">
-        <v>7.73</v>
+        <v>9.44</v>
       </c>
       <c r="N24" t="n">
-        <v>12.45</v>
+        <v>10.49</v>
       </c>
       <c r="O24" t="n">
-        <v>0.62</v>
+        <v>0.9</v>
       </c>
       <c r="P24" t="n">
-        <v>59</v>
+        <v>60.13</v>
       </c>
       <c r="Q24" t="n">
-        <v>59</v>
+        <v>60.39</v>
       </c>
       <c r="R24" t="n">
-        <v>56.86</v>
+        <v>59.58</v>
       </c>
       <c r="S24" t="n">
-        <v>2.1</v>
+        <v>2.56</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-09</t>
         </is>
       </c>
     </row>
@@ -2094,59 +2094,59 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>25.78</v>
+        <v>26.78</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.62</v>
+        <v>-2.97</v>
       </c>
       <c r="E25" t="n">
-        <v>27.56</v>
+        <v>26.62</v>
       </c>
       <c r="F25" t="n">
         <v>27.36</v>
       </c>
       <c r="G25" t="n">
-        <v>29.36</v>
+        <v>28.43</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.93</v>
+        <v>-0.909</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.631</v>
+        <v>-0.743</v>
       </c>
       <c r="J25" t="n">
-        <v>36.97</v>
+        <v>32.52</v>
       </c>
       <c r="K25" t="n">
-        <v>40.19</v>
+        <v>34.47</v>
       </c>
       <c r="L25" t="n">
-        <v>30.53</v>
+        <v>28.62</v>
       </c>
       <c r="M25" t="n">
-        <v>132.63</v>
+        <v>133.63</v>
       </c>
       <c r="N25" t="n">
-        <v>217.45</v>
+        <v>189.35</v>
       </c>
       <c r="O25" t="n">
-        <v>0.61</v>
+        <v>0.71</v>
       </c>
       <c r="P25" t="n">
-        <v>27.19</v>
+        <v>27.18</v>
       </c>
       <c r="Q25" t="n">
-        <v>27.3</v>
+        <v>27.5</v>
       </c>
       <c r="R25" t="n">
-        <v>25.7</v>
+        <v>26.65</v>
       </c>
       <c r="S25" t="n">
-        <v>8.35</v>
+        <v>8.41</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-09</t>
         </is>
       </c>
     </row>
@@ -2162,59 +2162,59 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>24.22</v>
+        <v>23.84</v>
       </c>
       <c r="D26" t="n">
-        <v>0.87</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>25.53</v>
+        <v>23.76</v>
       </c>
       <c r="F26" t="n">
-        <v>26.65</v>
+        <v>25.38</v>
       </c>
       <c r="G26" t="n">
-        <v>28.3</v>
+        <v>27.47</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.664</v>
+        <v>-1.107</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.003</v>
+        <v>-0.509</v>
       </c>
       <c r="J26" t="n">
-        <v>12.64</v>
+        <v>14.09</v>
       </c>
       <c r="K26" t="n">
-        <v>13.14</v>
+        <v>12.53</v>
       </c>
       <c r="L26" t="n">
-        <v>11.62</v>
+        <v>17.2</v>
       </c>
       <c r="M26" t="n">
-        <v>242.11</v>
+        <v>213.23</v>
       </c>
       <c r="N26" t="n">
-        <v>282.35</v>
+        <v>276.69</v>
       </c>
       <c r="O26" t="n">
-        <v>0.86</v>
+        <v>0.77</v>
       </c>
       <c r="P26" t="n">
-        <v>23.9</v>
+        <v>23.42</v>
       </c>
       <c r="Q26" t="n">
-        <v>24.44</v>
+        <v>24.2</v>
       </c>
       <c r="R26" t="n">
-        <v>22.93</v>
+        <v>23.01</v>
       </c>
       <c r="S26" t="n">
-        <v>7.2</v>
+        <v>6.34</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-09</t>
         </is>
       </c>
     </row>
@@ -2230,59 +2230,59 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>155</v>
+        <v>163.33</v>
       </c>
       <c r="D27" t="n">
-        <v>2.99</v>
+        <v>2.57</v>
       </c>
       <c r="E27" t="n">
-        <v>148.48</v>
+        <v>155.05</v>
       </c>
       <c r="F27" t="n">
-        <v>142.06</v>
+        <v>149.1</v>
       </c>
       <c r="G27" t="n">
-        <v>128.9</v>
+        <v>136.17</v>
       </c>
       <c r="H27" t="n">
-        <v>11.523</v>
+        <v>12.371</v>
       </c>
       <c r="I27" t="n">
-        <v>9.196999999999999</v>
+        <v>10.431</v>
       </c>
       <c r="J27" t="n">
-        <v>79.31</v>
+        <v>79.29000000000001</v>
       </c>
       <c r="K27" t="n">
-        <v>79.68000000000001</v>
+        <v>77.36</v>
       </c>
       <c r="L27" t="n">
-        <v>78.58</v>
+        <v>83.15000000000001</v>
       </c>
       <c r="M27" t="n">
-        <v>7.1</v>
+        <v>7.14</v>
       </c>
       <c r="N27" t="n">
-        <v>8.890000000000001</v>
+        <v>9.16</v>
       </c>
       <c r="O27" t="n">
-        <v>0.8</v>
+        <v>0.78</v>
       </c>
       <c r="P27" t="n">
-        <v>155.03</v>
+        <v>158.91</v>
       </c>
       <c r="Q27" t="n">
-        <v>164.1</v>
+        <v>168.2</v>
       </c>
       <c r="R27" t="n">
-        <v>150</v>
+        <v>154.61</v>
       </c>
       <c r="S27" t="n">
-        <v>8.050000000000001</v>
+        <v>8.09</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-09</t>
         </is>
       </c>
     </row>
@@ -2298,59 +2298,59 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>32.91</v>
+        <v>33.9</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.63</v>
+        <v>-2.08</v>
       </c>
       <c r="E28" t="n">
-        <v>33.14</v>
+        <v>33.39</v>
       </c>
       <c r="F28" t="n">
-        <v>32.63</v>
+        <v>33.12</v>
       </c>
       <c r="G28" t="n">
-        <v>33.9</v>
+        <v>33.41</v>
       </c>
       <c r="H28" t="n">
-        <v>-1.129</v>
+        <v>-0.84</v>
       </c>
       <c r="I28" t="n">
-        <v>-1.24</v>
+        <v>-1.128</v>
       </c>
       <c r="J28" t="n">
-        <v>62.66</v>
+        <v>68.75</v>
       </c>
       <c r="K28" t="n">
-        <v>57.4</v>
+        <v>62.31</v>
       </c>
       <c r="L28" t="n">
-        <v>73.18000000000001</v>
+        <v>81.63</v>
       </c>
       <c r="M28" t="n">
-        <v>142</v>
+        <v>220.66</v>
       </c>
       <c r="N28" t="n">
-        <v>302.18</v>
+        <v>304.14</v>
       </c>
       <c r="O28" t="n">
-        <v>0.47</v>
+        <v>0.73</v>
       </c>
       <c r="P28" t="n">
-        <v>33.25</v>
+        <v>33.99</v>
       </c>
       <c r="Q28" t="n">
-        <v>33.33</v>
+        <v>34.19</v>
       </c>
       <c r="R28" t="n">
-        <v>32.82</v>
+        <v>33.74</v>
       </c>
       <c r="S28" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.07</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-09</t>
         </is>
       </c>
     </row>
@@ -2366,59 +2366,59 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>5.94</v>
+        <v>6.32</v>
       </c>
       <c r="D29" t="n">
-        <v>-3.88</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="F29" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="G29" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="H29" t="n">
+        <v>-0.179</v>
+      </c>
+      <c r="I29" t="n">
+        <v>-0.198</v>
+      </c>
+      <c r="J29" t="n">
+        <v>56.28</v>
+      </c>
+      <c r="K29" t="n">
+        <v>47.63</v>
+      </c>
+      <c r="L29" t="n">
+        <v>73.58</v>
+      </c>
+      <c r="M29" t="n">
+        <v>200.42</v>
+      </c>
+      <c r="N29" t="n">
+        <v>274.38</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="P29" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>6.39</v>
+      </c>
+      <c r="R29" t="n">
         <v>6.18</v>
       </c>
-      <c r="F29" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="G29" t="n">
-        <v>6.51</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-0.251</v>
-      </c>
-      <c r="I29" t="n">
-        <v>-0.22</v>
-      </c>
-      <c r="J29" t="n">
-        <v>41.76</v>
-      </c>
-      <c r="K29" t="n">
-        <v>39.1</v>
-      </c>
-      <c r="L29" t="n">
-        <v>47.08</v>
-      </c>
-      <c r="M29" t="n">
-        <v>192.31</v>
-      </c>
-      <c r="N29" t="n">
-        <v>278.94</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="P29" t="n">
-        <v>6.17</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>6.17</v>
-      </c>
-      <c r="R29" t="n">
-        <v>5.88</v>
-      </c>
       <c r="S29" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-09</t>
         </is>
       </c>
     </row>
@@ -2434,59 +2434,59 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>9.4</v>
+        <v>9.27</v>
       </c>
       <c r="D30" t="n">
-        <v>-1.88</v>
+        <v>-0.32</v>
       </c>
       <c r="E30" t="n">
-        <v>9.52</v>
+        <v>9.35</v>
       </c>
       <c r="F30" t="n">
-        <v>9.43</v>
+        <v>9.42</v>
       </c>
       <c r="G30" t="n">
-        <v>9.300000000000001</v>
+        <v>9.34</v>
       </c>
       <c r="H30" t="n">
-        <v>0.158</v>
+        <v>0.094</v>
       </c>
       <c r="I30" t="n">
-        <v>0.152</v>
+        <v>0.126</v>
       </c>
       <c r="J30" t="n">
-        <v>69.02</v>
+        <v>38.64</v>
       </c>
       <c r="K30" t="n">
-        <v>77.79000000000001</v>
+        <v>52.98</v>
       </c>
       <c r="L30" t="n">
-        <v>51.48</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="M30" t="n">
-        <v>86.90000000000001</v>
+        <v>53.95</v>
       </c>
       <c r="N30" t="n">
-        <v>100.93</v>
+        <v>96.13</v>
       </c>
       <c r="O30" t="n">
-        <v>0.86</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="P30" t="n">
-        <v>9.529999999999999</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="Q30" t="n">
-        <v>9.550000000000001</v>
+        <v>9.31</v>
       </c>
       <c r="R30" t="n">
-        <v>9.33</v>
+        <v>9.18</v>
       </c>
       <c r="S30" t="n">
-        <v>0.91</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-09</t>
         </is>
       </c>
     </row>
@@ -2502,59 +2502,59 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>5.51</v>
+        <v>5.57</v>
       </c>
       <c r="D31" t="n">
-        <v>-3.33</v>
+        <v>-2.28</v>
       </c>
       <c r="E31" t="n">
-        <v>5.75</v>
+        <v>5.6</v>
       </c>
       <c r="F31" t="n">
-        <v>5.84</v>
+        <v>5.73</v>
       </c>
       <c r="G31" t="n">
-        <v>6.1</v>
+        <v>5.99</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.245</v>
+        <v>-0.25</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.203</v>
+        <v>-0.223</v>
       </c>
       <c r="J31" t="n">
-        <v>7.81</v>
+        <v>19.48</v>
       </c>
       <c r="K31" t="n">
-        <v>10.08</v>
+        <v>14.6</v>
       </c>
       <c r="L31" t="n">
-        <v>3.27</v>
+        <v>29.25</v>
       </c>
       <c r="M31" t="n">
-        <v>123.64</v>
+        <v>108.84</v>
       </c>
       <c r="N31" t="n">
-        <v>114.06</v>
+        <v>109.96</v>
       </c>
       <c r="O31" t="n">
-        <v>1.08</v>
+        <v>0.99</v>
       </c>
       <c r="P31" t="n">
-        <v>5.71</v>
+        <v>5.65</v>
       </c>
       <c r="Q31" t="n">
-        <v>5.73</v>
+        <v>5.66</v>
       </c>
       <c r="R31" t="n">
-        <v>5.5</v>
+        <v>5.53</v>
       </c>
       <c r="S31" t="n">
-        <v>1.03</v>
+        <v>0.91</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-09</t>
         </is>
       </c>
     </row>
@@ -2570,59 +2570,59 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>93.02</v>
+        <v>93.64</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.28</v>
+        <v>-0.37</v>
       </c>
       <c r="E32" t="n">
-        <v>93.47</v>
+        <v>93.45999999999999</v>
       </c>
       <c r="F32" t="n">
         <v>93.56</v>
       </c>
       <c r="G32" t="n">
-        <v>95.26000000000001</v>
+        <v>94.95</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.44</v>
+        <v>-0.642</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.079</v>
+        <v>-0.5620000000000001</v>
       </c>
       <c r="J32" t="n">
-        <v>26.94</v>
+        <v>52.95</v>
       </c>
       <c r="K32" t="n">
-        <v>24.54</v>
+        <v>40.86</v>
       </c>
       <c r="L32" t="n">
-        <v>31.74</v>
+        <v>77.13</v>
       </c>
       <c r="M32" t="n">
-        <v>7.07</v>
+        <v>5.28</v>
       </c>
       <c r="N32" t="n">
-        <v>10.29</v>
+        <v>9.43</v>
       </c>
       <c r="O32" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="P32" t="n">
-        <v>93.29000000000001</v>
+        <v>93.75</v>
       </c>
       <c r="Q32" t="n">
-        <v>93.48999999999999</v>
+        <v>93.78</v>
       </c>
       <c r="R32" t="n">
-        <v>92.69</v>
+        <v>93.36</v>
       </c>
       <c r="S32" t="n">
-        <v>0.78</v>
+        <v>0.59</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-09</t>
         </is>
       </c>
     </row>
@@ -2638,59 +2638,59 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>37.61</v>
+        <v>37.53</v>
       </c>
       <c r="D33" t="n">
-        <v>-1.39</v>
+        <v>-1.11</v>
       </c>
       <c r="E33" t="n">
-        <v>37.73</v>
+        <v>37.8</v>
       </c>
       <c r="F33" t="n">
-        <v>36.98</v>
+        <v>37.57</v>
       </c>
       <c r="G33" t="n">
-        <v>37.12</v>
+        <v>37.21</v>
       </c>
       <c r="H33" t="n">
-        <v>0.066</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.109</v>
+        <v>-0.06</v>
       </c>
       <c r="J33" t="n">
-        <v>73.42</v>
+        <v>65.08</v>
       </c>
       <c r="K33" t="n">
-        <v>67.06</v>
+        <v>68.20999999999999</v>
       </c>
       <c r="L33" t="n">
-        <v>86.12</v>
+        <v>58.82</v>
       </c>
       <c r="M33" t="n">
-        <v>15.26</v>
+        <v>14.01</v>
       </c>
       <c r="N33" t="n">
-        <v>22.9</v>
+        <v>23.07</v>
       </c>
       <c r="O33" t="n">
-        <v>0.67</v>
+        <v>0.61</v>
       </c>
       <c r="P33" t="n">
-        <v>38.04</v>
+        <v>37.8</v>
       </c>
       <c r="Q33" t="n">
-        <v>38.26</v>
+        <v>37.94</v>
       </c>
       <c r="R33" t="n">
-        <v>37.55</v>
+        <v>37.47</v>
       </c>
       <c r="S33" t="n">
-        <v>0.32</v>
+        <v>0.29</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-09</t>
         </is>
       </c>
     </row>
@@ -2706,59 +2706,59 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>13.21</v>
+        <v>14.34</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.38</v>
+        <v>2.43</v>
       </c>
       <c r="E34" t="n">
-        <v>13.22</v>
+        <v>13.59</v>
       </c>
       <c r="F34" t="n">
-        <v>14</v>
+        <v>13.58</v>
       </c>
       <c r="G34" t="n">
-        <v>13.23</v>
+        <v>13.64</v>
       </c>
       <c r="H34" t="n">
-        <v>0.676</v>
+        <v>0.599</v>
       </c>
       <c r="I34" t="n">
-        <v>0.859</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="J34" t="n">
-        <v>29.08</v>
+        <v>55.14</v>
       </c>
       <c r="K34" t="n">
-        <v>39.52</v>
+        <v>42.31</v>
       </c>
       <c r="L34" t="n">
-        <v>8.210000000000001</v>
+        <v>80.79000000000001</v>
       </c>
       <c r="M34" t="n">
-        <v>78.01000000000001</v>
+        <v>91.56999999999999</v>
       </c>
       <c r="N34" t="n">
-        <v>86.92</v>
+        <v>94.58</v>
       </c>
       <c r="O34" t="n">
-        <v>0.9</v>
+        <v>0.97</v>
       </c>
       <c r="P34" t="n">
-        <v>13.57</v>
+        <v>13.8</v>
       </c>
       <c r="Q34" t="n">
-        <v>14.18</v>
+        <v>14.5</v>
       </c>
       <c r="R34" t="n">
-        <v>13</v>
+        <v>13.46</v>
       </c>
       <c r="S34" t="n">
-        <v>18.36</v>
+        <v>21.55</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-09</t>
         </is>
       </c>
     </row>
@@ -2774,59 +2774,59 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>19.21</v>
+        <v>20.06</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.94</v>
+        <v>-0.79</v>
       </c>
       <c r="E35" t="n">
-        <v>18.73</v>
+        <v>19.73</v>
       </c>
       <c r="F35" t="n">
-        <v>18.24</v>
+        <v>18.98</v>
       </c>
       <c r="G35" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.239</v>
+        <v>0.055</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.342</v>
+        <v>-0.181</v>
       </c>
       <c r="J35" t="n">
-        <v>68.19</v>
+        <v>79.02</v>
       </c>
       <c r="K35" t="n">
-        <v>56.03</v>
+        <v>70.5</v>
       </c>
       <c r="L35" t="n">
-        <v>92.52</v>
+        <v>96.05</v>
       </c>
       <c r="M35" t="n">
-        <v>57.41</v>
+        <v>56.58</v>
       </c>
       <c r="N35" t="n">
-        <v>53.26</v>
+        <v>53.8</v>
       </c>
       <c r="O35" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="P35" t="n">
-        <v>19.87</v>
+        <v>20</v>
       </c>
       <c r="Q35" t="n">
-        <v>19.9</v>
+        <v>20.25</v>
       </c>
       <c r="R35" t="n">
-        <v>19.01</v>
+        <v>19.71</v>
       </c>
       <c r="S35" t="n">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-09</t>
         </is>
       </c>
     </row>
@@ -2842,59 +2842,59 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>33.2</v>
+        <v>32.97</v>
       </c>
       <c r="D36" t="n">
-        <v>-2.5</v>
+        <v>-4.66</v>
       </c>
       <c r="E36" t="n">
-        <v>32.98</v>
+        <v>33.54</v>
       </c>
       <c r="F36" t="n">
-        <v>32.4</v>
+        <v>32.93</v>
       </c>
       <c r="G36" t="n">
-        <v>33.59</v>
+        <v>33.27</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.339</v>
+        <v>-1.152</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.705</v>
+        <v>-1.612</v>
       </c>
       <c r="J36" t="n">
-        <v>54.87</v>
+        <v>57.48</v>
       </c>
       <c r="K36" t="n">
-        <v>43.38</v>
+        <v>53.61</v>
       </c>
       <c r="L36" t="n">
-        <v>77.86</v>
+        <v>65.23</v>
       </c>
       <c r="M36" t="n">
-        <v>38.26</v>
+        <v>55.65</v>
       </c>
       <c r="N36" t="n">
-        <v>42.68</v>
+        <v>41.14</v>
       </c>
       <c r="O36" t="n">
-        <v>0.9</v>
+        <v>1.35</v>
       </c>
       <c r="P36" t="n">
-        <v>34.69</v>
+        <v>33.9</v>
       </c>
       <c r="Q36" t="n">
-        <v>34.75</v>
+        <v>33.93</v>
       </c>
       <c r="R36" t="n">
-        <v>33.07</v>
+        <v>32.5</v>
       </c>
       <c r="S36" t="n">
-        <v>2.01</v>
+        <v>2.93</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-09</t>
         </is>
       </c>
     </row>
@@ -2910,59 +2910,59 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>47.58</v>
+        <v>46.79</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.23</v>
+        <v>0.06</v>
       </c>
       <c r="E37" t="n">
-        <v>47.29</v>
+        <v>47.45</v>
       </c>
       <c r="F37" t="n">
-        <v>47.69</v>
+        <v>47.36</v>
       </c>
       <c r="G37" t="n">
         <v>47.99</v>
       </c>
       <c r="H37" t="n">
-        <v>0.783</v>
+        <v>0.525</v>
       </c>
       <c r="I37" t="n">
-        <v>1.146</v>
+        <v>0.864</v>
       </c>
       <c r="J37" t="n">
-        <v>35.57</v>
+        <v>42.97</v>
       </c>
       <c r="K37" t="n">
-        <v>33.23</v>
+        <v>42.88</v>
       </c>
       <c r="L37" t="n">
-        <v>40.24</v>
+        <v>43.16</v>
       </c>
       <c r="M37" t="n">
-        <v>21.32</v>
+        <v>22.24</v>
       </c>
       <c r="N37" t="n">
-        <v>43.37</v>
+        <v>39.38</v>
       </c>
       <c r="O37" t="n">
-        <v>0.49</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="P37" t="n">
-        <v>47.7</v>
+        <v>46.8</v>
       </c>
       <c r="Q37" t="n">
-        <v>47.88</v>
+        <v>47.3</v>
       </c>
       <c r="R37" t="n">
-        <v>47.03</v>
+        <v>46.58</v>
       </c>
       <c r="S37" t="n">
         <v>0.13</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-09</t>
         </is>
       </c>
     </row>
@@ -2978,59 +2978,59 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>4.68</v>
+        <v>4.8</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.85</v>
+        <v>-1.44</v>
       </c>
       <c r="E38" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="F38" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="G38" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="H38" t="n">
+        <v>-0.216</v>
+      </c>
+      <c r="I38" t="n">
+        <v>-0.222</v>
+      </c>
+      <c r="J38" t="n">
+        <v>53.04</v>
+      </c>
+      <c r="K38" t="n">
+        <v>45.1</v>
+      </c>
+      <c r="L38" t="n">
+        <v>68.92</v>
+      </c>
+      <c r="M38" t="n">
+        <v>21.82</v>
+      </c>
+      <c r="N38" t="n">
+        <v>37.04</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="P38" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="R38" t="n">
         <v>4.77</v>
       </c>
-      <c r="F38" t="n">
-        <v>4.74</v>
-      </c>
-      <c r="G38" t="n">
-        <v>5.14</v>
-      </c>
-      <c r="H38" t="n">
-        <v>-0.296</v>
-      </c>
-      <c r="I38" t="n">
-        <v>-0.28</v>
-      </c>
-      <c r="J38" t="n">
-        <v>41.15</v>
-      </c>
-      <c r="K38" t="n">
-        <v>35.34</v>
-      </c>
-      <c r="L38" t="n">
-        <v>52.76</v>
-      </c>
-      <c r="M38" t="n">
-        <v>22.68</v>
-      </c>
-      <c r="N38" t="n">
-        <v>41.93</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="P38" t="n">
-        <v>4.73</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>4.77</v>
-      </c>
-      <c r="R38" t="n">
-        <v>4.64</v>
-      </c>
       <c r="S38" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-09</t>
         </is>
       </c>
     </row>
@@ -3046,59 +3046,59 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>31.19</v>
+        <v>32.75</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.76</v>
+        <v>0.09</v>
       </c>
       <c r="E39" t="n">
+        <v>31.97</v>
+      </c>
+      <c r="F39" t="n">
+        <v>32.71</v>
+      </c>
+      <c r="G39" t="n">
+        <v>34.34</v>
+      </c>
+      <c r="H39" t="n">
+        <v>-0.524</v>
+      </c>
+      <c r="I39" t="n">
+        <v>-0.134</v>
+      </c>
+      <c r="J39" t="n">
+        <v>29.39</v>
+      </c>
+      <c r="K39" t="n">
+        <v>20.08</v>
+      </c>
+      <c r="L39" t="n">
+        <v>48.01</v>
+      </c>
+      <c r="M39" t="n">
+        <v>24.88</v>
+      </c>
+      <c r="N39" t="n">
+        <v>43.99</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="P39" t="n">
         <v>32.34</v>
       </c>
-      <c r="F39" t="n">
-        <v>33.5</v>
-      </c>
-      <c r="G39" t="n">
-        <v>35.51</v>
-      </c>
-      <c r="H39" t="n">
-        <v>-0.386</v>
-      </c>
-      <c r="I39" t="n">
-        <v>0.289</v>
-      </c>
-      <c r="J39" t="n">
-        <v>9.779999999999999</v>
-      </c>
-      <c r="K39" t="n">
-        <v>15.14</v>
-      </c>
-      <c r="L39" t="n">
-        <v>-0.95</v>
-      </c>
-      <c r="M39" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="N39" t="n">
-        <v>54.85</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="P39" t="n">
-        <v>31.75</v>
-      </c>
       <c r="Q39" t="n">
-        <v>31.94</v>
+        <v>33.06</v>
       </c>
       <c r="R39" t="n">
-        <v>30.96</v>
+        <v>32.21</v>
       </c>
       <c r="S39" t="n">
-        <v>0.96</v>
+        <v>1.16</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-09</t>
         </is>
       </c>
     </row>

--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W57"/>
+  <dimension ref="A1:W58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -545,68 +545,68 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>97.08</v>
+        <v>92.26000000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>-1.28</v>
+        <v>-4.96</v>
       </c>
       <c r="E2" t="n">
-        <v>99.42</v>
+        <v>97.62</v>
       </c>
       <c r="F2" t="n">
-        <v>100.33</v>
+        <v>99.37</v>
       </c>
       <c r="G2" t="n">
-        <v>101.81</v>
+        <v>101.18</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.158</v>
+        <v>-1.724</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6929999999999999</v>
+        <v>-0.906</v>
       </c>
       <c r="J2" t="n">
-        <v>11.57</v>
+        <v>13.61</v>
       </c>
       <c r="K2" t="n">
-        <v>15.6</v>
+        <v>14.94</v>
       </c>
       <c r="L2" t="n">
-        <v>3.5</v>
+        <v>10.96</v>
       </c>
       <c r="M2" t="n">
-        <v>12.14</v>
+        <v>5.61</v>
       </c>
       <c r="N2" t="n">
-        <v>25.63</v>
+        <v>16.5</v>
       </c>
       <c r="O2" t="n">
-        <v>35.85</v>
+        <v>28.3</v>
       </c>
       <c r="P2" t="n">
-        <v>24.82</v>
+        <v>87.16</v>
       </c>
       <c r="Q2" t="n">
-        <v>14.16</v>
+        <v>17.75</v>
       </c>
       <c r="R2" t="n">
-        <v>1.75</v>
+        <v>4.91</v>
       </c>
       <c r="S2" t="n">
-        <v>97.73999999999999</v>
+        <v>90.78</v>
       </c>
       <c r="T2" t="n">
-        <v>97.95</v>
+        <v>94.5</v>
       </c>
       <c r="U2" t="n">
-        <v>97</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="V2" t="n">
-        <v>0.64</v>
+        <v>2.25</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
@@ -622,68 +622,68 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>436</v>
+        <v>460</v>
       </c>
       <c r="D3" t="n">
-        <v>-2.02</v>
+        <v>5.5</v>
       </c>
       <c r="E3" t="n">
-        <v>437.69</v>
+        <v>440.71</v>
       </c>
       <c r="F3" t="n">
-        <v>436.73</v>
+        <v>439</v>
       </c>
       <c r="G3" t="n">
-        <v>420.53</v>
+        <v>423.82</v>
       </c>
       <c r="H3" t="n">
-        <v>13.671</v>
+        <v>14.866</v>
       </c>
       <c r="I3" t="n">
-        <v>14.136</v>
+        <v>14.262</v>
       </c>
       <c r="J3" t="n">
-        <v>61.19</v>
+        <v>70.02</v>
       </c>
       <c r="K3" t="n">
-        <v>64.02</v>
+        <v>66.02</v>
       </c>
       <c r="L3" t="n">
-        <v>55.52</v>
+        <v>78.01000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>53.03</v>
+        <v>68.62</v>
       </c>
       <c r="N3" t="n">
-        <v>57.46</v>
+        <v>65.75</v>
       </c>
       <c r="O3" t="n">
-        <v>59.2</v>
+        <v>64</v>
       </c>
       <c r="P3" t="n">
-        <v>29.81</v>
+        <v>47.37</v>
       </c>
       <c r="Q3" t="n">
-        <v>38.38</v>
+        <v>39.63</v>
       </c>
       <c r="R3" t="n">
-        <v>0.78</v>
+        <v>1.2</v>
       </c>
       <c r="S3" t="n">
-        <v>446.5</v>
+        <v>457.5</v>
       </c>
       <c r="T3" t="n">
-        <v>449.5</v>
+        <v>465.88</v>
       </c>
       <c r="U3" t="n">
-        <v>436</v>
+        <v>448.63</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7</v>
+        <v>1.11</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
@@ -699,68 +699,68 @@
         </is>
       </c>
       <c r="C4" t="n">
+        <v>27.49</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="E4" t="n">
         <v>27.22</v>
       </c>
-      <c r="D4" t="n">
-        <v>-0.37</v>
-      </c>
-      <c r="E4" t="n">
-        <v>26.97</v>
-      </c>
       <c r="F4" t="n">
-        <v>26.69</v>
+        <v>26.81</v>
       </c>
       <c r="G4" t="n">
-        <v>25.91</v>
+        <v>26.08</v>
       </c>
       <c r="H4" t="n">
-        <v>0.445</v>
+        <v>0.48</v>
       </c>
       <c r="I4" t="n">
-        <v>0.253</v>
+        <v>0.294</v>
       </c>
       <c r="J4" t="n">
-        <v>71.53</v>
+        <v>74.5</v>
       </c>
       <c r="K4" t="n">
-        <v>72.22</v>
+        <v>72.98</v>
       </c>
       <c r="L4" t="n">
-        <v>70.13</v>
+        <v>77.53</v>
       </c>
       <c r="M4" t="n">
-        <v>72.36</v>
+        <v>77.14</v>
       </c>
       <c r="N4" t="n">
-        <v>66.39</v>
+        <v>69.01000000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>57.93</v>
+        <v>59.26</v>
       </c>
       <c r="P4" t="n">
-        <v>173</v>
+        <v>178.74</v>
       </c>
       <c r="Q4" t="n">
-        <v>147.51</v>
+        <v>152.5</v>
       </c>
       <c r="R4" t="n">
         <v>1.17</v>
       </c>
       <c r="S4" t="n">
-        <v>27.23</v>
+        <v>27.29</v>
       </c>
       <c r="T4" t="n">
-        <v>27.78</v>
+        <v>27.84</v>
       </c>
       <c r="U4" t="n">
-        <v>27.07</v>
+        <v>27.29</v>
       </c>
       <c r="V4" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
@@ -776,68 +776,68 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>102.8</v>
+        <v>107.1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.97</v>
+        <v>4.18</v>
       </c>
       <c r="E5" t="n">
-        <v>98.7</v>
+        <v>100.86</v>
       </c>
       <c r="F5" t="n">
-        <v>97.38</v>
+        <v>99.48999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>88.98999999999999</v>
+        <v>90.43000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>4.351</v>
+        <v>4.93</v>
       </c>
       <c r="I5" t="n">
-        <v>2.801</v>
+        <v>3.187</v>
       </c>
       <c r="J5" t="n">
-        <v>76.09</v>
+        <v>78.73</v>
       </c>
       <c r="K5" t="n">
-        <v>75.58</v>
+        <v>76.63</v>
       </c>
       <c r="L5" t="n">
-        <v>77.09999999999999</v>
+        <v>82.93000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>70.44</v>
+        <v>76.45999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>66.77</v>
+        <v>70.55</v>
       </c>
       <c r="O5" t="n">
-        <v>60.13</v>
+        <v>62.4</v>
       </c>
       <c r="P5" t="n">
-        <v>72.48999999999999</v>
+        <v>72.48</v>
       </c>
       <c r="Q5" t="n">
-        <v>57.34</v>
+        <v>59.8</v>
       </c>
       <c r="R5" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="S5" t="n">
-        <v>97.01000000000001</v>
+        <v>102</v>
       </c>
       <c r="T5" t="n">
-        <v>103.8</v>
+        <v>109.98</v>
       </c>
       <c r="U5" t="n">
-        <v>97.01000000000001</v>
+        <v>101.2</v>
       </c>
       <c r="V5" t="n">
         <v>6.13</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
@@ -853,68 +853,68 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>857.5</v>
+        <v>856</v>
       </c>
       <c r="D6" t="n">
-        <v>1.48</v>
+        <v>-0.17</v>
       </c>
       <c r="E6" t="n">
-        <v>853.7</v>
+        <v>847.71</v>
       </c>
       <c r="F6" t="n">
-        <v>861.3</v>
+        <v>861.9</v>
       </c>
       <c r="G6" t="n">
-        <v>781.37</v>
+        <v>795.12</v>
       </c>
       <c r="H6" t="n">
-        <v>65.47799999999999</v>
+        <v>62.732</v>
       </c>
       <c r="I6" t="n">
-        <v>66.893</v>
+        <v>66.08</v>
       </c>
       <c r="J6" t="n">
-        <v>49.2</v>
+        <v>45.9</v>
       </c>
       <c r="K6" t="n">
-        <v>63.7</v>
+        <v>57.77</v>
       </c>
       <c r="L6" t="n">
-        <v>20.21</v>
+        <v>22.17</v>
       </c>
       <c r="M6" t="n">
-        <v>61.39</v>
+        <v>60.49</v>
       </c>
       <c r="N6" t="n">
-        <v>67.95999999999999</v>
+        <v>67.51000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>66.90000000000001</v>
+        <v>66.73999999999999</v>
       </c>
       <c r="P6" t="n">
-        <v>21.27</v>
+        <v>30.94</v>
       </c>
       <c r="Q6" t="n">
-        <v>29.02</v>
+        <v>29.68</v>
       </c>
       <c r="R6" t="n">
-        <v>0.73</v>
+        <v>1.04</v>
       </c>
       <c r="S6" t="n">
-        <v>863.66</v>
+        <v>888.5</v>
       </c>
       <c r="T6" t="n">
-        <v>874.65</v>
+        <v>889</v>
       </c>
       <c r="U6" t="n">
-        <v>845</v>
+        <v>840.45</v>
       </c>
       <c r="V6" t="n">
-        <v>1.92</v>
+        <v>2.79</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
@@ -930,68 +930,68 @@
         </is>
       </c>
       <c r="C7" t="n">
+        <v>7.36</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-1.21</v>
+      </c>
+      <c r="E7" t="n">
+        <v>7.46</v>
+      </c>
+      <c r="F7" t="n">
+        <v>7.52</v>
+      </c>
+      <c r="G7" t="n">
+        <v>7.46</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="J7" t="n">
+        <v>25.89</v>
+      </c>
+      <c r="K7" t="n">
+        <v>40.46</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-3.25</v>
+      </c>
+      <c r="M7" t="n">
+        <v>28.76</v>
+      </c>
+      <c r="N7" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="O7" t="n">
+        <v>47.44</v>
+      </c>
+      <c r="P7" t="n">
+        <v>382.68</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>247</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S7" t="n">
         <v>7.45</v>
       </c>
-      <c r="D7" t="n">
-        <v>-0.27</v>
-      </c>
-      <c r="E7" t="n">
-        <v>7.51</v>
-      </c>
-      <c r="F7" t="n">
-        <v>7.53</v>
-      </c>
-      <c r="G7" t="n">
-        <v>7.48</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.037</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.047</v>
-      </c>
-      <c r="J7" t="n">
-        <v>32.08</v>
-      </c>
-      <c r="K7" t="n">
-        <v>47.75</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="M7" t="n">
-        <v>39.57</v>
-      </c>
-      <c r="N7" t="n">
-        <v>48.38</v>
-      </c>
-      <c r="O7" t="n">
-        <v>50.48</v>
-      </c>
-      <c r="P7" t="n">
-        <v>302.24</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>241.66</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S7" t="n">
-        <v>7.46</v>
-      </c>
       <c r="T7" t="n">
-        <v>7.51</v>
+        <v>7.45</v>
       </c>
       <c r="U7" t="n">
-        <v>7.42</v>
+        <v>7.31</v>
       </c>
       <c r="V7" t="n">
-        <v>0.11</v>
+        <v>0.14</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
@@ -1007,68 +1007,68 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>14.12</v>
+        <v>14.14</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.67</v>
+        <v>0.14</v>
       </c>
       <c r="E8" t="n">
-        <v>14.26</v>
+        <v>14.21</v>
       </c>
       <c r="F8" t="n">
-        <v>14.41</v>
+        <v>14.36</v>
       </c>
       <c r="G8" t="n">
-        <v>14.77</v>
+        <v>14.71</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.285</v>
+        <v>-0.292</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.225</v>
+        <v>-0.238</v>
       </c>
       <c r="J8" t="n">
-        <v>13.56</v>
+        <v>14.25</v>
       </c>
       <c r="K8" t="n">
-        <v>13.09</v>
+        <v>13.48</v>
       </c>
       <c r="L8" t="n">
-        <v>14.51</v>
+        <v>15.8</v>
       </c>
       <c r="M8" t="n">
-        <v>22.63</v>
+        <v>25.03</v>
       </c>
       <c r="N8" t="n">
-        <v>28.53</v>
+        <v>29.52</v>
       </c>
       <c r="O8" t="n">
-        <v>37.79</v>
+        <v>38.23</v>
       </c>
       <c r="P8" t="n">
-        <v>97.94</v>
+        <v>116.85</v>
       </c>
       <c r="Q8" t="n">
-        <v>71.47</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="R8" t="n">
-        <v>1.37</v>
+        <v>1.58</v>
       </c>
       <c r="S8" t="n">
-        <v>14.26</v>
+        <v>14.2</v>
       </c>
       <c r="T8" t="n">
-        <v>14.29</v>
+        <v>14.23</v>
       </c>
       <c r="U8" t="n">
-        <v>14.1</v>
+        <v>14.04</v>
       </c>
       <c r="V8" t="n">
-        <v>0.78</v>
+        <v>0.93</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
@@ -1084,68 +1084,68 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>35.44</v>
+        <v>37.6</v>
       </c>
       <c r="D9" t="n">
-        <v>1.52</v>
+        <v>6.09</v>
       </c>
       <c r="E9" t="n">
-        <v>36.63</v>
+        <v>36.26</v>
       </c>
       <c r="F9" t="n">
-        <v>37.13</v>
+        <v>37.12</v>
       </c>
       <c r="G9" t="n">
-        <v>36.3</v>
+        <v>36.51</v>
       </c>
       <c r="H9" t="n">
-        <v>0.175</v>
+        <v>0.243</v>
       </c>
       <c r="I9" t="n">
-        <v>0.382</v>
+        <v>0.35</v>
       </c>
       <c r="J9" t="n">
-        <v>30.99</v>
+        <v>38.77</v>
       </c>
       <c r="K9" t="n">
-        <v>45.2</v>
+        <v>43.06</v>
       </c>
       <c r="L9" t="n">
-        <v>2.57</v>
+        <v>30.2</v>
       </c>
       <c r="M9" t="n">
-        <v>39.31</v>
+        <v>57.25</v>
       </c>
       <c r="N9" t="n">
-        <v>45.48</v>
+        <v>54.48</v>
       </c>
       <c r="O9" t="n">
-        <v>48.83</v>
+        <v>53.31</v>
       </c>
       <c r="P9" t="n">
-        <v>92.64</v>
+        <v>165.44</v>
       </c>
       <c r="Q9" t="n">
-        <v>118.31</v>
+        <v>122.19</v>
       </c>
       <c r="R9" t="n">
-        <v>0.78</v>
+        <v>1.35</v>
       </c>
       <c r="S9" t="n">
-        <v>34.97</v>
+        <v>36.16</v>
       </c>
       <c r="T9" t="n">
-        <v>35.79</v>
+        <v>38.38</v>
       </c>
       <c r="U9" t="n">
-        <v>34.7</v>
+        <v>36.15</v>
       </c>
       <c r="V9" t="n">
-        <v>8.08</v>
+        <v>14.43</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
@@ -1161,68 +1161,68 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>525.79</v>
+        <v>522.48</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.09</v>
+        <v>-0.63</v>
       </c>
       <c r="E10" t="n">
-        <v>534.7</v>
+        <v>531.75</v>
       </c>
       <c r="F10" t="n">
-        <v>565.5</v>
+        <v>558.85</v>
       </c>
       <c r="G10" t="n">
-        <v>529.88</v>
+        <v>533.63</v>
       </c>
       <c r="H10" t="n">
-        <v>25.66</v>
+        <v>22.205</v>
       </c>
       <c r="I10" t="n">
-        <v>32.454</v>
+        <v>30.448</v>
       </c>
       <c r="J10" t="n">
-        <v>28.47</v>
+        <v>20.63</v>
       </c>
       <c r="K10" t="n">
-        <v>47.22</v>
+        <v>38.36</v>
       </c>
       <c r="L10" t="n">
-        <v>-9.029999999999999</v>
+        <v>-14.83</v>
       </c>
       <c r="M10" t="n">
-        <v>39.61</v>
+        <v>38.13</v>
       </c>
       <c r="N10" t="n">
-        <v>50.83</v>
+        <v>50.02</v>
       </c>
       <c r="O10" t="n">
-        <v>55.01</v>
+        <v>54.62</v>
       </c>
       <c r="P10" t="n">
-        <v>30.21</v>
+        <v>42.09</v>
       </c>
       <c r="Q10" t="n">
-        <v>39.46</v>
+        <v>40.48</v>
       </c>
       <c r="R10" t="n">
-        <v>0.77</v>
+        <v>1.04</v>
       </c>
       <c r="S10" t="n">
-        <v>549</v>
+        <v>539.9</v>
       </c>
       <c r="T10" t="n">
-        <v>549</v>
+        <v>542.58</v>
       </c>
       <c r="U10" t="n">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="V10" t="n">
-        <v>3.41</v>
+        <v>4.75</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
@@ -1238,68 +1238,68 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>307.5</v>
+        <v>316.16</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.15</v>
+        <v>2.82</v>
       </c>
       <c r="E11" t="n">
-        <v>314.9</v>
+        <v>313.36</v>
       </c>
       <c r="F11" t="n">
-        <v>340.68</v>
+        <v>334.37</v>
       </c>
       <c r="G11" t="n">
-        <v>340.33</v>
+        <v>340</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.54</v>
+        <v>-1.653</v>
       </c>
       <c r="I11" t="n">
-        <v>6.656</v>
+        <v>4.999</v>
       </c>
       <c r="J11" t="n">
-        <v>12.44</v>
+        <v>13.22</v>
       </c>
       <c r="K11" t="n">
-        <v>26.07</v>
+        <v>21.79</v>
       </c>
       <c r="L11" t="n">
-        <v>-14.83</v>
+        <v>-3.92</v>
       </c>
       <c r="M11" t="n">
-        <v>30.89</v>
+        <v>39.83</v>
       </c>
       <c r="N11" t="n">
-        <v>41.44</v>
+        <v>44.76</v>
       </c>
       <c r="O11" t="n">
-        <v>48.07</v>
+        <v>49.56</v>
       </c>
       <c r="P11" t="n">
-        <v>23.6</v>
+        <v>54.07</v>
       </c>
       <c r="Q11" t="n">
-        <v>41.61</v>
+        <v>42.91</v>
       </c>
       <c r="R11" t="n">
-        <v>0.57</v>
+        <v>1.26</v>
       </c>
       <c r="S11" t="n">
-        <v>312.87</v>
+        <v>312.85</v>
       </c>
       <c r="T11" t="n">
-        <v>314.9</v>
+        <v>336.58</v>
       </c>
       <c r="U11" t="n">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="V11" t="n">
-        <v>3.03</v>
+        <v>6.95</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
@@ -1315,68 +1315,68 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>119.53</v>
+        <v>125.19</v>
       </c>
       <c r="D12" t="n">
-        <v>0.41</v>
+        <v>4.74</v>
       </c>
       <c r="E12" t="n">
-        <v>117.65</v>
+        <v>119.63</v>
       </c>
       <c r="F12" t="n">
-        <v>117.48</v>
+        <v>118.33</v>
       </c>
       <c r="G12" t="n">
-        <v>114.73</v>
+        <v>115.97</v>
       </c>
       <c r="H12" t="n">
-        <v>2.865</v>
+        <v>3.31</v>
       </c>
       <c r="I12" t="n">
-        <v>2.994</v>
+        <v>3.055</v>
       </c>
       <c r="J12" t="n">
-        <v>59.45</v>
+        <v>64.58</v>
       </c>
       <c r="K12" t="n">
-        <v>58.25</v>
+        <v>60.36</v>
       </c>
       <c r="L12" t="n">
-        <v>61.86</v>
+        <v>73.01000000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>58.36</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>56.49</v>
+        <v>62.29</v>
       </c>
       <c r="O12" t="n">
-        <v>56.72</v>
+        <v>59.63</v>
       </c>
       <c r="P12" t="n">
-        <v>92.02</v>
+        <v>108.89</v>
       </c>
       <c r="Q12" t="n">
-        <v>91.06</v>
+        <v>93.53</v>
       </c>
       <c r="R12" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="S12" t="n">
-        <v>119.11</v>
+        <v>123.01</v>
       </c>
       <c r="T12" t="n">
-        <v>120.97</v>
+        <v>129.44</v>
       </c>
       <c r="U12" t="n">
-        <v>115</v>
+        <v>121.66</v>
       </c>
       <c r="V12" t="n">
-        <v>9.16</v>
+        <v>10.83</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
@@ -1392,68 +1392,68 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>312.99</v>
+        <v>344.29</v>
       </c>
       <c r="D13" t="n">
-        <v>1.33</v>
+        <v>10</v>
       </c>
       <c r="E13" t="n">
-        <v>306.1</v>
+        <v>315.42</v>
       </c>
       <c r="F13" t="n">
-        <v>303.5</v>
+        <v>309.04</v>
       </c>
       <c r="G13" t="n">
-        <v>282.76</v>
+        <v>287.63</v>
       </c>
       <c r="H13" t="n">
-        <v>10.056</v>
+        <v>12.853</v>
       </c>
       <c r="I13" t="n">
-        <v>6.443</v>
+        <v>7.607</v>
       </c>
       <c r="J13" t="n">
-        <v>66.11</v>
+        <v>77.41</v>
       </c>
       <c r="K13" t="n">
-        <v>69.70999999999999</v>
+        <v>72.27</v>
       </c>
       <c r="L13" t="n">
-        <v>58.92</v>
+        <v>87.67</v>
       </c>
       <c r="M13" t="n">
-        <v>72.17</v>
+        <v>86.51000000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>64.76000000000001</v>
+        <v>74.84999999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>58.54</v>
+        <v>64.5</v>
       </c>
       <c r="P13" t="n">
-        <v>58.8</v>
+        <v>42.34</v>
       </c>
       <c r="Q13" t="n">
-        <v>40.24</v>
+        <v>41.1</v>
       </c>
       <c r="R13" t="n">
-        <v>1.46</v>
+        <v>1.03</v>
       </c>
       <c r="S13" t="n">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="T13" t="n">
-        <v>321</v>
+        <v>344.29</v>
       </c>
       <c r="U13" t="n">
-        <v>306.48</v>
+        <v>330</v>
       </c>
       <c r="V13" t="n">
-        <v>8.800000000000001</v>
+        <v>6.34</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
@@ -1469,68 +1469,68 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>52.27</v>
+        <v>62.72</v>
       </c>
       <c r="D14" t="n">
-        <v>1.69</v>
+        <v>19.99</v>
       </c>
       <c r="E14" t="n">
-        <v>50.46</v>
+        <v>53.73</v>
       </c>
       <c r="F14" t="n">
-        <v>49.55</v>
+        <v>50.91</v>
       </c>
       <c r="G14" t="n">
-        <v>48.13</v>
+        <v>49.16</v>
       </c>
       <c r="H14" t="n">
-        <v>1.914</v>
+        <v>2.812</v>
       </c>
       <c r="I14" t="n">
-        <v>1.805</v>
+        <v>2.001</v>
       </c>
       <c r="J14" t="n">
-        <v>70.27</v>
+        <v>80.18000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>60.42</v>
+        <v>67.01000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>89.98999999999999</v>
+        <v>106.54</v>
       </c>
       <c r="M14" t="n">
-        <v>69.09999999999999</v>
+        <v>88.12</v>
       </c>
       <c r="N14" t="n">
-        <v>62.64</v>
+        <v>77.2</v>
       </c>
       <c r="O14" t="n">
-        <v>60.44</v>
+        <v>69.29000000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>39.04</v>
+        <v>46.32</v>
       </c>
       <c r="Q14" t="n">
-        <v>27.96</v>
+        <v>29.2</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4</v>
+        <v>1.59</v>
       </c>
       <c r="S14" t="n">
-        <v>51.41</v>
+        <v>56.63</v>
       </c>
       <c r="T14" t="n">
-        <v>53.58</v>
+        <v>62.72</v>
       </c>
       <c r="U14" t="n">
-        <v>49.8</v>
+        <v>56.6</v>
       </c>
       <c r="V14" t="n">
-        <v>19.48</v>
+        <v>23.12</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
@@ -1546,68 +1546,68 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>27.72</v>
+        <v>30.06</v>
       </c>
       <c r="D15" t="n">
-        <v>-3.14</v>
+        <v>8.44</v>
       </c>
       <c r="E15" t="n">
-        <v>25.82</v>
+        <v>27.18</v>
       </c>
       <c r="F15" t="n">
-        <v>25.06</v>
+        <v>25.63</v>
       </c>
       <c r="G15" t="n">
-        <v>23.32</v>
+        <v>23.86</v>
       </c>
       <c r="H15" t="n">
-        <v>1.441</v>
+        <v>1.737</v>
       </c>
       <c r="I15" t="n">
-        <v>1.013</v>
+        <v>1.153</v>
       </c>
       <c r="J15" t="n">
-        <v>74.38</v>
+        <v>78.81999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>70.63</v>
+        <v>73.36</v>
       </c>
       <c r="L15" t="n">
-        <v>81.89</v>
+        <v>89.75</v>
       </c>
       <c r="M15" t="n">
-        <v>74.06</v>
+        <v>81.92</v>
       </c>
       <c r="N15" t="n">
-        <v>69.83</v>
+        <v>75.56</v>
       </c>
       <c r="O15" t="n">
-        <v>64.69</v>
+        <v>68.65000000000001</v>
       </c>
       <c r="P15" t="n">
-        <v>51.16</v>
+        <v>64.44</v>
       </c>
       <c r="Q15" t="n">
-        <v>38.08</v>
+        <v>39.65</v>
       </c>
       <c r="R15" t="n">
-        <v>1.34</v>
+        <v>1.63</v>
       </c>
       <c r="S15" t="n">
-        <v>28.48</v>
+        <v>29.15</v>
       </c>
       <c r="T15" t="n">
-        <v>28.56</v>
+        <v>31.11</v>
       </c>
       <c r="U15" t="n">
-        <v>27.51</v>
+        <v>28.68</v>
       </c>
       <c r="V15" t="n">
-        <v>13.87</v>
+        <v>17.47</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
@@ -1623,68 +1623,68 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>15.96</v>
+        <v>15.95</v>
       </c>
       <c r="D16" t="n">
-        <v>0.19</v>
+        <v>-0.06</v>
       </c>
       <c r="E16" t="n">
-        <v>15.76</v>
+        <v>15.88</v>
       </c>
       <c r="F16" t="n">
-        <v>15.8</v>
+        <v>15.81</v>
       </c>
       <c r="G16" t="n">
-        <v>15.7</v>
+        <v>15.72</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.127</v>
+        <v>-0.111</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.144</v>
+        <v>-0.14</v>
       </c>
       <c r="J16" t="n">
-        <v>71.26000000000001</v>
+        <v>73.28</v>
       </c>
       <c r="K16" t="n">
-        <v>64.87</v>
+        <v>67.67</v>
       </c>
       <c r="L16" t="n">
-        <v>84.05</v>
+        <v>84.48999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>56.17</v>
+        <v>55.64</v>
       </c>
       <c r="N16" t="n">
-        <v>50.13</v>
+        <v>49.97</v>
       </c>
       <c r="O16" t="n">
-        <v>50.38</v>
+        <v>50.14</v>
       </c>
       <c r="P16" t="n">
-        <v>4.47</v>
+        <v>7.28</v>
       </c>
       <c r="Q16" t="n">
-        <v>7.12</v>
+        <v>6.89</v>
       </c>
       <c r="R16" t="n">
-        <v>0.63</v>
+        <v>1.06</v>
       </c>
       <c r="S16" t="n">
-        <v>15.9</v>
+        <v>16.01</v>
       </c>
       <c r="T16" t="n">
-        <v>16.22</v>
+        <v>16.15</v>
       </c>
       <c r="U16" t="n">
-        <v>15.85</v>
+        <v>15.78</v>
       </c>
       <c r="V16" t="n">
-        <v>2.47</v>
+        <v>4.02</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
@@ -1700,68 +1700,68 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>36.91</v>
+        <v>38.5</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.83</v>
+        <v>4.31</v>
       </c>
       <c r="E17" t="n">
-        <v>37.19</v>
+        <v>37.31</v>
       </c>
       <c r="F17" t="n">
-        <v>38.28</v>
+        <v>38.04</v>
       </c>
       <c r="G17" t="n">
-        <v>38.67</v>
+        <v>38.77</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.211</v>
+        <v>-0.167</v>
       </c>
       <c r="I17" t="n">
-        <v>0.18</v>
+        <v>0.106</v>
       </c>
       <c r="J17" t="n">
-        <v>17.03</v>
+        <v>30.62</v>
       </c>
       <c r="K17" t="n">
-        <v>24.23</v>
+        <v>26.36</v>
       </c>
       <c r="L17" t="n">
-        <v>2.63</v>
+        <v>39.13</v>
       </c>
       <c r="M17" t="n">
-        <v>36.33</v>
+        <v>54.09</v>
       </c>
       <c r="N17" t="n">
-        <v>43.48</v>
+        <v>50.74</v>
       </c>
       <c r="O17" t="n">
-        <v>47.91</v>
+        <v>51.01</v>
       </c>
       <c r="P17" t="n">
-        <v>28.15</v>
+        <v>51.55</v>
       </c>
       <c r="Q17" t="n">
-        <v>58.73</v>
+        <v>58.69</v>
       </c>
       <c r="R17" t="n">
-        <v>0.48</v>
+        <v>0.88</v>
       </c>
       <c r="S17" t="n">
-        <v>37.2</v>
+        <v>37.55</v>
       </c>
       <c r="T17" t="n">
-        <v>37.22</v>
+        <v>39</v>
       </c>
       <c r="U17" t="n">
-        <v>36.58</v>
+        <v>37.54</v>
       </c>
       <c r="V17" t="n">
-        <v>3.92</v>
+        <v>7.18</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
@@ -1777,68 +1777,68 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>16</v>
+        <v>17.3</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.74</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>16.66</v>
+        <v>16.56</v>
       </c>
       <c r="F18" t="n">
-        <v>17.69</v>
+        <v>17.53</v>
       </c>
       <c r="G18" t="n">
-        <v>17.72</v>
+        <v>17.76</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.28</v>
+        <v>-0.264</v>
       </c>
       <c r="I18" t="n">
-        <v>0.003</v>
+        <v>-0.052</v>
       </c>
       <c r="J18" t="n">
-        <v>18.02</v>
+        <v>25.92</v>
       </c>
       <c r="K18" t="n">
-        <v>32.2</v>
+        <v>30.11</v>
       </c>
       <c r="L18" t="n">
-        <v>-10.35</v>
+        <v>17.55</v>
       </c>
       <c r="M18" t="n">
-        <v>28.66</v>
+        <v>49.98</v>
       </c>
       <c r="N18" t="n">
-        <v>38.41</v>
+        <v>48.08</v>
       </c>
       <c r="O18" t="n">
-        <v>45.42</v>
+        <v>49.77</v>
       </c>
       <c r="P18" t="n">
-        <v>159.53</v>
+        <v>301.65</v>
       </c>
       <c r="Q18" t="n">
-        <v>235.67</v>
+        <v>239.62</v>
       </c>
       <c r="R18" t="n">
-        <v>0.68</v>
+        <v>1.26</v>
       </c>
       <c r="S18" t="n">
-        <v>16.3</v>
+        <v>16.31</v>
       </c>
       <c r="T18" t="n">
-        <v>16.66</v>
+        <v>17.98</v>
       </c>
       <c r="U18" t="n">
-        <v>15.83</v>
+        <v>16.31</v>
       </c>
       <c r="V18" t="n">
-        <v>6.92</v>
+        <v>13.09</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
@@ -1854,68 +1854,68 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>48.86</v>
+        <v>52.07</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.63</v>
+        <v>6.57</v>
       </c>
       <c r="E19" t="n">
-        <v>50.14</v>
+        <v>50.38</v>
       </c>
       <c r="F19" t="n">
-        <v>51.82</v>
+        <v>51.76</v>
       </c>
       <c r="G19" t="n">
-        <v>50.75</v>
+        <v>50.96</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.343</v>
+        <v>-0.231</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.156</v>
+        <v>-0.181</v>
       </c>
       <c r="J19" t="n">
-        <v>13.99</v>
+        <v>21.97</v>
       </c>
       <c r="K19" t="n">
-        <v>27.83</v>
+        <v>25.88</v>
       </c>
       <c r="L19" t="n">
-        <v>-13.71</v>
+        <v>14.16</v>
       </c>
       <c r="M19" t="n">
-        <v>32.07</v>
+        <v>56.95</v>
       </c>
       <c r="N19" t="n">
-        <v>42.02</v>
+        <v>52.57</v>
       </c>
       <c r="O19" t="n">
-        <v>46.26</v>
+        <v>50.58</v>
       </c>
       <c r="P19" t="n">
-        <v>40.74</v>
+        <v>73.45999999999999</v>
       </c>
       <c r="Q19" t="n">
-        <v>53.61</v>
+        <v>54.03</v>
       </c>
       <c r="R19" t="n">
-        <v>0.76</v>
+        <v>1.36</v>
       </c>
       <c r="S19" t="n">
-        <v>50.21</v>
+        <v>49.85</v>
       </c>
       <c r="T19" t="n">
-        <v>50.49</v>
+        <v>53.4</v>
       </c>
       <c r="U19" t="n">
-        <v>48.7</v>
+        <v>49.85</v>
       </c>
       <c r="V19" t="n">
-        <v>3.25</v>
+        <v>5.86</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
@@ -1931,68 +1931,68 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>47.79</v>
+        <v>49.48</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5600000000000001</v>
+        <v>3.54</v>
       </c>
       <c r="E20" t="n">
-        <v>48.78</v>
+        <v>48.86</v>
       </c>
       <c r="F20" t="n">
-        <v>48.83</v>
+        <v>48.95</v>
       </c>
       <c r="G20" t="n">
-        <v>48</v>
+        <v>48.18</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.239</v>
+        <v>-0.153</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.443</v>
+        <v>-0.396</v>
       </c>
       <c r="J20" t="n">
-        <v>48.06</v>
+        <v>57.93</v>
       </c>
       <c r="K20" t="n">
-        <v>62.17</v>
+        <v>60.76</v>
       </c>
       <c r="L20" t="n">
-        <v>19.82</v>
+        <v>52.27</v>
       </c>
       <c r="M20" t="n">
-        <v>37.4</v>
+        <v>60.31</v>
       </c>
       <c r="N20" t="n">
-        <v>43.8</v>
+        <v>54.96</v>
       </c>
       <c r="O20" t="n">
-        <v>43.67</v>
+        <v>48.76</v>
       </c>
       <c r="P20" t="n">
-        <v>38.02</v>
+        <v>70.81</v>
       </c>
       <c r="Q20" t="n">
-        <v>35.1</v>
+        <v>37.38</v>
       </c>
       <c r="R20" t="n">
-        <v>1.08</v>
+        <v>1.89</v>
       </c>
       <c r="S20" t="n">
-        <v>47.98</v>
+        <v>48.35</v>
       </c>
       <c r="T20" t="n">
-        <v>48.41</v>
+        <v>50.19</v>
       </c>
       <c r="U20" t="n">
-        <v>47.69</v>
+        <v>48.34</v>
       </c>
       <c r="V20" t="n">
-        <v>1.74</v>
+        <v>3.23</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
@@ -2008,68 +2008,68 @@
         </is>
       </c>
       <c r="C21" t="n">
+        <v>18.05</v>
+      </c>
+      <c r="D21" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="E21" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="F21" t="n">
+        <v>18.05</v>
+      </c>
+      <c r="G21" t="n">
         <v>17.12</v>
       </c>
-      <c r="D21" t="n">
-        <v>-1.55</v>
-      </c>
-      <c r="E21" t="n">
+      <c r="H21" t="n">
+        <v>0.468</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.491</v>
+      </c>
+      <c r="J21" t="n">
+        <v>27.95</v>
+      </c>
+      <c r="K21" t="n">
+        <v>33.34</v>
+      </c>
+      <c r="L21" t="n">
         <v>17.17</v>
       </c>
-      <c r="F21" t="n">
-        <v>18.04</v>
-      </c>
-      <c r="G21" t="n">
-        <v>16.91</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.454</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="J21" t="n">
-        <v>22.57</v>
-      </c>
-      <c r="K21" t="n">
-        <v>36.03</v>
-      </c>
-      <c r="L21" t="n">
-        <v>-4.35</v>
-      </c>
       <c r="M21" t="n">
-        <v>45.15</v>
+        <v>57.91</v>
       </c>
       <c r="N21" t="n">
-        <v>50.87</v>
+        <v>56.68</v>
       </c>
       <c r="O21" t="n">
-        <v>51.6</v>
+        <v>54.3</v>
       </c>
       <c r="P21" t="n">
-        <v>288.25</v>
+        <v>464.22</v>
       </c>
       <c r="Q21" t="n">
-        <v>519.15</v>
+        <v>527.72</v>
       </c>
       <c r="R21" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.88</v>
       </c>
       <c r="S21" t="n">
-        <v>17.22</v>
+        <v>17.7</v>
       </c>
       <c r="T21" t="n">
-        <v>17.58</v>
+        <v>18.31</v>
       </c>
       <c r="U21" t="n">
-        <v>17.02</v>
+        <v>17.7</v>
       </c>
       <c r="V21" t="n">
-        <v>8.289999999999999</v>
+        <v>13.35</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
@@ -2085,68 +2085,68 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>63.91</v>
+        <v>65.23999999999999</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.03</v>
+        <v>2.08</v>
       </c>
       <c r="E22" t="n">
-        <v>64.12</v>
+        <v>64.34999999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>63.48</v>
+        <v>63.87</v>
       </c>
       <c r="G22" t="n">
-        <v>61.57</v>
+        <v>61.95</v>
       </c>
       <c r="H22" t="n">
-        <v>0.226</v>
+        <v>0.36</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.375</v>
+        <v>-0.246</v>
       </c>
       <c r="J22" t="n">
-        <v>69.15000000000001</v>
+        <v>72.77</v>
       </c>
       <c r="K22" t="n">
-        <v>74.29000000000001</v>
+        <v>73.78</v>
       </c>
       <c r="L22" t="n">
-        <v>58.88</v>
+        <v>70.73999999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>56.79</v>
+        <v>66.33</v>
       </c>
       <c r="N22" t="n">
-        <v>54.53</v>
+        <v>59.15</v>
       </c>
       <c r="O22" t="n">
-        <v>49.33</v>
+        <v>51.42</v>
       </c>
       <c r="P22" t="n">
-        <v>10.7</v>
+        <v>18.18</v>
       </c>
       <c r="Q22" t="n">
-        <v>11.66</v>
+        <v>12.12</v>
       </c>
       <c r="R22" t="n">
-        <v>0.92</v>
+        <v>1.5</v>
       </c>
       <c r="S22" t="n">
-        <v>63.67</v>
+        <v>64.79000000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>64.09999999999999</v>
+        <v>66.45</v>
       </c>
       <c r="U22" t="n">
-        <v>62.88</v>
+        <v>64.78</v>
       </c>
       <c r="V22" t="n">
-        <v>2.9</v>
+        <v>4.93</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
@@ -2162,68 +2162,68 @@
         </is>
       </c>
       <c r="C23" t="n">
+        <v>24.95</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="E23" t="n">
+        <v>24.49</v>
+      </c>
+      <c r="F23" t="n">
+        <v>25.89</v>
+      </c>
+      <c r="G23" t="n">
+        <v>26.36</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-1.032</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-0.851</v>
+      </c>
+      <c r="J23" t="n">
+        <v>18.55</v>
+      </c>
+      <c r="K23" t="n">
+        <v>18.97</v>
+      </c>
+      <c r="L23" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="M23" t="n">
+        <v>41.66</v>
+      </c>
+      <c r="N23" t="n">
+        <v>41</v>
+      </c>
+      <c r="O23" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="P23" t="n">
+        <v>105.07</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>156.65</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="S23" t="n">
         <v>24.58</v>
       </c>
-      <c r="D23" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="E23" t="n">
-        <v>24.76</v>
-      </c>
-      <c r="F23" t="n">
-        <v>26.09</v>
-      </c>
-      <c r="G23" t="n">
-        <v>26.46</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-1.04</v>
-      </c>
-      <c r="I23" t="n">
-        <v>-0.802</v>
-      </c>
-      <c r="J23" t="n">
-        <v>14.42</v>
-      </c>
-      <c r="K23" t="n">
-        <v>19.19</v>
-      </c>
-      <c r="L23" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="M23" t="n">
-        <v>36.27</v>
-      </c>
-      <c r="N23" t="n">
-        <v>38.58</v>
-      </c>
-      <c r="O23" t="n">
-        <v>41.76</v>
-      </c>
-      <c r="P23" t="n">
-        <v>95.17</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>157.59</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="S23" t="n">
-        <v>24.36</v>
-      </c>
       <c r="T23" t="n">
-        <v>24.74</v>
+        <v>25.34</v>
       </c>
       <c r="U23" t="n">
-        <v>24.25</v>
+        <v>24.58</v>
       </c>
       <c r="V23" t="n">
-        <v>5.99</v>
+        <v>6.61</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
@@ -2239,68 +2239,68 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>27.55</v>
+        <v>27.94</v>
       </c>
       <c r="D24" t="n">
-        <v>7.07</v>
+        <v>1.42</v>
       </c>
       <c r="E24" t="n">
-        <v>26.16</v>
+        <v>26.65</v>
       </c>
       <c r="F24" t="n">
-        <v>26.08</v>
+        <v>26.34</v>
       </c>
       <c r="G24" t="n">
-        <v>25.16</v>
+        <v>25.35</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.08</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.356</v>
+        <v>-0.282</v>
       </c>
       <c r="J24" t="n">
-        <v>61.36</v>
+        <v>70.06999999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>60.37</v>
+        <v>63.61</v>
       </c>
       <c r="L24" t="n">
-        <v>63.33</v>
+        <v>83.01000000000001</v>
       </c>
       <c r="M24" t="n">
-        <v>69.83</v>
+        <v>72.59</v>
       </c>
       <c r="N24" t="n">
-        <v>59.72</v>
+        <v>61.59</v>
       </c>
       <c r="O24" t="n">
-        <v>53.92</v>
+        <v>54.59</v>
       </c>
       <c r="P24" t="n">
-        <v>349.36</v>
+        <v>305.05</v>
       </c>
       <c r="Q24" t="n">
-        <v>211.07</v>
+        <v>214.59</v>
       </c>
       <c r="R24" t="n">
-        <v>1.66</v>
+        <v>1.42</v>
       </c>
       <c r="S24" t="n">
-        <v>26.51</v>
+        <v>28</v>
       </c>
       <c r="T24" t="n">
-        <v>28.18</v>
+        <v>28.35</v>
       </c>
       <c r="U24" t="n">
-        <v>26.2</v>
+        <v>27.7</v>
       </c>
       <c r="V24" t="n">
-        <v>10.39</v>
+        <v>9.07</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
@@ -2316,68 +2316,68 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>178.31</v>
+        <v>190.01</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.09</v>
+        <v>6.56</v>
       </c>
       <c r="E25" t="n">
-        <v>182.64</v>
+        <v>182.83</v>
       </c>
       <c r="F25" t="n">
-        <v>182.81</v>
+        <v>183.45</v>
       </c>
       <c r="G25" t="n">
-        <v>173.74</v>
+        <v>175.72</v>
       </c>
       <c r="H25" t="n">
-        <v>12.339</v>
+        <v>12.325</v>
       </c>
       <c r="I25" t="n">
-        <v>14.113</v>
+        <v>13.764</v>
       </c>
       <c r="J25" t="n">
-        <v>50.16</v>
+        <v>60.35</v>
       </c>
       <c r="K25" t="n">
-        <v>56.39</v>
+        <v>57.71</v>
       </c>
       <c r="L25" t="n">
-        <v>37.7</v>
+        <v>65.63</v>
       </c>
       <c r="M25" t="n">
-        <v>47.86</v>
+        <v>63.27</v>
       </c>
       <c r="N25" t="n">
-        <v>57.25</v>
+        <v>63.93</v>
       </c>
       <c r="O25" t="n">
-        <v>61.32</v>
+        <v>64.81</v>
       </c>
       <c r="P25" t="n">
-        <v>6.76</v>
+        <v>8.26</v>
       </c>
       <c r="Q25" t="n">
-        <v>7.49</v>
+        <v>7.56</v>
       </c>
       <c r="R25" t="n">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="S25" t="n">
-        <v>184.88</v>
+        <v>182.01</v>
       </c>
       <c r="T25" t="n">
-        <v>187.5</v>
+        <v>195</v>
       </c>
       <c r="U25" t="n">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="V25" t="n">
-        <v>7.43</v>
+        <v>9.08</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
@@ -2393,68 +2393,68 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>33.3</v>
+        <v>34.21</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.46</v>
+        <v>2.73</v>
       </c>
       <c r="E26" t="n">
-        <v>33.65</v>
+        <v>33.63</v>
       </c>
       <c r="F26" t="n">
-        <v>34.34</v>
+        <v>34.29</v>
       </c>
       <c r="G26" t="n">
-        <v>34.14</v>
+        <v>34.19</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.238</v>
+        <v>-0.216</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.191</v>
+        <v>-0.207</v>
       </c>
       <c r="J26" t="n">
-        <v>29.92</v>
+        <v>36.86</v>
       </c>
       <c r="K26" t="n">
-        <v>37.46</v>
+        <v>37.26</v>
       </c>
       <c r="L26" t="n">
-        <v>14.82</v>
+        <v>36.05</v>
       </c>
       <c r="M26" t="n">
-        <v>39.46</v>
+        <v>52.01</v>
       </c>
       <c r="N26" t="n">
-        <v>43.87</v>
+        <v>49.9</v>
       </c>
       <c r="O26" t="n">
-        <v>45.43</v>
+        <v>47.94</v>
       </c>
       <c r="P26" t="n">
-        <v>240.39</v>
+        <v>399.07</v>
       </c>
       <c r="Q26" t="n">
-        <v>255.76</v>
+        <v>262.77</v>
       </c>
       <c r="R26" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.52</v>
       </c>
       <c r="S26" t="n">
-        <v>33.7</v>
+        <v>33.5</v>
       </c>
       <c r="T26" t="n">
-        <v>34.02</v>
+        <v>34.38</v>
       </c>
       <c r="U26" t="n">
-        <v>33.08</v>
+        <v>33.21</v>
       </c>
       <c r="V26" t="n">
-        <v>1.17</v>
+        <v>1.94</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
@@ -2470,68 +2470,68 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>5.37</v>
+        <v>5.48</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.74</v>
+        <v>2.05</v>
       </c>
       <c r="E27" t="n">
-        <v>5.56</v>
+        <v>5.48</v>
       </c>
       <c r="F27" t="n">
-        <v>5.87</v>
+        <v>5.78</v>
       </c>
       <c r="G27" t="n">
-        <v>6.05</v>
+        <v>6.01</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.25</v>
+        <v>-0.259</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.174</v>
+        <v>-0.192</v>
       </c>
       <c r="J27" t="n">
-        <v>15.44</v>
+        <v>19.63</v>
       </c>
       <c r="K27" t="n">
-        <v>21.2</v>
+        <v>20.68</v>
       </c>
       <c r="L27" t="n">
-        <v>3.91</v>
+        <v>17.53</v>
       </c>
       <c r="M27" t="n">
-        <v>21.65</v>
+        <v>31.85</v>
       </c>
       <c r="N27" t="n">
-        <v>30.53</v>
+        <v>34.8</v>
       </c>
       <c r="O27" t="n">
-        <v>38.49</v>
+        <v>40.09</v>
       </c>
       <c r="P27" t="n">
-        <v>203.51</v>
+        <v>266.95</v>
       </c>
       <c r="Q27" t="n">
-        <v>226.55</v>
+        <v>228.34</v>
       </c>
       <c r="R27" t="n">
-        <v>0.9</v>
+        <v>1.17</v>
       </c>
       <c r="S27" t="n">
-        <v>5.38</v>
+        <v>5.4</v>
       </c>
       <c r="T27" t="n">
-        <v>5.4</v>
+        <v>5.49</v>
       </c>
       <c r="U27" t="n">
-        <v>5.3</v>
+        <v>5.31</v>
       </c>
       <c r="V27" t="n">
-        <v>1.77</v>
+        <v>2.32</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
@@ -2547,68 +2547,68 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>9.949999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D28" t="n">
-        <v>1.43</v>
+        <v>-1.51</v>
       </c>
       <c r="E28" t="n">
-        <v>9.800000000000001</v>
+        <v>9.81</v>
       </c>
       <c r="F28" t="n">
-        <v>9.75</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="G28" t="n">
-        <v>9.550000000000001</v>
+        <v>9.57</v>
       </c>
       <c r="H28" t="n">
-        <v>0.16</v>
+        <v>0.156</v>
       </c>
       <c r="I28" t="n">
-        <v>0.137</v>
+        <v>0.141</v>
       </c>
       <c r="J28" t="n">
-        <v>78.72</v>
+        <v>68.27</v>
       </c>
       <c r="K28" t="n">
-        <v>73.61</v>
+        <v>71.83</v>
       </c>
       <c r="L28" t="n">
-        <v>88.94</v>
+        <v>61.15</v>
       </c>
       <c r="M28" t="n">
-        <v>77.08</v>
+        <v>56.78</v>
       </c>
       <c r="N28" t="n">
-        <v>69.48</v>
+        <v>60.06</v>
       </c>
       <c r="O28" t="n">
-        <v>64.42</v>
+        <v>59.86</v>
       </c>
       <c r="P28" t="n">
-        <v>156.84</v>
+        <v>97.78</v>
       </c>
       <c r="Q28" t="n">
-        <v>83.56999999999999</v>
+        <v>84.14</v>
       </c>
       <c r="R28" t="n">
-        <v>1.88</v>
+        <v>1.16</v>
       </c>
       <c r="S28" t="n">
-        <v>9.800000000000001</v>
+        <v>9.94</v>
       </c>
       <c r="T28" t="n">
-        <v>10</v>
+        <v>9.94</v>
       </c>
       <c r="U28" t="n">
-        <v>9.789999999999999</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="V28" t="n">
-        <v>1.63</v>
+        <v>1.02</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
@@ -2624,68 +2624,68 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>6.14</v>
+        <v>6.4</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="E29" t="n">
-        <v>5.97</v>
+        <v>6.1</v>
       </c>
       <c r="F29" t="n">
-        <v>5.96</v>
+        <v>5.99</v>
       </c>
       <c r="G29" t="n">
-        <v>5.84</v>
+        <v>5.87</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.015</v>
+        <v>0.021</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.053</v>
       </c>
       <c r="J29" t="n">
-        <v>71.88</v>
+        <v>77.88</v>
       </c>
       <c r="K29" t="n">
-        <v>60.59</v>
+        <v>66.34999999999999</v>
       </c>
       <c r="L29" t="n">
-        <v>94.45</v>
+        <v>100.92</v>
       </c>
       <c r="M29" t="n">
-        <v>69.97</v>
+        <v>81.03</v>
       </c>
       <c r="N29" t="n">
-        <v>59.11</v>
+        <v>67.55</v>
       </c>
       <c r="O29" t="n">
-        <v>51.6</v>
+        <v>56.73</v>
       </c>
       <c r="P29" t="n">
-        <v>117.57</v>
+        <v>232.72</v>
       </c>
       <c r="Q29" t="n">
-        <v>113.58</v>
+        <v>118.92</v>
       </c>
       <c r="R29" t="n">
-        <v>1.04</v>
+        <v>1.96</v>
       </c>
       <c r="S29" t="n">
-        <v>6.11</v>
+        <v>6.19</v>
       </c>
       <c r="T29" t="n">
-        <v>6.2</v>
+        <v>6.48</v>
       </c>
       <c r="U29" t="n">
-        <v>6.04</v>
+        <v>6.16</v>
       </c>
       <c r="V29" t="n">
-        <v>0.98</v>
+        <v>1.94</v>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
@@ -2701,68 +2701,68 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>96.63</v>
+        <v>96.79000000000001</v>
       </c>
       <c r="D30" t="n">
-        <v>0.08</v>
+        <v>0.17</v>
       </c>
       <c r="E30" t="n">
-        <v>96.03</v>
+        <v>96.3</v>
       </c>
       <c r="F30" t="n">
-        <v>95.52</v>
+        <v>95.86</v>
       </c>
       <c r="G30" t="n">
-        <v>94.56</v>
+        <v>94.73</v>
       </c>
       <c r="H30" t="n">
-        <v>0.436</v>
+        <v>0.508</v>
       </c>
       <c r="I30" t="n">
-        <v>0.109</v>
+        <v>0.19</v>
       </c>
       <c r="J30" t="n">
-        <v>79.51000000000001</v>
+        <v>82.95</v>
       </c>
       <c r="K30" t="n">
-        <v>71.7</v>
+        <v>75.45</v>
       </c>
       <c r="L30" t="n">
-        <v>95.12</v>
+        <v>97.95</v>
       </c>
       <c r="M30" t="n">
-        <v>73.89</v>
+        <v>75.62</v>
       </c>
       <c r="N30" t="n">
-        <v>64.18000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="O30" t="n">
-        <v>55.61</v>
+        <v>56.24</v>
       </c>
       <c r="P30" t="n">
-        <v>7.44</v>
+        <v>10.38</v>
       </c>
       <c r="Q30" t="n">
-        <v>7.61</v>
+        <v>7.82</v>
       </c>
       <c r="R30" t="n">
-        <v>0.98</v>
+        <v>1.33</v>
       </c>
       <c r="S30" t="n">
-        <v>96.3</v>
+        <v>96.61</v>
       </c>
       <c r="T30" t="n">
-        <v>97.11</v>
+        <v>96.8</v>
       </c>
       <c r="U30" t="n">
-        <v>96.3</v>
+        <v>95.2</v>
       </c>
       <c r="V30" t="n">
-        <v>0.82</v>
+        <v>1.15</v>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
@@ -2778,68 +2778,68 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>37.1</v>
+        <v>37.28</v>
       </c>
       <c r="D31" t="n">
-        <v>0.71</v>
+        <v>0.49</v>
       </c>
       <c r="E31" t="n">
-        <v>36.87</v>
+        <v>37.02</v>
       </c>
       <c r="F31" t="n">
-        <v>36.81</v>
+        <v>36.86</v>
       </c>
       <c r="G31" t="n">
-        <v>37.19</v>
+        <v>37.15</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.126</v>
+        <v>-0.094</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.124</v>
+        <v>-0.12</v>
       </c>
       <c r="J31" t="n">
-        <v>41.04</v>
+        <v>52.71</v>
       </c>
       <c r="K31" t="n">
-        <v>30.72</v>
+        <v>38.05</v>
       </c>
       <c r="L31" t="n">
-        <v>61.69</v>
+        <v>82.02</v>
       </c>
       <c r="M31" t="n">
-        <v>56.1</v>
+        <v>61.9</v>
       </c>
       <c r="N31" t="n">
-        <v>50.56</v>
+        <v>53.26</v>
       </c>
       <c r="O31" t="n">
-        <v>48.72</v>
+        <v>49.77</v>
       </c>
       <c r="P31" t="n">
-        <v>30.5</v>
+        <v>32.17</v>
       </c>
       <c r="Q31" t="n">
-        <v>20.48</v>
+        <v>20.79</v>
       </c>
       <c r="R31" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="S31" t="n">
-        <v>36.77</v>
+        <v>37</v>
       </c>
       <c r="T31" t="n">
-        <v>37.28</v>
+        <v>37.4</v>
       </c>
       <c r="U31" t="n">
-        <v>36.66</v>
+        <v>36.6</v>
       </c>
       <c r="V31" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
@@ -2855,68 +2855,68 @@
         </is>
       </c>
       <c r="C32" t="n">
+        <v>14.79</v>
+      </c>
+      <c r="D32" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="E32" t="n">
+        <v>14.27</v>
+      </c>
+      <c r="F32" t="n">
+        <v>14.76</v>
+      </c>
+      <c r="G32" t="n">
+        <v>14.64</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.508</v>
+      </c>
+      <c r="J32" t="n">
+        <v>43.26</v>
+      </c>
+      <c r="K32" t="n">
+        <v>38.93</v>
+      </c>
+      <c r="L32" t="n">
+        <v>51.91</v>
+      </c>
+      <c r="M32" t="n">
+        <v>53.16</v>
+      </c>
+      <c r="N32" t="n">
+        <v>53.33</v>
+      </c>
+      <c r="O32" t="n">
+        <v>55.05</v>
+      </c>
+      <c r="P32" t="n">
+        <v>49.96</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>67.48</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="S32" t="n">
         <v>14.3</v>
       </c>
-      <c r="D32" t="n">
-        <v>-3.83</v>
-      </c>
-      <c r="E32" t="n">
-        <v>14.19</v>
-      </c>
-      <c r="F32" t="n">
-        <v>14.85</v>
-      </c>
-      <c r="G32" t="n">
-        <v>14.57</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0.341</v>
-      </c>
-      <c r="I32" t="n">
-        <v>0.552</v>
-      </c>
-      <c r="J32" t="n">
-        <v>36.19</v>
-      </c>
-      <c r="K32" t="n">
-        <v>36.76</v>
-      </c>
-      <c r="L32" t="n">
-        <v>35.03</v>
-      </c>
-      <c r="M32" t="n">
-        <v>45.79</v>
-      </c>
-      <c r="N32" t="n">
-        <v>49.8</v>
-      </c>
-      <c r="O32" t="n">
-        <v>53.24</v>
-      </c>
-      <c r="P32" t="n">
-        <v>56.64</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>69.55</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="S32" t="n">
-        <v>15.2</v>
-      </c>
       <c r="T32" t="n">
-        <v>15.38</v>
+        <v>15</v>
       </c>
       <c r="U32" t="n">
-        <v>14.13</v>
+        <v>14.01</v>
       </c>
       <c r="V32" t="n">
-        <v>13.33</v>
+        <v>11.76</v>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
@@ -2932,68 +2932,68 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>15.21</v>
+        <v>16.28</v>
       </c>
       <c r="D33" t="n">
-        <v>-8.59</v>
+        <v>7.03</v>
       </c>
       <c r="E33" t="n">
-        <v>16.46</v>
+        <v>16.3</v>
       </c>
       <c r="F33" t="n">
-        <v>18.24</v>
+        <v>17.8</v>
       </c>
       <c r="G33" t="n">
-        <v>19.01</v>
+        <v>18.84</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.732</v>
+        <v>-0.802</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.252</v>
+        <v>-0.363</v>
       </c>
       <c r="J33" t="n">
-        <v>12.69</v>
+        <v>15.64</v>
       </c>
       <c r="K33" t="n">
-        <v>23.03</v>
+        <v>20.57</v>
       </c>
       <c r="L33" t="n">
-        <v>-8</v>
+        <v>5.78</v>
       </c>
       <c r="M33" t="n">
-        <v>19.7</v>
+        <v>36.19</v>
       </c>
       <c r="N33" t="n">
-        <v>28.27</v>
+        <v>37.22</v>
       </c>
       <c r="O33" t="n">
-        <v>36.42</v>
+        <v>41.14</v>
       </c>
       <c r="P33" t="n">
-        <v>127.56</v>
+        <v>114.97</v>
       </c>
       <c r="Q33" t="n">
-        <v>96.05</v>
+        <v>96.51000000000001</v>
       </c>
       <c r="R33" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="S33" t="n">
-        <v>16.11</v>
+        <v>15.84</v>
       </c>
       <c r="T33" t="n">
-        <v>16.33</v>
+        <v>16.65</v>
       </c>
       <c r="U33" t="n">
-        <v>15.1</v>
+        <v>15.82</v>
       </c>
       <c r="V33" t="n">
-        <v>6.98</v>
+        <v>6.29</v>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
@@ -3009,68 +3009,68 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>32.82</v>
+        <v>32.42</v>
       </c>
       <c r="D34" t="n">
-        <v>-2.06</v>
+        <v>-1.22</v>
       </c>
       <c r="E34" t="n">
-        <v>32.23</v>
+        <v>32.48</v>
       </c>
       <c r="F34" t="n">
-        <v>32.17</v>
+        <v>32.18</v>
       </c>
       <c r="G34" t="n">
-        <v>32.63</v>
+        <v>32.55</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.569</v>
+        <v>-0.532</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.8169999999999999</v>
+        <v>-0.766</v>
       </c>
       <c r="J34" t="n">
-        <v>58.68</v>
+        <v>57.79</v>
       </c>
       <c r="K34" t="n">
-        <v>43.68</v>
+        <v>48.38</v>
       </c>
       <c r="L34" t="n">
-        <v>88.68000000000001</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="M34" t="n">
-        <v>55.8</v>
+        <v>50.17</v>
       </c>
       <c r="N34" t="n">
-        <v>50.09</v>
+        <v>47.83</v>
       </c>
       <c r="O34" t="n">
-        <v>45.34</v>
+        <v>44.14</v>
       </c>
       <c r="P34" t="n">
-        <v>51.79</v>
+        <v>78.97</v>
       </c>
       <c r="Q34" t="n">
-        <v>56.15</v>
+        <v>57.01</v>
       </c>
       <c r="R34" t="n">
-        <v>0.92</v>
+        <v>1.39</v>
       </c>
       <c r="S34" t="n">
-        <v>33.39</v>
+        <v>32.93</v>
       </c>
       <c r="T34" t="n">
-        <v>33.58</v>
+        <v>33</v>
       </c>
       <c r="U34" t="n">
-        <v>32.68</v>
+        <v>31.84</v>
       </c>
       <c r="V34" t="n">
-        <v>2.72</v>
+        <v>4.16</v>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
@@ -3086,68 +3086,68 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>48</v>
+        <v>47.73</v>
       </c>
       <c r="D35" t="n">
-        <v>0.04</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="E35" t="n">
-        <v>47.62</v>
+        <v>47.73</v>
       </c>
       <c r="F35" t="n">
-        <v>46.77</v>
+        <v>46.99</v>
       </c>
       <c r="G35" t="n">
-        <v>46.73</v>
+        <v>46.74</v>
       </c>
       <c r="H35" t="n">
-        <v>0.286</v>
+        <v>0.316</v>
       </c>
       <c r="I35" t="n">
-        <v>0.105</v>
+        <v>0.146</v>
       </c>
       <c r="J35" t="n">
-        <v>77.8</v>
+        <v>75.91</v>
       </c>
       <c r="K35" t="n">
-        <v>69.06999999999999</v>
+        <v>71.34999999999999</v>
       </c>
       <c r="L35" t="n">
-        <v>95.28</v>
+        <v>85.04000000000001</v>
       </c>
       <c r="M35" t="n">
-        <v>69.8</v>
+        <v>62.24</v>
       </c>
       <c r="N35" t="n">
-        <v>60.35</v>
+        <v>57.52</v>
       </c>
       <c r="O35" t="n">
-        <v>57.3</v>
+        <v>56.08</v>
       </c>
       <c r="P35" t="n">
-        <v>30.53</v>
+        <v>30.82</v>
       </c>
       <c r="Q35" t="n">
-        <v>30.22</v>
+        <v>30.15</v>
       </c>
       <c r="R35" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="S35" t="n">
-        <v>48.1</v>
+        <v>47.6</v>
       </c>
       <c r="T35" t="n">
-        <v>48.18</v>
+        <v>47.99</v>
       </c>
       <c r="U35" t="n">
-        <v>47.52</v>
+        <v>46.67</v>
       </c>
       <c r="V35" t="n">
         <v>0.19</v>
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
@@ -3163,68 +3163,68 @@
         </is>
       </c>
       <c r="C36" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="E36" t="n">
         <v>4.64</v>
       </c>
-      <c r="D36" t="n">
-        <v>-0.85</v>
-      </c>
-      <c r="E36" t="n">
-        <v>4.6</v>
-      </c>
       <c r="F36" t="n">
-        <v>4.75</v>
+        <v>4.73</v>
       </c>
       <c r="G36" t="n">
         <v>4.76</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.12</v>
+        <v>-0.116</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.126</v>
+        <v>-0.125</v>
       </c>
       <c r="J36" t="n">
-        <v>33.44</v>
+        <v>33.4</v>
       </c>
       <c r="K36" t="n">
-        <v>38.77</v>
+        <v>36.98</v>
       </c>
       <c r="L36" t="n">
-        <v>22.77</v>
+        <v>26.25</v>
       </c>
       <c r="M36" t="n">
-        <v>41.56</v>
+        <v>43.97</v>
       </c>
       <c r="N36" t="n">
-        <v>41.72</v>
+        <v>42.77</v>
       </c>
       <c r="O36" t="n">
-        <v>43.12</v>
+        <v>43.51</v>
       </c>
       <c r="P36" t="n">
-        <v>21.43</v>
+        <v>28.07</v>
       </c>
       <c r="Q36" t="n">
-        <v>29.24</v>
+        <v>29.5</v>
       </c>
       <c r="R36" t="n">
-        <v>0.73</v>
+        <v>0.95</v>
       </c>
       <c r="S36" t="n">
-        <v>4.66</v>
+        <v>4.62</v>
       </c>
       <c r="T36" t="n">
-        <v>4.68</v>
+        <v>4.7</v>
       </c>
       <c r="U36" t="n">
-        <v>4.56</v>
+        <v>4.57</v>
       </c>
       <c r="V36" t="n">
-        <v>1.22</v>
+        <v>1.6</v>
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
@@ -3240,68 +3240,68 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>32.73</v>
+        <v>33.14</v>
       </c>
       <c r="D37" t="n">
-        <v>0.4</v>
+        <v>1.25</v>
       </c>
       <c r="E37" t="n">
-        <v>32.29</v>
+        <v>32.44</v>
       </c>
       <c r="F37" t="n">
-        <v>32.46</v>
+        <v>32.52</v>
       </c>
       <c r="G37" t="n">
-        <v>32.62</v>
+        <v>32.69</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.362</v>
+        <v>-0.294</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.353</v>
+        <v>-0.344</v>
       </c>
       <c r="J37" t="n">
-        <v>46.95</v>
+        <v>61.68</v>
       </c>
       <c r="K37" t="n">
-        <v>34.33</v>
+        <v>43.45</v>
       </c>
       <c r="L37" t="n">
-        <v>72.2</v>
+        <v>98.14</v>
       </c>
       <c r="M37" t="n">
-        <v>53.92</v>
+        <v>61.72</v>
       </c>
       <c r="N37" t="n">
-        <v>48.39</v>
+        <v>51.92</v>
       </c>
       <c r="O37" t="n">
-        <v>49.28</v>
+        <v>50.65</v>
       </c>
       <c r="P37" t="n">
-        <v>27.16</v>
+        <v>36.16</v>
       </c>
       <c r="Q37" t="n">
-        <v>29.24</v>
+        <v>29.61</v>
       </c>
       <c r="R37" t="n">
-        <v>0.93</v>
+        <v>1.22</v>
       </c>
       <c r="S37" t="n">
-        <v>32.47</v>
+        <v>32.78</v>
       </c>
       <c r="T37" t="n">
-        <v>32.96</v>
+        <v>33.32</v>
       </c>
       <c r="U37" t="n">
-        <v>32.15</v>
+        <v>32.61</v>
       </c>
       <c r="V37" t="n">
-        <v>1.26</v>
+        <v>1.68</v>
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
@@ -3317,68 +3317,68 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>77.31999999999999</v>
+        <v>79.05</v>
       </c>
       <c r="D38" t="n">
-        <v>1.9</v>
+        <v>2.24</v>
       </c>
       <c r="E38" t="n">
-        <v>74.42</v>
+        <v>76.01000000000001</v>
       </c>
       <c r="F38" t="n">
-        <v>73.22</v>
+        <v>73.83</v>
       </c>
       <c r="G38" t="n">
-        <v>70.90000000000001</v>
+        <v>71.55</v>
       </c>
       <c r="H38" t="n">
-        <v>0.994</v>
+        <v>1.393</v>
       </c>
       <c r="I38" t="n">
-        <v>0.063</v>
+        <v>0.329</v>
       </c>
       <c r="J38" t="n">
-        <v>81.78</v>
+        <v>80.29000000000001</v>
       </c>
       <c r="K38" t="n">
-        <v>74.01000000000001</v>
+        <v>76.11</v>
       </c>
       <c r="L38" t="n">
-        <v>97.31999999999999</v>
+        <v>88.67</v>
       </c>
       <c r="M38" t="n">
-        <v>79.20999999999999</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="N38" t="n">
-        <v>67.62</v>
+        <v>71.03</v>
       </c>
       <c r="O38" t="n">
-        <v>56.93</v>
+        <v>59.33</v>
       </c>
       <c r="P38" t="n">
-        <v>34.27</v>
+        <v>51.57</v>
       </c>
       <c r="Q38" t="n">
-        <v>19.14</v>
+        <v>21.15</v>
       </c>
       <c r="R38" t="n">
-        <v>1.79</v>
+        <v>2.44</v>
       </c>
       <c r="S38" t="n">
-        <v>75.51000000000001</v>
+        <v>78.91</v>
       </c>
       <c r="T38" t="n">
-        <v>77.68000000000001</v>
+        <v>81.76000000000001</v>
       </c>
       <c r="U38" t="n">
-        <v>75.23999999999999</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="V38" t="n">
-        <v>4.03</v>
+        <v>6.07</v>
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
@@ -3394,68 +3394,68 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>60.14</v>
+        <v>62.04</v>
       </c>
       <c r="D39" t="n">
-        <v>4.45</v>
+        <v>3.16</v>
       </c>
       <c r="E39" t="n">
-        <v>57.99</v>
+        <v>59.05</v>
       </c>
       <c r="F39" t="n">
-        <v>58.89</v>
+        <v>59</v>
       </c>
       <c r="G39" t="n">
-        <v>58.98</v>
+        <v>59.15</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.8179999999999999</v>
+        <v>-0.493</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.998</v>
+        <v>-0.894</v>
       </c>
       <c r="J39" t="n">
-        <v>44.96</v>
+        <v>59.28</v>
       </c>
       <c r="K39" t="n">
-        <v>39.36</v>
+        <v>46</v>
       </c>
       <c r="L39" t="n">
-        <v>56.16</v>
+        <v>85.84</v>
       </c>
       <c r="M39" t="n">
-        <v>59.57</v>
+        <v>67.81</v>
       </c>
       <c r="N39" t="n">
-        <v>52.89</v>
+        <v>58.48</v>
       </c>
       <c r="O39" t="n">
-        <v>46.93</v>
+        <v>50.54</v>
       </c>
       <c r="P39" t="n">
-        <v>50.1</v>
+        <v>43.69</v>
       </c>
       <c r="Q39" t="n">
-        <v>29.13</v>
+        <v>29.79</v>
       </c>
       <c r="R39" t="n">
-        <v>1.72</v>
+        <v>1.47</v>
       </c>
       <c r="S39" t="n">
-        <v>57.51</v>
+        <v>60.68</v>
       </c>
       <c r="T39" t="n">
-        <v>60.88</v>
+        <v>62.87</v>
       </c>
       <c r="U39" t="n">
-        <v>57.5</v>
+        <v>60.5</v>
       </c>
       <c r="V39" t="n">
-        <v>2.88</v>
+        <v>2.51</v>
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
@@ -3471,68 +3471,68 @@
         </is>
       </c>
       <c r="C40" t="n">
+        <v>48.16</v>
+      </c>
+      <c r="D40" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="E40" t="n">
+        <v>45.99</v>
+      </c>
+      <c r="F40" t="n">
+        <v>45.82</v>
+      </c>
+      <c r="G40" t="n">
+        <v>45.06</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.203</v>
+      </c>
+      <c r="I40" t="n">
+        <v>-0.178</v>
+      </c>
+      <c r="J40" t="n">
+        <v>65.76000000000001</v>
+      </c>
+      <c r="K40" t="n">
+        <v>54.99</v>
+      </c>
+      <c r="L40" t="n">
+        <v>87.3</v>
+      </c>
+      <c r="M40" t="n">
+        <v>72.70999999999999</v>
+      </c>
+      <c r="N40" t="n">
+        <v>63.64</v>
+      </c>
+      <c r="O40" t="n">
+        <v>54.24</v>
+      </c>
+      <c r="P40" t="n">
+        <v>159.01</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>88.78</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="S40" t="n">
         <v>46.92</v>
       </c>
-      <c r="D40" t="n">
-        <v>4.69</v>
-      </c>
-      <c r="E40" t="n">
-        <v>45.35</v>
-      </c>
-      <c r="F40" t="n">
-        <v>45.56</v>
-      </c>
-      <c r="G40" t="n">
-        <v>44.79</v>
-      </c>
-      <c r="H40" t="n">
-        <v>-0.019</v>
-      </c>
-      <c r="I40" t="n">
-        <v>-0.267</v>
-      </c>
-      <c r="J40" t="n">
-        <v>53.2</v>
-      </c>
-      <c r="K40" t="n">
-        <v>49.6</v>
-      </c>
-      <c r="L40" t="n">
-        <v>60.4</v>
-      </c>
-      <c r="M40" t="n">
-        <v>65.77</v>
-      </c>
-      <c r="N40" t="n">
-        <v>58.8</v>
-      </c>
-      <c r="O40" t="n">
-        <v>51.31</v>
-      </c>
-      <c r="P40" t="n">
-        <v>164.47</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>83.73</v>
-      </c>
-      <c r="R40" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="S40" t="n">
-        <v>44.69</v>
-      </c>
       <c r="T40" t="n">
-        <v>47.37</v>
+        <v>48.6</v>
       </c>
       <c r="U40" t="n">
-        <v>44.58</v>
+        <v>46.6</v>
       </c>
       <c r="V40" t="n">
-        <v>4.46</v>
+        <v>4.32</v>
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
@@ -3548,68 +3548,68 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>17.4</v>
+        <v>17.76</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.57</v>
+        <v>2.07</v>
       </c>
       <c r="E41" t="n">
-        <v>17.68</v>
+        <v>17.61</v>
       </c>
       <c r="F41" t="n">
-        <v>18.16</v>
+        <v>18.04</v>
       </c>
       <c r="G41" t="n">
-        <v>18.24</v>
+        <v>18.23</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.353</v>
+        <v>-0.348</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.284</v>
+        <v>-0.297</v>
       </c>
       <c r="J41" t="n">
-        <v>17.24</v>
+        <v>23.67</v>
       </c>
       <c r="K41" t="n">
-        <v>27.41</v>
+        <v>26.16</v>
       </c>
       <c r="L41" t="n">
-        <v>-3.09</v>
+        <v>18.7</v>
       </c>
       <c r="M41" t="n">
-        <v>29.96</v>
+        <v>43.75</v>
       </c>
       <c r="N41" t="n">
-        <v>35.88</v>
+        <v>42.42</v>
       </c>
       <c r="O41" t="n">
-        <v>37.58</v>
+        <v>40.92</v>
       </c>
       <c r="P41" t="n">
-        <v>17.95</v>
+        <v>25.32</v>
       </c>
       <c r="Q41" t="n">
-        <v>17.11</v>
+        <v>17.61</v>
       </c>
       <c r="R41" t="n">
-        <v>1.05</v>
+        <v>1.44</v>
       </c>
       <c r="S41" t="n">
-        <v>17.44</v>
+        <v>17.7</v>
       </c>
       <c r="T41" t="n">
-        <v>17.65</v>
+        <v>17.99</v>
       </c>
       <c r="U41" t="n">
-        <v>17.29</v>
+        <v>17.64</v>
       </c>
       <c r="V41" t="n">
-        <v>1.37</v>
+        <v>1.93</v>
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
@@ -3625,68 +3625,68 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>72.3</v>
+        <v>73.2</v>
       </c>
       <c r="D42" t="n">
-        <v>-1.46</v>
+        <v>1.24</v>
       </c>
       <c r="E42" t="n">
-        <v>74.08</v>
+        <v>73.41</v>
       </c>
       <c r="F42" t="n">
-        <v>77.14</v>
+        <v>76.76000000000001</v>
       </c>
       <c r="G42" t="n">
-        <v>76.39</v>
+        <v>76.44</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.892</v>
+        <v>-1.056</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.511</v>
+        <v>-0.633</v>
       </c>
       <c r="J42" t="n">
-        <v>14.99</v>
+        <v>13.22</v>
       </c>
       <c r="K42" t="n">
-        <v>32.61</v>
+        <v>26.14</v>
       </c>
       <c r="L42" t="n">
-        <v>-20.25</v>
+        <v>-12.64</v>
       </c>
       <c r="M42" t="n">
-        <v>31.99</v>
+        <v>37.66</v>
       </c>
       <c r="N42" t="n">
-        <v>39.4</v>
+        <v>41.94</v>
       </c>
       <c r="O42" t="n">
-        <v>40.91</v>
+        <v>42.06</v>
       </c>
       <c r="P42" t="n">
-        <v>5.98</v>
+        <v>7.1</v>
       </c>
       <c r="Q42" t="n">
-        <v>7.09</v>
+        <v>7.21</v>
       </c>
       <c r="R42" t="n">
-        <v>0.84</v>
+        <v>0.98</v>
       </c>
       <c r="S42" t="n">
-        <v>73.06</v>
+        <v>72</v>
       </c>
       <c r="T42" t="n">
-        <v>73.34999999999999</v>
+        <v>74.28</v>
       </c>
       <c r="U42" t="n">
-        <v>71.84999999999999</v>
+        <v>72</v>
       </c>
       <c r="V42" t="n">
-        <v>2.28</v>
+        <v>2.71</v>
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
@@ -3702,68 +3702,68 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>37.54</v>
+        <v>38.02</v>
       </c>
       <c r="D43" t="n">
-        <v>0.78</v>
+        <v>1.28</v>
       </c>
       <c r="E43" t="n">
-        <v>36.39</v>
+        <v>36.87</v>
       </c>
       <c r="F43" t="n">
-        <v>36.66</v>
+        <v>36.75</v>
       </c>
       <c r="G43" t="n">
-        <v>36.59</v>
+        <v>36.7</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.382</v>
+        <v>-0.251</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.585</v>
+        <v>-0.523</v>
       </c>
       <c r="J43" t="n">
-        <v>64.8</v>
+        <v>74.72</v>
       </c>
       <c r="K43" t="n">
-        <v>50.41</v>
+        <v>58.51</v>
       </c>
       <c r="L43" t="n">
-        <v>93.58</v>
+        <v>107.13</v>
       </c>
       <c r="M43" t="n">
-        <v>69</v>
+        <v>74.41</v>
       </c>
       <c r="N43" t="n">
-        <v>55.91</v>
+        <v>59.67</v>
       </c>
       <c r="O43" t="n">
-        <v>48.07</v>
+        <v>49.79</v>
       </c>
       <c r="P43" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="S43" t="n">
+        <v>37.6</v>
+      </c>
+      <c r="T43" t="n">
+        <v>38.19</v>
+      </c>
+      <c r="U43" t="n">
+        <v>37.35</v>
+      </c>
+      <c r="V43" t="n">
         <v>3.65</v>
       </c>
-      <c r="Q43" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="R43" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="S43" t="n">
-        <v>37.25</v>
-      </c>
-      <c r="T43" t="n">
-        <v>37.69</v>
-      </c>
-      <c r="U43" t="n">
-        <v>36.85</v>
-      </c>
-      <c r="V43" t="n">
-        <v>2.89</v>
-      </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
@@ -3779,68 +3779,68 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>41.51</v>
+        <v>41.98</v>
       </c>
       <c r="D44" t="n">
-        <v>1.99</v>
+        <v>1.13</v>
       </c>
       <c r="E44" t="n">
-        <v>40.69</v>
+        <v>41.04</v>
       </c>
       <c r="F44" t="n">
-        <v>40.91</v>
+        <v>40.99</v>
       </c>
       <c r="G44" t="n">
-        <v>40.18</v>
+        <v>40.38</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.083</v>
+        <v>0.028</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.305</v>
+        <v>-0.237</v>
       </c>
       <c r="J44" t="n">
-        <v>46.66</v>
+        <v>58.56</v>
       </c>
       <c r="K44" t="n">
-        <v>46.34</v>
+        <v>50.41</v>
       </c>
       <c r="L44" t="n">
-        <v>47.3</v>
+        <v>74.84999999999999</v>
       </c>
       <c r="M44" t="n">
-        <v>63.44</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="N44" t="n">
-        <v>56.03</v>
+        <v>58.85</v>
       </c>
       <c r="O44" t="n">
-        <v>49.97</v>
+        <v>51.41</v>
       </c>
       <c r="P44" t="n">
-        <v>1.4</v>
+        <v>1.68</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="R44" t="n">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="S44" t="n">
-        <v>41.76</v>
+        <v>41.53</v>
       </c>
       <c r="T44" t="n">
-        <v>41.9</v>
+        <v>42.38</v>
       </c>
       <c r="U44" t="n">
-        <v>40.9</v>
+        <v>41.53</v>
       </c>
       <c r="V44" t="n">
-        <v>3.22</v>
+        <v>3.85</v>
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
@@ -3856,68 +3856,68 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>36.74</v>
+        <v>38.56</v>
       </c>
       <c r="D45" t="n">
-        <v>-2.68</v>
+        <v>4.95</v>
       </c>
       <c r="E45" t="n">
-        <v>38.57</v>
+        <v>38.31</v>
       </c>
       <c r="F45" t="n">
+        <v>39.22</v>
+      </c>
+      <c r="G45" t="n">
+        <v>38.34</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.292</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.493</v>
+      </c>
+      <c r="J45" t="n">
+        <v>38.95</v>
+      </c>
+      <c r="K45" t="n">
+        <v>43.31</v>
+      </c>
+      <c r="L45" t="n">
+        <v>30.23</v>
+      </c>
+      <c r="M45" t="n">
+        <v>49.04</v>
+      </c>
+      <c r="N45" t="n">
+        <v>50.85</v>
+      </c>
+      <c r="O45" t="n">
+        <v>51</v>
+      </c>
+      <c r="P45" t="n">
+        <v>65.58</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>64.09</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="S45" t="n">
+        <v>37.23</v>
+      </c>
+      <c r="T45" t="n">
         <v>39.39</v>
       </c>
-      <c r="G45" t="n">
-        <v>38.16</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0.329</v>
-      </c>
-      <c r="I45" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="J45" t="n">
-        <v>32.88</v>
-      </c>
-      <c r="K45" t="n">
-        <v>45.49</v>
-      </c>
-      <c r="L45" t="n">
-        <v>7.66</v>
-      </c>
-      <c r="M45" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="N45" t="n">
-        <v>39.39</v>
-      </c>
-      <c r="O45" t="n">
-        <v>45.33</v>
-      </c>
-      <c r="P45" t="n">
-        <v>56.4</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>62.46</v>
-      </c>
-      <c r="R45" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="S45" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="T45" t="n">
-        <v>37.96</v>
-      </c>
       <c r="U45" t="n">
-        <v>36.69</v>
+        <v>36.98</v>
       </c>
       <c r="V45" t="n">
-        <v>3.25</v>
+        <v>3.78</v>
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
@@ -3933,68 +3933,68 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>55.22</v>
+        <v>57.01</v>
       </c>
       <c r="D46" t="n">
-        <v>-1.06</v>
+        <v>3.24</v>
       </c>
       <c r="E46" t="n">
-        <v>56.16</v>
+        <v>56.17</v>
       </c>
       <c r="F46" t="n">
-        <v>56.79</v>
+        <v>56.9</v>
       </c>
       <c r="G46" t="n">
-        <v>53.82</v>
+        <v>54.31</v>
       </c>
       <c r="H46" t="n">
-        <v>1.496</v>
+        <v>1.492</v>
       </c>
       <c r="I46" t="n">
-        <v>1.422</v>
+        <v>1.42</v>
       </c>
       <c r="J46" t="n">
-        <v>52.55</v>
+        <v>57.1</v>
       </c>
       <c r="K46" t="n">
-        <v>63.03</v>
+        <v>61.05</v>
       </c>
       <c r="L46" t="n">
-        <v>31.59</v>
+        <v>49.21</v>
       </c>
       <c r="M46" t="n">
-        <v>45.66</v>
+        <v>60.38</v>
       </c>
       <c r="N46" t="n">
-        <v>54.27</v>
+        <v>60.4</v>
       </c>
       <c r="O46" t="n">
-        <v>53.89</v>
+        <v>56.73</v>
       </c>
       <c r="P46" t="n">
-        <v>47.82</v>
+        <v>76.95</v>
       </c>
       <c r="Q46" t="n">
-        <v>60.74</v>
+        <v>62.86</v>
       </c>
       <c r="R46" t="n">
-        <v>0.79</v>
+        <v>1.22</v>
       </c>
       <c r="S46" t="n">
-        <v>55.55</v>
+        <v>55.1</v>
       </c>
       <c r="T46" t="n">
-        <v>56.33</v>
+        <v>57.1</v>
       </c>
       <c r="U46" t="n">
-        <v>55</v>
+        <v>54.72</v>
       </c>
       <c r="V46" t="n">
-        <v>3.07</v>
+        <v>4.93</v>
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
@@ -4010,68 +4010,68 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>62.03</v>
+        <v>63.16</v>
       </c>
       <c r="D47" t="n">
-        <v>0.13</v>
+        <v>1.82</v>
       </c>
       <c r="E47" t="n">
-        <v>62.66</v>
+        <v>62.3</v>
       </c>
       <c r="F47" t="n">
-        <v>65.17</v>
+        <v>64.78</v>
       </c>
       <c r="G47" t="n">
-        <v>62.5</v>
+        <v>62.79</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.336</v>
+        <v>-0.35</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.396</v>
+        <v>-0.408</v>
       </c>
       <c r="J47" t="n">
-        <v>25.61</v>
+        <v>27.8</v>
       </c>
       <c r="K47" t="n">
-        <v>34.63</v>
+        <v>32.36</v>
       </c>
       <c r="L47" t="n">
-        <v>7.57</v>
+        <v>18.69</v>
       </c>
       <c r="M47" t="n">
-        <v>39.54</v>
+        <v>48.19</v>
       </c>
       <c r="N47" t="n">
-        <v>45.24</v>
+        <v>48.76</v>
       </c>
       <c r="O47" t="n">
-        <v>44.54</v>
+        <v>45.93</v>
       </c>
       <c r="P47" t="n">
-        <v>4.74</v>
+        <v>7.53</v>
       </c>
       <c r="Q47" t="n">
-        <v>9.23</v>
+        <v>9.42</v>
       </c>
       <c r="R47" t="n">
-        <v>0.51</v>
+        <v>0.8</v>
       </c>
       <c r="S47" t="n">
-        <v>61.36</v>
+        <v>61.8</v>
       </c>
       <c r="T47" t="n">
-        <v>62.99</v>
+        <v>63.51</v>
       </c>
       <c r="U47" t="n">
-        <v>61.36</v>
+        <v>61.66</v>
       </c>
       <c r="V47" t="n">
-        <v>2.7</v>
+        <v>4.29</v>
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
@@ -4087,68 +4087,68 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>26.93</v>
+        <v>28.33</v>
       </c>
       <c r="D48" t="n">
-        <v>-1.89</v>
+        <v>5.2</v>
       </c>
       <c r="E48" t="n">
-        <v>26.93</v>
+        <v>27.25</v>
       </c>
       <c r="F48" t="n">
-        <v>26.92</v>
+        <v>27.08</v>
       </c>
       <c r="G48" t="n">
-        <v>26.42</v>
+        <v>26.61</v>
       </c>
       <c r="H48" t="n">
-        <v>0.112</v>
+        <v>0.203</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.003</v>
+        <v>0.011</v>
       </c>
       <c r="J48" t="n">
-        <v>49.57</v>
+        <v>65.94</v>
       </c>
       <c r="K48" t="n">
-        <v>49.01</v>
+        <v>54.66</v>
       </c>
       <c r="L48" t="n">
-        <v>50.68</v>
+        <v>88.5</v>
       </c>
       <c r="M48" t="n">
-        <v>51.64</v>
+        <v>67.45</v>
       </c>
       <c r="N48" t="n">
-        <v>51.89</v>
+        <v>60.48</v>
       </c>
       <c r="O48" t="n">
-        <v>50.33</v>
+        <v>53.91</v>
       </c>
       <c r="P48" t="n">
-        <v>33.33</v>
+        <v>52.53</v>
       </c>
       <c r="Q48" t="n">
-        <v>31.83</v>
+        <v>33.59</v>
       </c>
       <c r="R48" t="n">
-        <v>1.05</v>
+        <v>1.56</v>
       </c>
       <c r="S48" t="n">
-        <v>27.26</v>
+        <v>27.23</v>
       </c>
       <c r="T48" t="n">
-        <v>27.58</v>
+        <v>28.36</v>
       </c>
       <c r="U48" t="n">
-        <v>26.75</v>
+        <v>27.14</v>
       </c>
       <c r="V48" t="n">
-        <v>4.85</v>
+        <v>7.64</v>
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
@@ -4164,68 +4164,68 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>27.55</v>
+        <v>27.94</v>
       </c>
       <c r="D49" t="n">
-        <v>7.07</v>
+        <v>1.42</v>
       </c>
       <c r="E49" t="n">
-        <v>26.16</v>
+        <v>26.65</v>
       </c>
       <c r="F49" t="n">
-        <v>26.08</v>
+        <v>26.34</v>
       </c>
       <c r="G49" t="n">
-        <v>25.16</v>
+        <v>25.35</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.08</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.356</v>
+        <v>-0.282</v>
       </c>
       <c r="J49" t="n">
-        <v>61.36</v>
+        <v>70.06999999999999</v>
       </c>
       <c r="K49" t="n">
-        <v>60.37</v>
+        <v>63.61</v>
       </c>
       <c r="L49" t="n">
-        <v>63.33</v>
+        <v>83.01000000000001</v>
       </c>
       <c r="M49" t="n">
-        <v>69.83</v>
+        <v>72.59</v>
       </c>
       <c r="N49" t="n">
-        <v>59.72</v>
+        <v>61.59</v>
       </c>
       <c r="O49" t="n">
-        <v>53.92</v>
+        <v>54.59</v>
       </c>
       <c r="P49" t="n">
-        <v>349.36</v>
+        <v>305.05</v>
       </c>
       <c r="Q49" t="n">
-        <v>211.07</v>
+        <v>214.59</v>
       </c>
       <c r="R49" t="n">
-        <v>1.66</v>
+        <v>1.42</v>
       </c>
       <c r="S49" t="n">
-        <v>26.51</v>
+        <v>28</v>
       </c>
       <c r="T49" t="n">
-        <v>28.18</v>
+        <v>28.35</v>
       </c>
       <c r="U49" t="n">
-        <v>26.2</v>
+        <v>27.7</v>
       </c>
       <c r="V49" t="n">
-        <v>10.39</v>
+        <v>9.07</v>
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
@@ -4241,68 +4241,68 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>23.12</v>
+        <v>23.19</v>
       </c>
       <c r="D50" t="n">
-        <v>1.31</v>
+        <v>0.3</v>
       </c>
       <c r="E50" t="n">
-        <v>23</v>
+        <v>23.05</v>
       </c>
       <c r="F50" t="n">
-        <v>23.62</v>
+        <v>23.51</v>
       </c>
       <c r="G50" t="n">
-        <v>23.3</v>
+        <v>23.35</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.28</v>
+        <v>-0.276</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.291</v>
+        <v>-0.293</v>
       </c>
       <c r="J50" t="n">
-        <v>31.32</v>
+        <v>34.59</v>
       </c>
       <c r="K50" t="n">
-        <v>38.13</v>
+        <v>36.95</v>
       </c>
       <c r="L50" t="n">
-        <v>17.72</v>
+        <v>29.88</v>
       </c>
       <c r="M50" t="n">
-        <v>43.85</v>
+        <v>46.01</v>
       </c>
       <c r="N50" t="n">
-        <v>44.85</v>
+        <v>45.75</v>
       </c>
       <c r="O50" t="n">
-        <v>42.67</v>
+        <v>42.72</v>
       </c>
       <c r="P50" t="n">
-        <v>3.66</v>
+        <v>3.97</v>
       </c>
       <c r="Q50" t="n">
-        <v>4.36</v>
+        <v>4.42</v>
       </c>
       <c r="R50" t="n">
-        <v>0.84</v>
+        <v>0.9</v>
       </c>
       <c r="S50" t="n">
-        <v>22.85</v>
+        <v>23.25</v>
       </c>
       <c r="T50" t="n">
-        <v>23.33</v>
+        <v>23.55</v>
       </c>
       <c r="U50" t="n">
-        <v>22.7</v>
+        <v>23.09</v>
       </c>
       <c r="V50" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
@@ -4318,68 +4318,68 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>73.19</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="D51" t="n">
-        <v>8.16</v>
+        <v>4.39</v>
       </c>
       <c r="E51" t="n">
-        <v>72.29000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="F51" t="n">
-        <v>74.59999999999999</v>
+        <v>74.26000000000001</v>
       </c>
       <c r="G51" t="n">
-        <v>73.58</v>
+        <v>74.37</v>
       </c>
       <c r="H51" t="n">
-        <v>2.307</v>
+        <v>2.378</v>
       </c>
       <c r="I51" t="n">
-        <v>3.65</v>
+        <v>3.373</v>
       </c>
       <c r="J51" t="n">
-        <v>24.01</v>
+        <v>39</v>
       </c>
       <c r="K51" t="n">
-        <v>30.47</v>
+        <v>33.31</v>
       </c>
       <c r="L51" t="n">
-        <v>11.09</v>
+        <v>50.37</v>
       </c>
       <c r="M51" t="n">
-        <v>50.11</v>
+        <v>58.03</v>
       </c>
       <c r="N51" t="n">
-        <v>52.5</v>
+        <v>56.57</v>
       </c>
       <c r="O51" t="n">
-        <v>55.17</v>
+        <v>57.2</v>
       </c>
       <c r="P51" t="n">
-        <v>42.81</v>
+        <v>37.01</v>
       </c>
       <c r="Q51" t="n">
-        <v>35.19</v>
+        <v>35.73</v>
       </c>
       <c r="R51" t="n">
-        <v>1.22</v>
+        <v>1.04</v>
       </c>
       <c r="S51" t="n">
-        <v>68.7</v>
+        <v>75</v>
       </c>
       <c r="T51" t="n">
-        <v>74.44</v>
+        <v>77.59</v>
       </c>
       <c r="U51" t="n">
-        <v>67.95</v>
+        <v>74</v>
       </c>
       <c r="V51" t="n">
-        <v>9.43</v>
+        <v>8.15</v>
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
@@ -4395,68 +4395,68 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>45.56</v>
+        <v>48.2</v>
       </c>
       <c r="D52" t="n">
-        <v>2.71</v>
+        <v>5.79</v>
       </c>
       <c r="E52" t="n">
-        <v>45.25</v>
+        <v>45.91</v>
       </c>
       <c r="F52" t="n">
-        <v>44.86</v>
+        <v>45.29</v>
       </c>
       <c r="G52" t="n">
-        <v>43.28</v>
+        <v>43.77</v>
       </c>
       <c r="H52" t="n">
-        <v>0.713</v>
+        <v>0.951</v>
       </c>
       <c r="I52" t="n">
-        <v>0.421</v>
+        <v>0.522</v>
       </c>
       <c r="J52" t="n">
-        <v>58.77</v>
+        <v>67.15000000000001</v>
       </c>
       <c r="K52" t="n">
-        <v>64.78</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="L52" t="n">
-        <v>46.76</v>
+        <v>70.31999999999999</v>
       </c>
       <c r="M52" t="n">
-        <v>60.09</v>
+        <v>74.28</v>
       </c>
       <c r="N52" t="n">
-        <v>58.26</v>
+        <v>66.77</v>
       </c>
       <c r="O52" t="n">
-        <v>54.53</v>
+        <v>59.31</v>
       </c>
       <c r="P52" t="n">
-        <v>101.4</v>
+        <v>150</v>
       </c>
       <c r="Q52" t="n">
-        <v>63.3</v>
+        <v>69.16</v>
       </c>
       <c r="R52" t="n">
-        <v>1.6</v>
+        <v>2.17</v>
       </c>
       <c r="S52" t="n">
-        <v>44.65</v>
+        <v>47.86</v>
       </c>
       <c r="T52" t="n">
-        <v>45.86</v>
+        <v>49.18</v>
       </c>
       <c r="U52" t="n">
-        <v>44.11</v>
+        <v>47.85</v>
       </c>
       <c r="V52" t="n">
-        <v>5.67</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
@@ -4472,68 +4472,68 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>29.31</v>
+        <v>28.1</v>
       </c>
       <c r="D53" t="n">
-        <v>-1.48</v>
+        <v>-4.13</v>
       </c>
       <c r="E53" t="n">
+        <v>29.48</v>
+      </c>
+      <c r="F53" t="n">
+        <v>29.74</v>
+      </c>
+      <c r="G53" t="n">
+        <v>30.24</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="J53" t="n">
+        <v>22.62</v>
+      </c>
+      <c r="K53" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="L53" t="n">
+        <v>9.449999999999999</v>
+      </c>
+      <c r="M53" t="n">
         <v>29.71</v>
       </c>
-      <c r="F53" t="n">
-        <v>29.97</v>
-      </c>
-      <c r="G53" t="n">
-        <v>30.37</v>
-      </c>
-      <c r="H53" t="n">
-        <v>0.269</v>
-      </c>
-      <c r="I53" t="n">
-        <v>0.451</v>
-      </c>
-      <c r="J53" t="n">
-        <v>30.97</v>
-      </c>
-      <c r="K53" t="n">
-        <v>32.49</v>
-      </c>
-      <c r="L53" t="n">
-        <v>27.95</v>
-      </c>
-      <c r="M53" t="n">
-        <v>40.57</v>
-      </c>
       <c r="N53" t="n">
-        <v>46.81</v>
+        <v>39.51</v>
       </c>
       <c r="O53" t="n">
-        <v>49.65</v>
+        <v>44.95</v>
       </c>
       <c r="P53" t="n">
-        <v>36.56</v>
+        <v>52.16</v>
       </c>
       <c r="Q53" t="n">
-        <v>38.57</v>
+        <v>37.79</v>
       </c>
       <c r="R53" t="n">
-        <v>0.95</v>
+        <v>1.38</v>
       </c>
       <c r="S53" t="n">
-        <v>29.76</v>
+        <v>28.33</v>
       </c>
       <c r="T53" t="n">
-        <v>30.27</v>
+        <v>28.54</v>
       </c>
       <c r="U53" t="n">
-        <v>29.21</v>
+        <v>27.89</v>
       </c>
       <c r="V53" t="n">
-        <v>2.57</v>
+        <v>3.67</v>
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
@@ -4549,68 +4549,68 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>63.76</v>
+        <v>61.25</v>
       </c>
       <c r="D54" t="n">
-        <v>0.46</v>
+        <v>-3.94</v>
       </c>
       <c r="E54" t="n">
-        <v>65.53</v>
+        <v>64.45999999999999</v>
       </c>
       <c r="F54" t="n">
-        <v>66.73999999999999</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="G54" t="n">
-        <v>67.25</v>
+        <v>66.84</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.235</v>
+        <v>-0.622</v>
       </c>
       <c r="I54" t="n">
-        <v>0.245</v>
+        <v>0.065</v>
       </c>
       <c r="J54" t="n">
-        <v>31.19</v>
+        <v>22.05</v>
       </c>
       <c r="K54" t="n">
-        <v>39.98</v>
+        <v>34</v>
       </c>
       <c r="L54" t="n">
-        <v>13.6</v>
+        <v>-1.86</v>
       </c>
       <c r="M54" t="n">
-        <v>31.49</v>
+        <v>22.77</v>
       </c>
       <c r="N54" t="n">
-        <v>41.32</v>
+        <v>35.57</v>
       </c>
       <c r="O54" t="n">
-        <v>45.9</v>
+        <v>42.74</v>
       </c>
       <c r="P54" t="n">
-        <v>1.09</v>
+        <v>2.2</v>
       </c>
       <c r="Q54" t="n">
-        <v>1.97</v>
+        <v>1.88</v>
       </c>
       <c r="R54" t="n">
-        <v>0.55</v>
+        <v>1.17</v>
       </c>
       <c r="S54" t="n">
-        <v>63.01</v>
+        <v>63.81</v>
       </c>
       <c r="T54" t="n">
-        <v>64.59999999999999</v>
+        <v>64.05</v>
       </c>
       <c r="U54" t="n">
-        <v>62.02</v>
+        <v>60.93</v>
       </c>
       <c r="V54" t="n">
-        <v>1.13</v>
+        <v>2.28</v>
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
@@ -4626,68 +4626,68 @@
         </is>
       </c>
       <c r="C55" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="D55" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="E55" t="n">
+        <v>33.63</v>
+      </c>
+      <c r="F55" t="n">
+        <v>34.01</v>
+      </c>
+      <c r="G55" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="H55" t="n">
+        <v>-0.519</v>
+      </c>
+      <c r="I55" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="J55" t="n">
+        <v>12.13</v>
+      </c>
+      <c r="K55" t="n">
+        <v>15.79</v>
+      </c>
+      <c r="L55" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="M55" t="n">
+        <v>29.18</v>
+      </c>
+      <c r="N55" t="n">
+        <v>36.62</v>
+      </c>
+      <c r="O55" t="n">
+        <v>40.55</v>
+      </c>
+      <c r="P55" t="n">
+        <v>14.32</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>12.33</v>
+      </c>
+      <c r="R55" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="S55" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="T55" t="n">
         <v>33.35</v>
       </c>
-      <c r="D55" t="n">
-        <v>-0.57</v>
-      </c>
-      <c r="E55" t="n">
-        <v>34.01</v>
-      </c>
-      <c r="F55" t="n">
-        <v>34.12</v>
-      </c>
-      <c r="G55" t="n">
-        <v>34.97</v>
-      </c>
-      <c r="H55" t="n">
-        <v>-0.477</v>
-      </c>
-      <c r="I55" t="n">
-        <v>-0.319</v>
-      </c>
-      <c r="J55" t="n">
-        <v>14.37</v>
-      </c>
-      <c r="K55" t="n">
-        <v>17.61</v>
-      </c>
-      <c r="L55" t="n">
-        <v>7.87</v>
-      </c>
-      <c r="M55" t="n">
-        <v>29.86</v>
-      </c>
-      <c r="N55" t="n">
-        <v>36.98</v>
-      </c>
-      <c r="O55" t="n">
-        <v>40.78</v>
-      </c>
-      <c r="P55" t="n">
-        <v>13.22</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>12.59</v>
-      </c>
-      <c r="R55" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="S55" t="n">
-        <v>33.52</v>
-      </c>
-      <c r="T55" t="n">
-        <v>33.59</v>
-      </c>
       <c r="U55" t="n">
-        <v>33.2</v>
+        <v>33.11</v>
       </c>
       <c r="V55" t="n">
-        <v>0.75</v>
+        <v>0.82</v>
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
@@ -4703,68 +4703,68 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>33.5</v>
+        <v>33.58</v>
       </c>
       <c r="D56" t="n">
-        <v>-1.06</v>
+        <v>0.24</v>
       </c>
       <c r="E56" t="n">
         <v>33.59</v>
       </c>
       <c r="F56" t="n">
-        <v>33.92</v>
+        <v>33.86</v>
       </c>
       <c r="G56" t="n">
-        <v>34.14</v>
+        <v>34.1</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.233</v>
+        <v>-0.242</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.198</v>
+        <v>-0.21</v>
       </c>
       <c r="J56" t="n">
-        <v>13.64</v>
+        <v>11.85</v>
       </c>
       <c r="K56" t="n">
-        <v>21.08</v>
+        <v>18</v>
       </c>
       <c r="L56" t="n">
-        <v>-1.23</v>
+        <v>-0.44</v>
       </c>
       <c r="M56" t="n">
-        <v>37.73</v>
+        <v>40.98</v>
       </c>
       <c r="N56" t="n">
-        <v>41.92</v>
+        <v>43.22</v>
       </c>
       <c r="O56" t="n">
-        <v>43.22</v>
+        <v>43.55</v>
       </c>
       <c r="P56" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="Q56" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="R56" t="n">
-        <v>0.95</v>
+        <v>1.02</v>
       </c>
       <c r="S56" t="n">
-        <v>33.86</v>
+        <v>33.5</v>
       </c>
       <c r="T56" t="n">
-        <v>33.92</v>
+        <v>33.85</v>
       </c>
       <c r="U56" t="n">
-        <v>33.48</v>
+        <v>33.45</v>
       </c>
       <c r="V56" t="n">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
@@ -4780,68 +4780,145 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>25.4</v>
+        <v>25.3</v>
       </c>
       <c r="D57" t="n">
-        <v>-1.82</v>
+        <v>-0.39</v>
       </c>
       <c r="E57" t="n">
-        <v>26.03</v>
+        <v>25.74</v>
       </c>
       <c r="F57" t="n">
-        <v>26.2</v>
+        <v>26.05</v>
       </c>
       <c r="G57" t="n">
-        <v>26.21</v>
+        <v>26.15</v>
       </c>
       <c r="H57" t="n">
-        <v>0.028</v>
+        <v>-0.041</v>
       </c>
       <c r="I57" t="n">
-        <v>0.119</v>
+        <v>0.081</v>
       </c>
       <c r="J57" t="n">
-        <v>18.93</v>
+        <v>14.06</v>
       </c>
       <c r="K57" t="n">
-        <v>30.29</v>
+        <v>24.88</v>
       </c>
       <c r="L57" t="n">
-        <v>-3.79</v>
+        <v>-7.57</v>
       </c>
       <c r="M57" t="n">
-        <v>33.05</v>
+        <v>31.44</v>
       </c>
       <c r="N57" t="n">
-        <v>42.61</v>
+        <v>41.62</v>
       </c>
       <c r="O57" t="n">
-        <v>45.29</v>
+        <v>44.32</v>
       </c>
       <c r="P57" t="n">
-        <v>9.300000000000001</v>
+        <v>10.86</v>
       </c>
       <c r="Q57" t="n">
-        <v>11.2</v>
+        <v>10.94</v>
       </c>
       <c r="R57" t="n">
-        <v>0.83</v>
+        <v>0.99</v>
       </c>
       <c r="S57" t="n">
-        <v>25.94</v>
+        <v>25.51</v>
       </c>
       <c r="T57" t="n">
-        <v>25.97</v>
+        <v>25.68</v>
       </c>
       <c r="U57" t="n">
-        <v>25.26</v>
+        <v>25.18</v>
       </c>
       <c r="V57" t="n">
-        <v>1.92</v>
+        <v>2.24</v>
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>300456</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>赛威电子</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>52.04</v>
+      </c>
+      <c r="D58" t="n">
+        <v>13.57</v>
+      </c>
+      <c r="E58" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="F58" t="n">
+        <v>49.42</v>
+      </c>
+      <c r="G58" t="n">
+        <v>50.83</v>
+      </c>
+      <c r="H58" t="n">
+        <v>-0.422</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="J58" t="n">
+        <v>27.74</v>
+      </c>
+      <c r="K58" t="n">
+        <v>26.07</v>
+      </c>
+      <c r="L58" t="n">
+        <v>31.07</v>
+      </c>
+      <c r="M58" t="n">
+        <v>63.69</v>
+      </c>
+      <c r="N58" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="O58" t="n">
+        <v>52.84</v>
+      </c>
+      <c r="P58" t="n">
+        <v>111.83</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>72.70999999999999</v>
+      </c>
+      <c r="R58" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="S58" t="n">
+        <v>47.7</v>
+      </c>
+      <c r="T58" t="n">
+        <v>54.59</v>
+      </c>
+      <c r="U58" t="n">
+        <v>47.38</v>
+      </c>
+      <c r="V58" t="n">
+        <v>18.72</v>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
